--- a/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
+++ b/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FF4DC4-D8E1-47B3-A09F-17F8FE3DE5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0738FBD8-8065-44BF-A917-2954EBC440FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{D57B88DC-6A9D-42A6-BE16-0F559C48DA93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sertifikat" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sertifikat!$B$2:$AJ$70</definedName>
   </definedNames>
@@ -889,20 +886,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1060,17 +1057,17 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sertifikat!$H$26:$H$35</c:f>
+              <c:f>Sertifikat!$H$26:$H$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0_ </c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1680-4EB8-B1FC-AE50047EA0ED}"/>
+              <c16:uniqueId val="{00000000-6C72-4356-A7AC-15A840331872}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1109,17 +1106,17 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sertifikat!$L$26:$L$35</c:f>
+              <c:f>Sertifikat!$L$26:$L$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0_ </c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1680-4EB8-B1FC-AE50047EA0ED}"/>
+              <c16:uniqueId val="{00000001-6C72-4356-A7AC-15A840331872}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1158,17 +1155,17 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sertifikat!$O$26:$O$35</c:f>
+              <c:f>Sertifikat!$O$26:$O$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0_ </c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1680-4EB8-B1FC-AE50047EA0ED}"/>
+              <c16:uniqueId val="{00000002-6C72-4356-A7AC-15A840331872}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1205,17 +1202,17 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sertifikat!$R$26:$R$35</c:f>
+              <c:f>Sertifikat!$R$26:$R$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0_ </c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-1680-4EB8-B1FC-AE50047EA0ED}"/>
+              <c16:uniqueId val="{00000003-6C72-4356-A7AC-15A840331872}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1256,17 +1253,17 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sertifikat!$U$26:$U$35</c:f>
+              <c:f>Sertifikat!$U$26:$U$32</c:f>
               <c:numCache>
                 <c:formatCode>0.0_ </c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-1680-4EB8-B1FC-AE50047EA0ED}"/>
+              <c16:uniqueId val="{00000004-6C72-4356-A7AC-15A840331872}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1280,11 +1277,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="283134335"/>
+        <c:axId val="936390815"/>
         <c:axId val="1"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="283134335"/>
+        <c:axId val="936390815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1382,7 +1379,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="283134335"/>
+        <c:crossAx val="936390815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1555,22 +1552,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>260350</xdr:colOff>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>150533</xdr:colOff>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>201706</xdr:rowOff>
+      <xdr:rowOff>203200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="3" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E41C6A1-CE7B-4687-9CCC-CB76351181A2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C1A6C03-80B8-4C89-8DA4-EC7C8F19F8AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1591,128 +1588,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Hitung Tekanan Naik"/>
-      <sheetName val="Hitung Tekanan Turun"/>
-      <sheetName val="Hitung U Gabungan"/>
-      <sheetName val="Sertifikat "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="26">
-          <cell r="H26">
-            <v>0</v>
-          </cell>
-          <cell r="L26">
-            <v>0</v>
-          </cell>
-          <cell r="O26">
-            <v>0</v>
-          </cell>
-          <cell r="R26">
-            <v>0</v>
-          </cell>
-          <cell r="U26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="H27">
-            <v>0.98066500000000001</v>
-          </cell>
-          <cell r="L27">
-            <v>0.98066500000000001</v>
-          </cell>
-          <cell r="O27">
-            <v>0.98066500000000001</v>
-          </cell>
-          <cell r="R27">
-            <v>1.2</v>
-          </cell>
-          <cell r="U27">
-            <v>1.2</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="H28">
-            <v>1.96133</v>
-          </cell>
-          <cell r="L28">
-            <v>1.96133</v>
-          </cell>
-          <cell r="O28">
-            <v>1.96133</v>
-          </cell>
-          <cell r="R28">
-            <v>2.1</v>
-          </cell>
-          <cell r="U28">
-            <v>2.1</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="H29">
-            <v>3</v>
-          </cell>
-          <cell r="L29">
-            <v>3</v>
-          </cell>
-          <cell r="O29">
-            <v>3</v>
-          </cell>
-          <cell r="R29">
-            <v>3.1</v>
-          </cell>
-          <cell r="U29">
-            <v>3.1</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="H30">
-            <v>4</v>
-          </cell>
-          <cell r="L30">
-            <v>4</v>
-          </cell>
-          <cell r="O30">
-            <v>4</v>
-          </cell>
-          <cell r="R30">
-            <v>4.0999999999999996</v>
-          </cell>
-          <cell r="U30">
-            <v>4.0999999999999996</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="H31">
-            <v>5</v>
-          </cell>
-          <cell r="L31">
-            <v>5</v>
-          </cell>
-          <cell r="O31">
-            <v>5</v>
-          </cell>
-          <cell r="R31">
-            <v>5.0999999999999996</v>
-          </cell>
-          <cell r="U31">
-            <v>5.0999999999999996</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3096,11 +2971,11 @@
       <c r="I25" s="71"/>
       <c r="J25" s="71"/>
       <c r="K25" s="72"/>
-      <c r="L25" s="73" t="s">
+      <c r="L25" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="73"/>
-      <c r="N25" s="73"/>
+      <c r="M25" s="77"/>
+      <c r="N25" s="77"/>
       <c r="O25" s="55" t="s">
         <v>27</v>
       </c>
@@ -3149,30 +3024,30 @@
       <c r="I26" s="66"/>
       <c r="J26" s="66"/>
       <c r="K26" s="66"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-      <c r="AA26" s="74"/>
-      <c r="AB26" s="74"/>
-      <c r="AC26" s="74"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="76"/>
-      <c r="AF26" s="76"/>
-      <c r="AG26" s="76"/>
-      <c r="AH26" s="76"/>
-      <c r="AI26" s="77"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="73"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="73"/>
+      <c r="T26" s="73"/>
+      <c r="U26" s="73"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="73"/>
+      <c r="AB26" s="73"/>
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="75"/>
+      <c r="AI26" s="76"/>
       <c r="AJ26" s="8"/>
     </row>
     <row r="27" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3184,34 +3059,34 @@
       <c r="E27" s="66"/>
       <c r="F27" s="66"/>
       <c r="G27" s="66"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="74"/>
-      <c r="S27" s="74"/>
-      <c r="T27" s="74"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="74"/>
-      <c r="W27" s="74"/>
-      <c r="X27" s="74"/>
-      <c r="Y27" s="74"/>
-      <c r="Z27" s="74"/>
-      <c r="AA27" s="74"/>
-      <c r="AB27" s="74"/>
-      <c r="AC27" s="74"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="73"/>
+      <c r="O27" s="73"/>
+      <c r="P27" s="73"/>
+      <c r="Q27" s="73"/>
+      <c r="R27" s="73"/>
+      <c r="S27" s="73"/>
+      <c r="T27" s="73"/>
+      <c r="U27" s="73"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="73"/>
+      <c r="X27" s="73"/>
+      <c r="Y27" s="73"/>
+      <c r="Z27" s="73"/>
+      <c r="AA27" s="73"/>
+      <c r="AB27" s="73"/>
+      <c r="AC27" s="73"/>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="75"/>
+      <c r="AF27" s="75"/>
+      <c r="AG27" s="75"/>
+      <c r="AH27" s="75"/>
+      <c r="AI27" s="76"/>
       <c r="AJ27" s="8"/>
     </row>
     <row r="28" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3223,34 +3098,34 @@
       <c r="E28" s="66"/>
       <c r="F28" s="66"/>
       <c r="G28" s="66"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="74"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="74"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="74"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="74"/>
-      <c r="Z28" s="74"/>
-      <c r="AA28" s="74"/>
-      <c r="AB28" s="74"/>
-      <c r="AC28" s="74"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
-      <c r="AF28" s="76"/>
-      <c r="AG28" s="76"/>
-      <c r="AH28" s="76"/>
-      <c r="AI28" s="77"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="73"/>
+      <c r="Q28" s="73"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="73"/>
+      <c r="T28" s="73"/>
+      <c r="U28" s="73"/>
+      <c r="V28" s="73"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="73"/>
+      <c r="Y28" s="73"/>
+      <c r="Z28" s="73"/>
+      <c r="AA28" s="73"/>
+      <c r="AB28" s="73"/>
+      <c r="AC28" s="73"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="75"/>
+      <c r="AF28" s="75"/>
+      <c r="AG28" s="75"/>
+      <c r="AH28" s="75"/>
+      <c r="AI28" s="76"/>
       <c r="AJ28" s="19"/>
     </row>
     <row r="29" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3262,34 +3137,34 @@
       <c r="E29" s="66"/>
       <c r="F29" s="66"/>
       <c r="G29" s="66"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="74"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="74"/>
-      <c r="S29" s="74"/>
-      <c r="T29" s="74"/>
-      <c r="U29" s="74"/>
-      <c r="V29" s="74"/>
-      <c r="W29" s="74"/>
-      <c r="X29" s="74"/>
-      <c r="Y29" s="74"/>
-      <c r="Z29" s="74"/>
-      <c r="AA29" s="74"/>
-      <c r="AB29" s="74"/>
-      <c r="AC29" s="74"/>
-      <c r="AD29" s="75"/>
-      <c r="AE29" s="76"/>
-      <c r="AF29" s="76"/>
-      <c r="AG29" s="76"/>
-      <c r="AH29" s="76"/>
-      <c r="AI29" s="77"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="73"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="73"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="73"/>
+      <c r="T29" s="73"/>
+      <c r="U29" s="73"/>
+      <c r="V29" s="73"/>
+      <c r="W29" s="73"/>
+      <c r="X29" s="73"/>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="73"/>
+      <c r="AA29" s="73"/>
+      <c r="AB29" s="73"/>
+      <c r="AC29" s="73"/>
+      <c r="AD29" s="74"/>
+      <c r="AE29" s="75"/>
+      <c r="AF29" s="75"/>
+      <c r="AG29" s="75"/>
+      <c r="AH29" s="75"/>
+      <c r="AI29" s="76"/>
       <c r="AJ29" s="19"/>
     </row>
     <row r="30" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3301,34 +3176,34 @@
       <c r="E30" s="66"/>
       <c r="F30" s="66"/>
       <c r="G30" s="66"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="74"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="74"/>
-      <c r="T30" s="74"/>
-      <c r="U30" s="74"/>
-      <c r="V30" s="74"/>
-      <c r="W30" s="74"/>
-      <c r="X30" s="74"/>
-      <c r="Y30" s="74"/>
-      <c r="Z30" s="74"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="73"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="73"/>
+      <c r="T30" s="73"/>
+      <c r="U30" s="73"/>
+      <c r="V30" s="73"/>
+      <c r="W30" s="73"/>
+      <c r="X30" s="73"/>
+      <c r="Y30" s="73"/>
+      <c r="Z30" s="73"/>
       <c r="AA30" s="78"/>
       <c r="AB30" s="78"/>
       <c r="AC30" s="78"/>
-      <c r="AD30" s="75"/>
-      <c r="AE30" s="76"/>
-      <c r="AF30" s="76"/>
-      <c r="AG30" s="76"/>
-      <c r="AH30" s="76"/>
-      <c r="AI30" s="77"/>
+      <c r="AD30" s="74"/>
+      <c r="AE30" s="75"/>
+      <c r="AF30" s="75"/>
+      <c r="AG30" s="75"/>
+      <c r="AH30" s="75"/>
+      <c r="AI30" s="76"/>
       <c r="AJ30" s="19"/>
     </row>
     <row r="31" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3340,34 +3215,34 @@
       <c r="E31" s="66"/>
       <c r="F31" s="66"/>
       <c r="G31" s="66"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="Z31" s="74"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="74"/>
-      <c r="AC31" s="74"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="73"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="73"/>
+      <c r="X31" s="73"/>
+      <c r="Y31" s="73"/>
+      <c r="Z31" s="73"/>
+      <c r="AA31" s="73"/>
+      <c r="AB31" s="73"/>
+      <c r="AC31" s="73"/>
+      <c r="AD31" s="74"/>
+      <c r="AE31" s="75"/>
+      <c r="AF31" s="75"/>
+      <c r="AG31" s="75"/>
+      <c r="AH31" s="75"/>
+      <c r="AI31" s="76"/>
       <c r="AJ31" s="19"/>
     </row>
     <row r="32" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3379,34 +3254,34 @@
       <c r="E32" s="66"/>
       <c r="F32" s="66"/>
       <c r="G32" s="66"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="74"/>
-      <c r="T32" s="74"/>
-      <c r="U32" s="74"/>
-      <c r="V32" s="74"/>
-      <c r="W32" s="74"/>
-      <c r="X32" s="74"/>
-      <c r="Y32" s="74"/>
-      <c r="Z32" s="74"/>
-      <c r="AA32" s="74"/>
-      <c r="AB32" s="74"/>
-      <c r="AC32" s="74"/>
-      <c r="AD32" s="75"/>
-      <c r="AE32" s="76"/>
-      <c r="AF32" s="76"/>
-      <c r="AG32" s="76"/>
-      <c r="AH32" s="76"/>
-      <c r="AI32" s="77"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="U32" s="73"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="73"/>
+      <c r="X32" s="73"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="73"/>
+      <c r="AB32" s="73"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="74"/>
+      <c r="AE32" s="75"/>
+      <c r="AF32" s="75"/>
+      <c r="AG32" s="75"/>
+      <c r="AH32" s="75"/>
+      <c r="AI32" s="76"/>
       <c r="AJ32" s="8"/>
     </row>
     <row r="33" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3428,24 +3303,24 @@
       <c r="O33" s="66"/>
       <c r="P33" s="66"/>
       <c r="Q33" s="66"/>
-      <c r="R33" s="74"/>
-      <c r="S33" s="74"/>
-      <c r="T33" s="74"/>
-      <c r="U33" s="74"/>
-      <c r="V33" s="74"/>
-      <c r="W33" s="74"/>
-      <c r="X33" s="74"/>
-      <c r="Y33" s="74"/>
-      <c r="Z33" s="74"/>
-      <c r="AA33" s="74"/>
-      <c r="AB33" s="74"/>
-      <c r="AC33" s="74"/>
-      <c r="AD33" s="75"/>
-      <c r="AE33" s="76"/>
-      <c r="AF33" s="76"/>
-      <c r="AG33" s="76"/>
-      <c r="AH33" s="76"/>
-      <c r="AI33" s="77"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="73"/>
+      <c r="T33" s="73"/>
+      <c r="U33" s="73"/>
+      <c r="V33" s="73"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="73"/>
+      <c r="Y33" s="73"/>
+      <c r="Z33" s="73"/>
+      <c r="AA33" s="73"/>
+      <c r="AB33" s="73"/>
+      <c r="AC33" s="73"/>
+      <c r="AD33" s="74"/>
+      <c r="AE33" s="75"/>
+      <c r="AF33" s="75"/>
+      <c r="AG33" s="75"/>
+      <c r="AH33" s="75"/>
+      <c r="AI33" s="76"/>
       <c r="AJ33" s="8"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3467,24 +3342,24 @@
       <c r="O34" s="66"/>
       <c r="P34" s="66"/>
       <c r="Q34" s="66"/>
-      <c r="R34" s="74"/>
-      <c r="S34" s="74"/>
-      <c r="T34" s="74"/>
-      <c r="U34" s="74"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="74"/>
-      <c r="X34" s="74"/>
-      <c r="Y34" s="74"/>
-      <c r="Z34" s="74"/>
-      <c r="AA34" s="74"/>
-      <c r="AB34" s="74"/>
-      <c r="AC34" s="74"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="73"/>
+      <c r="U34" s="73"/>
+      <c r="V34" s="73"/>
+      <c r="W34" s="73"/>
+      <c r="X34" s="73"/>
+      <c r="Y34" s="73"/>
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="73"/>
+      <c r="AB34" s="73"/>
+      <c r="AC34" s="73"/>
+      <c r="AD34" s="74"/>
+      <c r="AE34" s="75"/>
+      <c r="AF34" s="75"/>
+      <c r="AG34" s="75"/>
+      <c r="AH34" s="75"/>
+      <c r="AI34" s="76"/>
       <c r="AJ34" s="8"/>
     </row>
     <row r="35" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3506,24 +3381,24 @@
       <c r="O35" s="66"/>
       <c r="P35" s="66"/>
       <c r="Q35" s="66"/>
-      <c r="R35" s="74"/>
-      <c r="S35" s="74"/>
-      <c r="T35" s="74"/>
-      <c r="U35" s="74"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="74"/>
-      <c r="Y35" s="74"/>
-      <c r="Z35" s="74"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="74"/>
-      <c r="AC35" s="74"/>
-      <c r="AD35" s="75"/>
-      <c r="AE35" s="76"/>
-      <c r="AF35" s="76"/>
-      <c r="AG35" s="76"/>
-      <c r="AH35" s="76"/>
-      <c r="AI35" s="77"/>
+      <c r="R35" s="73"/>
+      <c r="S35" s="73"/>
+      <c r="T35" s="73"/>
+      <c r="U35" s="73"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="73"/>
+      <c r="X35" s="73"/>
+      <c r="Y35" s="73"/>
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="73"/>
+      <c r="AB35" s="73"/>
+      <c r="AC35" s="73"/>
+      <c r="AD35" s="74"/>
+      <c r="AE35" s="75"/>
+      <c r="AF35" s="75"/>
+      <c r="AG35" s="75"/>
+      <c r="AH35" s="75"/>
+      <c r="AI35" s="76"/>
       <c r="AJ35" s="8"/>
     </row>
     <row r="36" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3545,24 +3420,24 @@
       <c r="O36" s="66"/>
       <c r="P36" s="66"/>
       <c r="Q36" s="66"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="74"/>
-      <c r="T36" s="74"/>
-      <c r="U36" s="74"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="74"/>
-      <c r="X36" s="74"/>
-      <c r="Y36" s="74"/>
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="74"/>
-      <c r="AC36" s="74"/>
-      <c r="AD36" s="75"/>
-      <c r="AE36" s="76"/>
-      <c r="AF36" s="76"/>
-      <c r="AG36" s="76"/>
-      <c r="AH36" s="76"/>
-      <c r="AI36" s="77"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="73"/>
+      <c r="U36" s="73"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="73"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="73"/>
+      <c r="AC36" s="73"/>
+      <c r="AD36" s="74"/>
+      <c r="AE36" s="75"/>
+      <c r="AF36" s="75"/>
+      <c r="AG36" s="75"/>
+      <c r="AH36" s="75"/>
+      <c r="AI36" s="76"/>
       <c r="AJ36" s="8"/>
     </row>
     <row r="37" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4464,13 +4339,13 @@
     </row>
     <row r="68" spans="2:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="17"/>
-      <c r="C68" s="73" t="s">
+      <c r="C68" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="73"/>
+      <c r="D68" s="77"/>
+      <c r="E68" s="77"/>
+      <c r="F68" s="77"/>
+      <c r="G68" s="77"/>
       <c r="H68" s="55" t="s">
         <v>52</v>
       </c>
@@ -4486,13 +4361,13 @@
       <c r="P68" s="71"/>
       <c r="Q68" s="71"/>
       <c r="R68" s="72"/>
-      <c r="S68" s="73" t="s">
+      <c r="S68" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="T68" s="73"/>
-      <c r="U68" s="73"/>
-      <c r="V68" s="73"/>
-      <c r="W68" s="73"/>
+      <c r="T68" s="77"/>
+      <c r="U68" s="77"/>
+      <c r="V68" s="77"/>
+      <c r="W68" s="77"/>
       <c r="X68" s="100"/>
       <c r="Y68" s="100"/>
       <c r="Z68" s="100"/>

--- a/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
+++ b/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0738FBD8-8065-44BF-A917-2954EBC440FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE243DE-9F21-4870-94CE-174878320EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{D57B88DC-6A9D-42A6-BE16-0F559C48DA93}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>SERTIFIKAT KALIBRASI INTERNAL MANOMETER</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>Diterima oleh :</t>
-  </si>
-  <si>
-    <t>Diterbitkan tanggal : 01/07/2025</t>
   </si>
   <si>
     <r>
@@ -745,6 +742,189 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -757,12 +937,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -807,183 +981,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2023,201 +2020,201 @@
   <sheetData>
     <row r="1" spans="2:39" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:39" ht="19" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="35" t="s">
+      <c r="B2" s="87"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="37"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="95"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="95"/>
+      <c r="R2" s="95"/>
+      <c r="S2" s="95"/>
+      <c r="T2" s="95"/>
+      <c r="U2" s="95"/>
+      <c r="V2" s="95"/>
+      <c r="W2" s="95"/>
+      <c r="X2" s="95"/>
+      <c r="Y2" s="95"/>
+      <c r="Z2" s="95"/>
+      <c r="AA2" s="95"/>
+      <c r="AB2" s="95"/>
+      <c r="AC2" s="95"/>
+      <c r="AD2" s="95"/>
+      <c r="AE2" s="95"/>
+      <c r="AF2" s="95"/>
+      <c r="AG2" s="95"/>
+      <c r="AH2" s="95"/>
+      <c r="AI2" s="95"/>
+      <c r="AJ2" s="96"/>
     </row>
     <row r="3" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="39"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
+      <c r="AB3" s="97"/>
+      <c r="AC3" s="97"/>
+      <c r="AD3" s="97"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="97"/>
+      <c r="AI3" s="97"/>
+      <c r="AJ3" s="98"/>
     </row>
     <row r="4" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="39"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+      <c r="AA4" s="97"/>
+      <c r="AB4" s="97"/>
+      <c r="AC4" s="97"/>
+      <c r="AD4" s="97"/>
+      <c r="AE4" s="97"/>
+      <c r="AF4" s="97"/>
+      <c r="AG4" s="97"/>
+      <c r="AH4" s="97"/>
+      <c r="AI4" s="97"/>
+      <c r="AJ4" s="98"/>
     </row>
     <row r="5" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="40"/>
-      <c r="AB5" s="40"/>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="41"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
+      <c r="AA5" s="99"/>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
+      <c r="AH5" s="99"/>
+      <c r="AI5" s="99"/>
+      <c r="AJ5" s="100"/>
     </row>
     <row r="6" spans="2:39" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="42"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="92"/>
+      <c r="Q6" s="92"/>
+      <c r="R6" s="92"/>
+      <c r="S6" s="92"/>
+      <c r="T6" s="92"/>
+      <c r="U6" s="92"/>
+      <c r="V6" s="92"/>
+      <c r="W6" s="92"/>
+      <c r="X6" s="92"/>
+      <c r="Y6" s="92"/>
+      <c r="Z6" s="92"/>
+      <c r="AA6" s="92"/>
+      <c r="AB6" s="92"/>
+      <c r="AC6" s="92"/>
+      <c r="AD6" s="92"/>
+      <c r="AE6" s="92"/>
+      <c r="AF6" s="92"/>
+      <c r="AG6" s="92"/>
+      <c r="AH6" s="92"/>
+      <c r="AI6" s="92"/>
+      <c r="AJ6" s="101"/>
     </row>
     <row r="7" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
       <c r="H7" s="4" t="s">
         <v>2</v>
       </c>
@@ -2231,15 +2228,15 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="45" t="s">
+      <c r="S7" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
+      <c r="T7" s="104"/>
+      <c r="U7" s="104"/>
+      <c r="V7" s="104"/>
+      <c r="W7" s="104"/>
+      <c r="X7" s="104"/>
+      <c r="Y7" s="104"/>
       <c r="Z7" s="6" t="s">
         <v>2</v>
       </c>
@@ -2255,14 +2252,14 @@
       <c r="AJ7" s="8"/>
     </row>
     <row r="8" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
       <c r="H8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2276,15 +2273,15 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
+      <c r="S8" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="T8" s="104"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="104"/>
+      <c r="W8" s="104"/>
+      <c r="X8" s="104"/>
+      <c r="Y8" s="104"/>
       <c r="Z8" s="6" t="s">
         <v>2</v>
       </c>
@@ -2300,14 +2297,14 @@
       <c r="AJ8" s="8"/>
     </row>
     <row r="9" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
       <c r="H9" s="4" t="s">
         <v>2</v>
       </c>
@@ -2321,15 +2318,15 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="103"/>
       <c r="Z9" s="6" t="s">
         <v>2</v>
       </c>
@@ -2348,14 +2345,14 @@
       <c r="AM9" s="11"/>
     </row>
     <row r="10" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
       <c r="H10" s="4" t="s">
         <v>2</v>
       </c>
@@ -2369,15 +2366,15 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="45" t="s">
+      <c r="S10" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
+      <c r="T10" s="104"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="104"/>
+      <c r="W10" s="104"/>
+      <c r="X10" s="104"/>
+      <c r="Y10" s="104"/>
       <c r="Z10" s="6" t="s">
         <v>2</v>
       </c>
@@ -2396,14 +2393,14 @@
       <c r="AM10" s="11"/>
     </row>
     <row r="11" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
       <c r="H11" s="4" t="s">
         <v>2</v>
       </c>
@@ -2417,15 +2414,15 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="45" t="s">
+      <c r="S11" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
+      <c r="T11" s="104"/>
+      <c r="U11" s="104"/>
+      <c r="V11" s="104"/>
+      <c r="W11" s="104"/>
+      <c r="X11" s="104"/>
+      <c r="Y11" s="104"/>
       <c r="Z11" s="6" t="s">
         <v>2</v>
       </c>
@@ -2444,14 +2441,14 @@
       <c r="AM11" s="11"/>
     </row>
     <row r="12" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
       <c r="H12" s="4" t="s">
         <v>2</v>
       </c>
@@ -2465,43 +2462,43 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="45" t="s">
+      <c r="S12" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
+      <c r="T12" s="104"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="104"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="104"/>
+      <c r="Y12" s="104"/>
       <c r="Z12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="46" t="s">
+      <c r="AA12" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="AB12" s="46"/>
-      <c r="AC12" s="46"/>
-      <c r="AD12" s="46"/>
-      <c r="AE12" s="46"/>
-      <c r="AF12" s="46"/>
-      <c r="AG12" s="46"/>
-      <c r="AH12" s="46"/>
-      <c r="AI12" s="46"/>
+      <c r="AB12" s="105"/>
+      <c r="AC12" s="105"/>
+      <c r="AD12" s="105"/>
+      <c r="AE12" s="105"/>
+      <c r="AF12" s="105"/>
+      <c r="AG12" s="105"/>
+      <c r="AH12" s="105"/>
+      <c r="AI12" s="105"/>
       <c r="AJ12" s="10"/>
       <c r="AK12" s="11"/>
       <c r="AL12" s="11"/>
       <c r="AM12" s="11"/>
     </row>
     <row r="13" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
       <c r="H13" s="4" t="s">
         <v>2</v>
       </c>
@@ -2523,29 +2520,29 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="46"/>
-      <c r="AB13" s="46"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="46"/>
-      <c r="AE13" s="46"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="46"/>
-      <c r="AH13" s="46"/>
-      <c r="AI13" s="46"/>
+      <c r="AA13" s="105"/>
+      <c r="AB13" s="105"/>
+      <c r="AC13" s="105"/>
+      <c r="AD13" s="105"/>
+      <c r="AE13" s="105"/>
+      <c r="AF13" s="105"/>
+      <c r="AG13" s="105"/>
+      <c r="AH13" s="105"/>
+      <c r="AI13" s="105"/>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="11"/>
       <c r="AL13" s="11"/>
       <c r="AM13" s="11"/>
     </row>
     <row r="14" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
       <c r="H14" s="4" t="s">
         <v>2</v>
       </c>
@@ -2567,29 +2564,29 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="46"/>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="46"/>
-      <c r="AE14" s="46"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="46"/>
-      <c r="AH14" s="46"/>
-      <c r="AI14" s="46"/>
+      <c r="AA14" s="105"/>
+      <c r="AB14" s="105"/>
+      <c r="AC14" s="105"/>
+      <c r="AD14" s="105"/>
+      <c r="AE14" s="105"/>
+      <c r="AF14" s="105"/>
+      <c r="AG14" s="105"/>
+      <c r="AH14" s="105"/>
+      <c r="AI14" s="105"/>
       <c r="AJ14" s="10"/>
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
     </row>
     <row r="15" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
       <c r="H15" s="4" t="s">
         <v>2</v>
       </c>
@@ -2611,26 +2608,26 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
-      <c r="AA15" s="46"/>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="46"/>
-      <c r="AE15" s="46"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="46"/>
-      <c r="AI15" s="46"/>
+      <c r="AA15" s="105"/>
+      <c r="AB15" s="105"/>
+      <c r="AC15" s="105"/>
+      <c r="AD15" s="105"/>
+      <c r="AE15" s="105"/>
+      <c r="AF15" s="105"/>
+      <c r="AG15" s="105"/>
+      <c r="AH15" s="105"/>
+      <c r="AI15" s="105"/>
       <c r="AJ15" s="8"/>
     </row>
     <row r="16" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
       <c r="H16" s="4" t="s">
         <v>2</v>
       </c>
@@ -2652,26 +2649,26 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
-      <c r="AA16" s="46"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="46"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="46"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="46"/>
-      <c r="AH16" s="46"/>
-      <c r="AI16" s="46"/>
+      <c r="AA16" s="105"/>
+      <c r="AB16" s="105"/>
+      <c r="AC16" s="105"/>
+      <c r="AD16" s="105"/>
+      <c r="AE16" s="105"/>
+      <c r="AF16" s="105"/>
+      <c r="AG16" s="105"/>
+      <c r="AH16" s="105"/>
+      <c r="AI16" s="105"/>
       <c r="AJ16" s="8"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
       <c r="H17" s="4" t="s">
         <v>2</v>
       </c>
@@ -2693,53 +2690,53 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="46"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AH17" s="46"/>
-      <c r="AI17" s="46"/>
+      <c r="AA17" s="105"/>
+      <c r="AB17" s="105"/>
+      <c r="AC17" s="105"/>
+      <c r="AD17" s="105"/>
+      <c r="AE17" s="105"/>
+      <c r="AF17" s="105"/>
+      <c r="AG17" s="105"/>
+      <c r="AH17" s="105"/>
+      <c r="AI17" s="105"/>
       <c r="AJ17" s="8"/>
     </row>
     <row r="18" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="49"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="49"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="49"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="49"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="49"/>
-      <c r="AG18" s="49"/>
-      <c r="AH18" s="49"/>
-      <c r="AI18" s="49"/>
-      <c r="AJ18" s="50"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="69"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="69"/>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="70"/>
     </row>
     <row r="19" spans="2:36" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="2"/>
@@ -2757,14 +2754,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="15"/>
-      <c r="Q19" s="51" t="s">
+      <c r="Q19" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="52"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="52"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="72"/>
       <c r="W19" s="15"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2786,229 +2783,229 @@
     </row>
     <row r="21" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="17"/>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="D21" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="65" t="s">
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65" t="s">
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="66" t="s">
+      <c r="S21" s="83"/>
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="Y21" s="66"/>
-      <c r="Z21" s="66"/>
-      <c r="AA21" s="66"/>
-      <c r="AB21" s="66"/>
-      <c r="AC21" s="66"/>
-      <c r="AD21" s="56" t="s">
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="AE21" s="57"/>
-      <c r="AF21" s="57"/>
-      <c r="AG21" s="57"/>
-      <c r="AH21" s="57"/>
-      <c r="AI21" s="58"/>
+      <c r="AE21" s="75"/>
+      <c r="AF21" s="75"/>
+      <c r="AG21" s="75"/>
+      <c r="AH21" s="75"/>
+      <c r="AI21" s="76"/>
       <c r="AJ21" s="8"/>
     </row>
     <row r="22" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="60"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="60"/>
-      <c r="AI22" s="61"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="83"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="83"/>
+      <c r="Q22" s="83"/>
+      <c r="R22" s="83"/>
+      <c r="S22" s="83"/>
+      <c r="T22" s="83"/>
+      <c r="U22" s="83"/>
+      <c r="V22" s="83"/>
+      <c r="W22" s="83"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="77"/>
+      <c r="AE22" s="78"/>
+      <c r="AF22" s="78"/>
+      <c r="AG22" s="78"/>
+      <c r="AH22" s="78"/>
+      <c r="AI22" s="79"/>
       <c r="AJ22" s="8"/>
     </row>
     <row r="23" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="17"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="59"/>
-      <c r="AE23" s="60"/>
-      <c r="AF23" s="60"/>
-      <c r="AG23" s="60"/>
-      <c r="AH23" s="60"/>
-      <c r="AI23" s="61"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="82"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="83"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="83"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="83"/>
+      <c r="S23" s="83"/>
+      <c r="T23" s="83"/>
+      <c r="U23" s="83"/>
+      <c r="V23" s="83"/>
+      <c r="W23" s="83"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="77"/>
+      <c r="AE23" s="78"/>
+      <c r="AF23" s="78"/>
+      <c r="AG23" s="78"/>
+      <c r="AH23" s="78"/>
+      <c r="AI23" s="79"/>
       <c r="AJ23" s="8"/>
     </row>
     <row r="24" spans="2:36" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="67" t="s">
+      <c r="C24" s="31"/>
+      <c r="D24" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67" t="s">
+      <c r="E24" s="85"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="47" t="s">
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47" t="s">
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47" t="s">
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="47" t="s">
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="V24" s="47"/>
-      <c r="W24" s="47"/>
-      <c r="X24" s="47" t="s">
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
-      <c r="AA24" s="47" t="s">
+      <c r="Y24" s="67"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="AB24" s="47"/>
-      <c r="AC24" s="47"/>
-      <c r="AD24" s="59"/>
-      <c r="AE24" s="60"/>
-      <c r="AF24" s="60"/>
-      <c r="AG24" s="60"/>
-      <c r="AH24" s="60"/>
-      <c r="AI24" s="61"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="77"/>
+      <c r="AE24" s="78"/>
+      <c r="AF24" s="78"/>
+      <c r="AG24" s="78"/>
+      <c r="AH24" s="78"/>
+      <c r="AI24" s="79"/>
       <c r="AJ24" s="8"/>
     </row>
     <row r="25" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="77" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="77"/>
-      <c r="N25" s="77"/>
-      <c r="O25" s="55" t="s">
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55" t="s">
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55" t="s">
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55" t="s">
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="Y25" s="55"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="55" t="s">
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="AB25" s="55"/>
-      <c r="AC25" s="55"/>
-      <c r="AD25" s="70" t="s">
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="AE25" s="71"/>
-      <c r="AF25" s="71"/>
-      <c r="AG25" s="71"/>
-      <c r="AH25" s="71"/>
-      <c r="AI25" s="72"/>
+      <c r="AE25" s="35"/>
+      <c r="AF25" s="35"/>
+      <c r="AG25" s="35"/>
+      <c r="AH25" s="35"/>
+      <c r="AI25" s="36"/>
       <c r="AJ25" s="8"/>
     </row>
     <row r="26" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3016,38 +3013,38 @@
       <c r="C26" s="18">
         <v>1</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="73"/>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="73"/>
-      <c r="S26" s="73"/>
-      <c r="T26" s="73"/>
-      <c r="U26" s="73"/>
-      <c r="V26" s="73"/>
-      <c r="W26" s="73"/>
-      <c r="X26" s="73"/>
-      <c r="Y26" s="73"/>
-      <c r="Z26" s="73"/>
-      <c r="AA26" s="73"/>
-      <c r="AB26" s="73"/>
-      <c r="AC26" s="73"/>
-      <c r="AD26" s="74"/>
-      <c r="AE26" s="75"/>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="75"/>
-      <c r="AH26" s="75"/>
-      <c r="AI26" s="76"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="61"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="61"/>
+      <c r="AC26" s="61"/>
+      <c r="AD26" s="62"/>
+      <c r="AE26" s="63"/>
+      <c r="AF26" s="63"/>
+      <c r="AG26" s="63"/>
+      <c r="AH26" s="63"/>
+      <c r="AI26" s="64"/>
       <c r="AJ26" s="8"/>
     </row>
     <row r="27" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3055,38 +3052,38 @@
       <c r="C27" s="18">
         <v>2</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
-      <c r="K27" s="73"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="73"/>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="73"/>
-      <c r="R27" s="73"/>
-      <c r="S27" s="73"/>
-      <c r="T27" s="73"/>
-      <c r="U27" s="73"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="73"/>
-      <c r="X27" s="73"/>
-      <c r="Y27" s="73"/>
-      <c r="Z27" s="73"/>
-      <c r="AA27" s="73"/>
-      <c r="AB27" s="73"/>
-      <c r="AC27" s="73"/>
-      <c r="AD27" s="74"/>
-      <c r="AE27" s="75"/>
-      <c r="AF27" s="75"/>
-      <c r="AG27" s="75"/>
-      <c r="AH27" s="75"/>
-      <c r="AI27" s="76"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="61"/>
+      <c r="S27" s="61"/>
+      <c r="T27" s="61"/>
+      <c r="U27" s="61"/>
+      <c r="V27" s="61"/>
+      <c r="W27" s="61"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="61"/>
+      <c r="Z27" s="61"/>
+      <c r="AA27" s="61"/>
+      <c r="AB27" s="61"/>
+      <c r="AC27" s="61"/>
+      <c r="AD27" s="62"/>
+      <c r="AE27" s="63"/>
+      <c r="AF27" s="63"/>
+      <c r="AG27" s="63"/>
+      <c r="AH27" s="63"/>
+      <c r="AI27" s="64"/>
       <c r="AJ27" s="8"/>
     </row>
     <row r="28" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3094,38 +3091,38 @@
       <c r="C28" s="18">
         <v>3</v>
       </c>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="73"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="73"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="73"/>
-      <c r="U28" s="73"/>
-      <c r="V28" s="73"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="73"/>
-      <c r="Y28" s="73"/>
-      <c r="Z28" s="73"/>
-      <c r="AA28" s="73"/>
-      <c r="AB28" s="73"/>
-      <c r="AC28" s="73"/>
-      <c r="AD28" s="74"/>
-      <c r="AE28" s="75"/>
-      <c r="AF28" s="75"/>
-      <c r="AG28" s="75"/>
-      <c r="AH28" s="75"/>
-      <c r="AI28" s="76"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="61"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="61"/>
+      <c r="P28" s="61"/>
+      <c r="Q28" s="61"/>
+      <c r="R28" s="61"/>
+      <c r="S28" s="61"/>
+      <c r="T28" s="61"/>
+      <c r="U28" s="61"/>
+      <c r="V28" s="61"/>
+      <c r="W28" s="61"/>
+      <c r="X28" s="61"/>
+      <c r="Y28" s="61"/>
+      <c r="Z28" s="61"/>
+      <c r="AA28" s="61"/>
+      <c r="AB28" s="61"/>
+      <c r="AC28" s="61"/>
+      <c r="AD28" s="62"/>
+      <c r="AE28" s="63"/>
+      <c r="AF28" s="63"/>
+      <c r="AG28" s="63"/>
+      <c r="AH28" s="63"/>
+      <c r="AI28" s="64"/>
       <c r="AJ28" s="19"/>
     </row>
     <row r="29" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3133,38 +3130,38 @@
       <c r="C29" s="18">
         <v>4</v>
       </c>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="73"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="73"/>
-      <c r="T29" s="73"/>
-      <c r="U29" s="73"/>
-      <c r="V29" s="73"/>
-      <c r="W29" s="73"/>
-      <c r="X29" s="73"/>
-      <c r="Y29" s="73"/>
-      <c r="Z29" s="73"/>
-      <c r="AA29" s="73"/>
-      <c r="AB29" s="73"/>
-      <c r="AC29" s="73"/>
-      <c r="AD29" s="74"/>
-      <c r="AE29" s="75"/>
-      <c r="AF29" s="75"/>
-      <c r="AG29" s="75"/>
-      <c r="AH29" s="75"/>
-      <c r="AI29" s="76"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="61"/>
+      <c r="P29" s="61"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="61"/>
+      <c r="U29" s="61"/>
+      <c r="V29" s="61"/>
+      <c r="W29" s="61"/>
+      <c r="X29" s="61"/>
+      <c r="Y29" s="61"/>
+      <c r="Z29" s="61"/>
+      <c r="AA29" s="61"/>
+      <c r="AB29" s="61"/>
+      <c r="AC29" s="61"/>
+      <c r="AD29" s="62"/>
+      <c r="AE29" s="63"/>
+      <c r="AF29" s="63"/>
+      <c r="AG29" s="63"/>
+      <c r="AH29" s="63"/>
+      <c r="AI29" s="64"/>
       <c r="AJ29" s="19"/>
     </row>
     <row r="30" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3172,38 +3169,38 @@
       <c r="C30" s="18">
         <v>5</v>
       </c>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="73"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="73"/>
-      <c r="X30" s="73"/>
-      <c r="Y30" s="73"/>
-      <c r="Z30" s="73"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="74"/>
-      <c r="AE30" s="75"/>
-      <c r="AF30" s="75"/>
-      <c r="AG30" s="75"/>
-      <c r="AH30" s="75"/>
-      <c r="AI30" s="76"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="61"/>
+      <c r="O30" s="61"/>
+      <c r="P30" s="61"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="61"/>
+      <c r="U30" s="61"/>
+      <c r="V30" s="61"/>
+      <c r="W30" s="61"/>
+      <c r="X30" s="61"/>
+      <c r="Y30" s="61"/>
+      <c r="Z30" s="61"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="62"/>
+      <c r="AE30" s="63"/>
+      <c r="AF30" s="63"/>
+      <c r="AG30" s="63"/>
+      <c r="AH30" s="63"/>
+      <c r="AI30" s="64"/>
       <c r="AJ30" s="19"/>
     </row>
     <row r="31" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3211,38 +3208,38 @@
       <c r="C31" s="18">
         <v>6</v>
       </c>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="73"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="73"/>
-      <c r="X31" s="73"/>
-      <c r="Y31" s="73"/>
-      <c r="Z31" s="73"/>
-      <c r="AA31" s="73"/>
-      <c r="AB31" s="73"/>
-      <c r="AC31" s="73"/>
-      <c r="AD31" s="74"/>
-      <c r="AE31" s="75"/>
-      <c r="AF31" s="75"/>
-      <c r="AG31" s="75"/>
-      <c r="AH31" s="75"/>
-      <c r="AI31" s="76"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="61"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="61"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
+      <c r="U31" s="61"/>
+      <c r="V31" s="61"/>
+      <c r="W31" s="61"/>
+      <c r="X31" s="61"/>
+      <c r="Y31" s="61"/>
+      <c r="Z31" s="61"/>
+      <c r="AA31" s="61"/>
+      <c r="AB31" s="61"/>
+      <c r="AC31" s="61"/>
+      <c r="AD31" s="62"/>
+      <c r="AE31" s="63"/>
+      <c r="AF31" s="63"/>
+      <c r="AG31" s="63"/>
+      <c r="AH31" s="63"/>
+      <c r="AI31" s="64"/>
       <c r="AJ31" s="19"/>
     </row>
     <row r="32" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3250,38 +3247,38 @@
       <c r="C32" s="18">
         <v>7</v>
       </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="U32" s="73"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="73"/>
-      <c r="X32" s="73"/>
-      <c r="Y32" s="73"/>
-      <c r="Z32" s="73"/>
-      <c r="AA32" s="73"/>
-      <c r="AB32" s="73"/>
-      <c r="AC32" s="73"/>
-      <c r="AD32" s="74"/>
-      <c r="AE32" s="75"/>
-      <c r="AF32" s="75"/>
-      <c r="AG32" s="75"/>
-      <c r="AH32" s="75"/>
-      <c r="AI32" s="76"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="61"/>
+      <c r="U32" s="61"/>
+      <c r="V32" s="61"/>
+      <c r="W32" s="61"/>
+      <c r="X32" s="61"/>
+      <c r="Y32" s="61"/>
+      <c r="Z32" s="61"/>
+      <c r="AA32" s="61"/>
+      <c r="AB32" s="61"/>
+      <c r="AC32" s="61"/>
+      <c r="AD32" s="62"/>
+      <c r="AE32" s="63"/>
+      <c r="AF32" s="63"/>
+      <c r="AG32" s="63"/>
+      <c r="AH32" s="63"/>
+      <c r="AI32" s="64"/>
       <c r="AJ32" s="8"/>
     </row>
     <row r="33" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3289,38 +3286,38 @@
       <c r="C33" s="18">
         <v>8</v>
       </c>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="66"/>
-      <c r="M33" s="66"/>
-      <c r="N33" s="66"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="73"/>
-      <c r="S33" s="73"/>
-      <c r="T33" s="73"/>
-      <c r="U33" s="73"/>
-      <c r="V33" s="73"/>
-      <c r="W33" s="73"/>
-      <c r="X33" s="73"/>
-      <c r="Y33" s="73"/>
-      <c r="Z33" s="73"/>
-      <c r="AA33" s="73"/>
-      <c r="AB33" s="73"/>
-      <c r="AC33" s="73"/>
-      <c r="AD33" s="74"/>
-      <c r="AE33" s="75"/>
-      <c r="AF33" s="75"/>
-      <c r="AG33" s="75"/>
-      <c r="AH33" s="75"/>
-      <c r="AI33" s="76"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="65"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="65"/>
+      <c r="P33" s="65"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="61"/>
+      <c r="X33" s="61"/>
+      <c r="Y33" s="61"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="61"/>
+      <c r="AB33" s="61"/>
+      <c r="AC33" s="61"/>
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="63"/>
+      <c r="AF33" s="63"/>
+      <c r="AG33" s="63"/>
+      <c r="AH33" s="63"/>
+      <c r="AI33" s="64"/>
       <c r="AJ33" s="8"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3328,38 +3325,38 @@
       <c r="C34" s="18">
         <v>9</v>
       </c>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="66"/>
-      <c r="M34" s="66"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="66"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="73"/>
-      <c r="W34" s="73"/>
-      <c r="X34" s="73"/>
-      <c r="Y34" s="73"/>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="73"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="73"/>
-      <c r="AD34" s="74"/>
-      <c r="AE34" s="75"/>
-      <c r="AF34" s="75"/>
-      <c r="AG34" s="75"/>
-      <c r="AH34" s="75"/>
-      <c r="AI34" s="76"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="65"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="65"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="61"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="61"/>
+      <c r="U34" s="61"/>
+      <c r="V34" s="61"/>
+      <c r="W34" s="61"/>
+      <c r="X34" s="61"/>
+      <c r="Y34" s="61"/>
+      <c r="Z34" s="61"/>
+      <c r="AA34" s="61"/>
+      <c r="AB34" s="61"/>
+      <c r="AC34" s="61"/>
+      <c r="AD34" s="62"/>
+      <c r="AE34" s="63"/>
+      <c r="AF34" s="63"/>
+      <c r="AG34" s="63"/>
+      <c r="AH34" s="63"/>
+      <c r="AI34" s="64"/>
       <c r="AJ34" s="8"/>
     </row>
     <row r="35" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3367,38 +3364,38 @@
       <c r="C35" s="18">
         <v>10</v>
       </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="66"/>
-      <c r="N35" s="66"/>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="73"/>
-      <c r="S35" s="73"/>
-      <c r="T35" s="73"/>
-      <c r="U35" s="73"/>
-      <c r="V35" s="73"/>
-      <c r="W35" s="73"/>
-      <c r="X35" s="73"/>
-      <c r="Y35" s="73"/>
-      <c r="Z35" s="73"/>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="73"/>
-      <c r="AC35" s="73"/>
-      <c r="AD35" s="74"/>
-      <c r="AE35" s="75"/>
-      <c r="AF35" s="75"/>
-      <c r="AG35" s="75"/>
-      <c r="AH35" s="75"/>
-      <c r="AI35" s="76"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="65"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="65"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="61"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="61"/>
+      <c r="V35" s="61"/>
+      <c r="W35" s="61"/>
+      <c r="X35" s="61"/>
+      <c r="Y35" s="61"/>
+      <c r="Z35" s="61"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="62"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="63"/>
+      <c r="AG35" s="63"/>
+      <c r="AH35" s="63"/>
+      <c r="AI35" s="64"/>
       <c r="AJ35" s="8"/>
     </row>
     <row r="36" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3406,38 +3403,38 @@
       <c r="C36" s="18">
         <v>11</v>
       </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="73"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="73"/>
-      <c r="U36" s="73"/>
-      <c r="V36" s="73"/>
-      <c r="W36" s="73"/>
-      <c r="X36" s="73"/>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="73"/>
-      <c r="AD36" s="74"/>
-      <c r="AE36" s="75"/>
-      <c r="AF36" s="75"/>
-      <c r="AG36" s="75"/>
-      <c r="AH36" s="75"/>
-      <c r="AI36" s="76"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="61"/>
+      <c r="S36" s="61"/>
+      <c r="T36" s="61"/>
+      <c r="U36" s="61"/>
+      <c r="V36" s="61"/>
+      <c r="W36" s="61"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="62"/>
+      <c r="AE36" s="63"/>
+      <c r="AF36" s="63"/>
+      <c r="AG36" s="63"/>
+      <c r="AH36" s="63"/>
+      <c r="AI36" s="64"/>
       <c r="AJ36" s="8"/>
     </row>
     <row r="37" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3445,38 +3442,38 @@
       <c r="C37" s="18">
         <v>12</v>
       </c>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80"/>
-      <c r="M37" s="80"/>
-      <c r="N37" s="80"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="80"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="80"/>
-      <c r="U37" s="80"/>
-      <c r="V37" s="80"/>
-      <c r="W37" s="80"/>
-      <c r="X37" s="80"/>
-      <c r="Y37" s="80"/>
-      <c r="Z37" s="80"/>
-      <c r="AA37" s="80"/>
-      <c r="AB37" s="80"/>
-      <c r="AC37" s="80"/>
-      <c r="AD37" s="81"/>
-      <c r="AE37" s="82"/>
-      <c r="AF37" s="82"/>
-      <c r="AG37" s="82"/>
-      <c r="AH37" s="82"/>
-      <c r="AI37" s="83"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="51"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="51"/>
+      <c r="S37" s="51"/>
+      <c r="T37" s="51"/>
+      <c r="U37" s="51"/>
+      <c r="V37" s="51"/>
+      <c r="W37" s="51"/>
+      <c r="X37" s="51"/>
+      <c r="Y37" s="51"/>
+      <c r="Z37" s="51"/>
+      <c r="AA37" s="51"/>
+      <c r="AB37" s="51"/>
+      <c r="AC37" s="51"/>
+      <c r="AD37" s="52"/>
+      <c r="AE37" s="53"/>
+      <c r="AF37" s="53"/>
+      <c r="AG37" s="53"/>
+      <c r="AH37" s="53"/>
+      <c r="AI37" s="54"/>
       <c r="AJ37" s="8"/>
     </row>
     <row r="38" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3484,38 +3481,38 @@
       <c r="C38" s="18">
         <v>13</v>
       </c>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
-      <c r="M38" s="80"/>
-      <c r="N38" s="80"/>
-      <c r="O38" s="80"/>
-      <c r="P38" s="80"/>
-      <c r="Q38" s="80"/>
-      <c r="R38" s="80"/>
-      <c r="S38" s="80"/>
-      <c r="T38" s="80"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="80"/>
-      <c r="W38" s="80"/>
-      <c r="X38" s="80"/>
-      <c r="Y38" s="80"/>
-      <c r="Z38" s="80"/>
-      <c r="AA38" s="80"/>
-      <c r="AB38" s="80"/>
-      <c r="AC38" s="80"/>
-      <c r="AD38" s="81"/>
-      <c r="AE38" s="82"/>
-      <c r="AF38" s="82"/>
-      <c r="AG38" s="82"/>
-      <c r="AH38" s="82"/>
-      <c r="AI38" s="83"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="51"/>
+      <c r="Q38" s="51"/>
+      <c r="R38" s="51"/>
+      <c r="S38" s="51"/>
+      <c r="T38" s="51"/>
+      <c r="U38" s="51"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="51"/>
+      <c r="Y38" s="51"/>
+      <c r="Z38" s="51"/>
+      <c r="AA38" s="51"/>
+      <c r="AB38" s="51"/>
+      <c r="AC38" s="51"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="53"/>
+      <c r="AF38" s="53"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="53"/>
+      <c r="AI38" s="54"/>
       <c r="AJ38" s="8"/>
     </row>
     <row r="39" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3523,38 +3520,38 @@
       <c r="C39" s="18">
         <v>14</v>
       </c>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="80"/>
-      <c r="M39" s="80"/>
-      <c r="N39" s="80"/>
-      <c r="O39" s="80"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="80"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="80"/>
-      <c r="U39" s="80"/>
-      <c r="V39" s="80"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="80"/>
-      <c r="Y39" s="80"/>
-      <c r="Z39" s="80"/>
-      <c r="AA39" s="80"/>
-      <c r="AB39" s="80"/>
-      <c r="AC39" s="80"/>
-      <c r="AD39" s="81"/>
-      <c r="AE39" s="82"/>
-      <c r="AF39" s="82"/>
-      <c r="AG39" s="82"/>
-      <c r="AH39" s="82"/>
-      <c r="AI39" s="83"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="51"/>
+      <c r="L39" s="51"/>
+      <c r="M39" s="51"/>
+      <c r="N39" s="51"/>
+      <c r="O39" s="51"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="51"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="51"/>
+      <c r="U39" s="51"/>
+      <c r="V39" s="51"/>
+      <c r="W39" s="51"/>
+      <c r="X39" s="51"/>
+      <c r="Y39" s="51"/>
+      <c r="Z39" s="51"/>
+      <c r="AA39" s="51"/>
+      <c r="AB39" s="51"/>
+      <c r="AC39" s="51"/>
+      <c r="AD39" s="52"/>
+      <c r="AE39" s="53"/>
+      <c r="AF39" s="53"/>
+      <c r="AG39" s="53"/>
+      <c r="AH39" s="53"/>
+      <c r="AI39" s="54"/>
       <c r="AJ39" s="8"/>
     </row>
     <row r="40" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3562,373 +3559,373 @@
       <c r="C40" s="18">
         <v>15</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80"/>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="80"/>
-      <c r="U40" s="80"/>
-      <c r="V40" s="80"/>
-      <c r="W40" s="80"/>
-      <c r="X40" s="80"/>
-      <c r="Y40" s="80"/>
-      <c r="Z40" s="80"/>
-      <c r="AA40" s="80"/>
-      <c r="AB40" s="80"/>
-      <c r="AC40" s="80"/>
-      <c r="AD40" s="81"/>
-      <c r="AE40" s="82"/>
-      <c r="AF40" s="82"/>
-      <c r="AG40" s="82"/>
-      <c r="AH40" s="82"/>
-      <c r="AI40" s="83"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+      <c r="L40" s="51"/>
+      <c r="M40" s="51"/>
+      <c r="N40" s="51"/>
+      <c r="O40" s="51"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="51"/>
+      <c r="S40" s="51"/>
+      <c r="T40" s="51"/>
+      <c r="U40" s="51"/>
+      <c r="V40" s="51"/>
+      <c r="W40" s="51"/>
+      <c r="X40" s="51"/>
+      <c r="Y40" s="51"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="51"/>
+      <c r="AB40" s="51"/>
+      <c r="AC40" s="51"/>
+      <c r="AD40" s="52"/>
+      <c r="AE40" s="53"/>
+      <c r="AF40" s="53"/>
+      <c r="AG40" s="53"/>
+      <c r="AH40" s="53"/>
+      <c r="AI40" s="54"/>
       <c r="AJ40" s="8"/>
     </row>
     <row r="41" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="17"/>
-      <c r="C41" s="84" t="s">
+      <c r="C41" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
-      <c r="N41" s="84"/>
-      <c r="O41" s="84"/>
-      <c r="P41" s="84"/>
-      <c r="Q41" s="84"/>
-      <c r="R41" s="84"/>
-      <c r="S41" s="84"/>
-      <c r="T41" s="84"/>
-      <c r="U41" s="84"/>
-      <c r="V41" s="84"/>
-      <c r="W41" s="84"/>
-      <c r="X41" s="84"/>
-      <c r="Y41" s="84"/>
-      <c r="Z41" s="84"/>
-      <c r="AA41" s="84"/>
-      <c r="AB41" s="84"/>
-      <c r="AC41" s="84"/>
-      <c r="AD41" s="84"/>
-      <c r="AE41" s="84"/>
-      <c r="AF41" s="84"/>
-      <c r="AG41" s="84"/>
-      <c r="AH41" s="84"/>
-      <c r="AI41" s="84"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="55"/>
+      <c r="V41" s="55"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="55"/>
+      <c r="Y41" s="55"/>
+      <c r="Z41" s="55"/>
+      <c r="AA41" s="55"/>
+      <c r="AB41" s="55"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="55"/>
+      <c r="AE41" s="55"/>
+      <c r="AF41" s="55"/>
+      <c r="AG41" s="55"/>
+      <c r="AH41" s="55"/>
+      <c r="AI41" s="55"/>
       <c r="AJ41" s="8"/>
     </row>
     <row r="42" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="17"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-      <c r="R42" s="84"/>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
-      <c r="V42" s="84"/>
-      <c r="W42" s="84"/>
-      <c r="X42" s="84"/>
-      <c r="Y42" s="84"/>
-      <c r="Z42" s="84"/>
-      <c r="AA42" s="84"/>
-      <c r="AB42" s="84"/>
-      <c r="AC42" s="84"/>
-      <c r="AD42" s="84"/>
-      <c r="AE42" s="84"/>
-      <c r="AF42" s="84"/>
-      <c r="AG42" s="84"/>
-      <c r="AH42" s="84"/>
-      <c r="AI42" s="84"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="55"/>
+      <c r="Q42" s="55"/>
+      <c r="R42" s="55"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="55"/>
+      <c r="U42" s="55"/>
+      <c r="V42" s="55"/>
+      <c r="W42" s="55"/>
+      <c r="X42" s="55"/>
+      <c r="Y42" s="55"/>
+      <c r="Z42" s="55"/>
+      <c r="AA42" s="55"/>
+      <c r="AB42" s="55"/>
+      <c r="AC42" s="55"/>
+      <c r="AD42" s="55"/>
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="55"/>
+      <c r="AG42" s="55"/>
+      <c r="AH42" s="55"/>
+      <c r="AI42" s="55"/>
       <c r="AJ42" s="8"/>
     </row>
     <row r="43" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="17"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="84"/>
-      <c r="P43" s="84"/>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="84"/>
-      <c r="S43" s="84"/>
-      <c r="T43" s="84"/>
-      <c r="U43" s="84"/>
-      <c r="V43" s="84"/>
-      <c r="W43" s="84"/>
-      <c r="X43" s="84"/>
-      <c r="Y43" s="84"/>
-      <c r="Z43" s="84"/>
-      <c r="AA43" s="84"/>
-      <c r="AB43" s="84"/>
-      <c r="AC43" s="84"/>
-      <c r="AD43" s="84"/>
-      <c r="AE43" s="84"/>
-      <c r="AF43" s="84"/>
-      <c r="AG43" s="84"/>
-      <c r="AH43" s="84"/>
-      <c r="AI43" s="84"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="55"/>
+      <c r="Q43" s="55"/>
+      <c r="R43" s="55"/>
+      <c r="S43" s="55"/>
+      <c r="T43" s="55"/>
+      <c r="U43" s="55"/>
+      <c r="V43" s="55"/>
+      <c r="W43" s="55"/>
+      <c r="X43" s="55"/>
+      <c r="Y43" s="55"/>
+      <c r="Z43" s="55"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="55"/>
+      <c r="AC43" s="55"/>
+      <c r="AD43" s="55"/>
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="55"/>
+      <c r="AG43" s="55"/>
+      <c r="AH43" s="55"/>
+      <c r="AI43" s="55"/>
       <c r="AJ43" s="8"/>
     </row>
     <row r="44" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="17"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="84"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="84"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="84"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="84"/>
-      <c r="R44" s="84"/>
-      <c r="S44" s="84"/>
-      <c r="T44" s="84"/>
-      <c r="U44" s="84"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="84"/>
-      <c r="X44" s="84"/>
-      <c r="Y44" s="84"/>
-      <c r="Z44" s="84"/>
-      <c r="AA44" s="84"/>
-      <c r="AB44" s="84"/>
-      <c r="AC44" s="84"/>
-      <c r="AD44" s="84"/>
-      <c r="AE44" s="84"/>
-      <c r="AF44" s="84"/>
-      <c r="AG44" s="84"/>
-      <c r="AH44" s="84"/>
-      <c r="AI44" s="84"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="55"/>
+      <c r="Q44" s="55"/>
+      <c r="R44" s="55"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="55"/>
+      <c r="U44" s="55"/>
+      <c r="V44" s="55"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="55"/>
+      <c r="Y44" s="55"/>
+      <c r="Z44" s="55"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="55"/>
+      <c r="AC44" s="55"/>
+      <c r="AD44" s="55"/>
+      <c r="AE44" s="55"/>
+      <c r="AF44" s="55"/>
+      <c r="AG44" s="55"/>
+      <c r="AH44" s="55"/>
+      <c r="AI44" s="55"/>
       <c r="AJ44" s="8"/>
     </row>
     <row r="45" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="17"/>
-      <c r="C45" s="84"/>
-      <c r="D45" s="84"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="84"/>
-      <c r="L45" s="84"/>
-      <c r="M45" s="84"/>
-      <c r="N45" s="84"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="84"/>
-      <c r="Q45" s="84"/>
-      <c r="R45" s="84"/>
-      <c r="S45" s="84"/>
-      <c r="T45" s="84"/>
-      <c r="U45" s="84"/>
-      <c r="V45" s="84"/>
-      <c r="W45" s="84"/>
-      <c r="X45" s="84"/>
-      <c r="Y45" s="84"/>
-      <c r="Z45" s="84"/>
-      <c r="AA45" s="84"/>
-      <c r="AB45" s="84"/>
-      <c r="AC45" s="84"/>
-      <c r="AD45" s="84"/>
-      <c r="AE45" s="84"/>
-      <c r="AF45" s="84"/>
-      <c r="AG45" s="84"/>
-      <c r="AH45" s="84"/>
-      <c r="AI45" s="84"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="55"/>
+      <c r="U45" s="55"/>
+      <c r="V45" s="55"/>
+      <c r="W45" s="55"/>
+      <c r="X45" s="55"/>
+      <c r="Y45" s="55"/>
+      <c r="Z45" s="55"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="55"/>
+      <c r="AC45" s="55"/>
+      <c r="AD45" s="55"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="55"/>
+      <c r="AH45" s="55"/>
+      <c r="AI45" s="55"/>
       <c r="AJ45" s="8"/>
     </row>
     <row r="46" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="17"/>
-      <c r="C46" s="84"/>
-      <c r="D46" s="84"/>
-      <c r="E46" s="84"/>
-      <c r="F46" s="84"/>
-      <c r="G46" s="84"/>
-      <c r="H46" s="84"/>
-      <c r="I46" s="84"/>
-      <c r="J46" s="84"/>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84"/>
-      <c r="M46" s="84"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="84"/>
-      <c r="P46" s="84"/>
-      <c r="Q46" s="84"/>
-      <c r="R46" s="84"/>
-      <c r="S46" s="84"/>
-      <c r="T46" s="84"/>
-      <c r="U46" s="84"/>
-      <c r="V46" s="84"/>
-      <c r="W46" s="84"/>
-      <c r="X46" s="84"/>
-      <c r="Y46" s="84"/>
-      <c r="Z46" s="84"/>
-      <c r="AA46" s="84"/>
-      <c r="AB46" s="84"/>
-      <c r="AC46" s="84"/>
-      <c r="AD46" s="84"/>
-      <c r="AE46" s="84"/>
-      <c r="AF46" s="84"/>
-      <c r="AG46" s="84"/>
-      <c r="AH46" s="84"/>
-      <c r="AI46" s="84"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="55"/>
+      <c r="Q46" s="55"/>
+      <c r="R46" s="55"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="55"/>
+      <c r="U46" s="55"/>
+      <c r="V46" s="55"/>
+      <c r="W46" s="55"/>
+      <c r="X46" s="55"/>
+      <c r="Y46" s="55"/>
+      <c r="Z46" s="55"/>
+      <c r="AA46" s="55"/>
+      <c r="AB46" s="55"/>
+      <c r="AC46" s="55"/>
+      <c r="AD46" s="55"/>
+      <c r="AE46" s="55"/>
+      <c r="AF46" s="55"/>
+      <c r="AG46" s="55"/>
+      <c r="AH46" s="55"/>
+      <c r="AI46" s="55"/>
       <c r="AJ46" s="8"/>
     </row>
     <row r="47" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="17"/>
-      <c r="C47" s="84"/>
-      <c r="D47" s="84"/>
-      <c r="E47" s="84"/>
-      <c r="F47" s="84"/>
-      <c r="G47" s="84"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="84"/>
-      <c r="J47" s="84"/>
-      <c r="K47" s="84"/>
-      <c r="L47" s="84"/>
-      <c r="M47" s="84"/>
-      <c r="N47" s="84"/>
-      <c r="O47" s="84"/>
-      <c r="P47" s="84"/>
-      <c r="Q47" s="84"/>
-      <c r="R47" s="84"/>
-      <c r="S47" s="84"/>
-      <c r="T47" s="84"/>
-      <c r="U47" s="84"/>
-      <c r="V47" s="84"/>
-      <c r="W47" s="84"/>
-      <c r="X47" s="84"/>
-      <c r="Y47" s="84"/>
-      <c r="Z47" s="84"/>
-      <c r="AA47" s="84"/>
-      <c r="AB47" s="84"/>
-      <c r="AC47" s="84"/>
-      <c r="AD47" s="84"/>
-      <c r="AE47" s="84"/>
-      <c r="AF47" s="84"/>
-      <c r="AG47" s="84"/>
-      <c r="AH47" s="84"/>
-      <c r="AI47" s="84"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="55"/>
+      <c r="N47" s="55"/>
+      <c r="O47" s="55"/>
+      <c r="P47" s="55"/>
+      <c r="Q47" s="55"/>
+      <c r="R47" s="55"/>
+      <c r="S47" s="55"/>
+      <c r="T47" s="55"/>
+      <c r="U47" s="55"/>
+      <c r="V47" s="55"/>
+      <c r="W47" s="55"/>
+      <c r="X47" s="55"/>
+      <c r="Y47" s="55"/>
+      <c r="Z47" s="55"/>
+      <c r="AA47" s="55"/>
+      <c r="AB47" s="55"/>
+      <c r="AC47" s="55"/>
+      <c r="AD47" s="55"/>
+      <c r="AE47" s="55"/>
+      <c r="AF47" s="55"/>
+      <c r="AG47" s="55"/>
+      <c r="AH47" s="55"/>
+      <c r="AI47" s="55"/>
       <c r="AJ47" s="8"/>
     </row>
     <row r="48" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="17"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84"/>
-      <c r="M48" s="84"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
-      <c r="P48" s="84"/>
-      <c r="Q48" s="84"/>
-      <c r="R48" s="84"/>
-      <c r="S48" s="84"/>
-      <c r="T48" s="84"/>
-      <c r="U48" s="84"/>
-      <c r="V48" s="84"/>
-      <c r="W48" s="84"/>
-      <c r="X48" s="84"/>
-      <c r="Y48" s="84"/>
-      <c r="Z48" s="84"/>
-      <c r="AA48" s="84"/>
-      <c r="AB48" s="84"/>
-      <c r="AC48" s="84"/>
-      <c r="AD48" s="84"/>
-      <c r="AE48" s="84"/>
-      <c r="AF48" s="84"/>
-      <c r="AG48" s="84"/>
-      <c r="AH48" s="84"/>
-      <c r="AI48" s="84"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="55"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
+      <c r="U48" s="55"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="55"/>
+      <c r="Z48" s="55"/>
+      <c r="AA48" s="55"/>
+      <c r="AB48" s="55"/>
+      <c r="AC48" s="55"/>
+      <c r="AD48" s="55"/>
+      <c r="AE48" s="55"/>
+      <c r="AF48" s="55"/>
+      <c r="AG48" s="55"/>
+      <c r="AH48" s="55"/>
+      <c r="AI48" s="55"/>
       <c r="AJ48" s="8"/>
     </row>
     <row r="49" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="17"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="84"/>
-      <c r="E49" s="84"/>
-      <c r="F49" s="84"/>
-      <c r="G49" s="84"/>
-      <c r="H49" s="84"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="84"/>
-      <c r="K49" s="84"/>
-      <c r="L49" s="84"/>
-      <c r="M49" s="84"/>
-      <c r="N49" s="84"/>
-      <c r="O49" s="84"/>
-      <c r="P49" s="84"/>
-      <c r="Q49" s="84"/>
-      <c r="R49" s="84"/>
-      <c r="S49" s="84"/>
-      <c r="T49" s="84"/>
-      <c r="U49" s="84"/>
-      <c r="V49" s="84"/>
-      <c r="W49" s="84"/>
-      <c r="X49" s="84"/>
-      <c r="Y49" s="84"/>
-      <c r="Z49" s="84"/>
-      <c r="AA49" s="84"/>
-      <c r="AB49" s="84"/>
-      <c r="AC49" s="84"/>
-      <c r="AD49" s="84"/>
-      <c r="AE49" s="84"/>
-      <c r="AF49" s="84"/>
-      <c r="AG49" s="84"/>
-      <c r="AH49" s="84"/>
-      <c r="AI49" s="84"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="55"/>
+      <c r="P49" s="55"/>
+      <c r="Q49" s="55"/>
+      <c r="R49" s="55"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="55"/>
+      <c r="U49" s="55"/>
+      <c r="V49" s="55"/>
+      <c r="W49" s="55"/>
+      <c r="X49" s="55"/>
+      <c r="Y49" s="55"/>
+      <c r="Z49" s="55"/>
+      <c r="AA49" s="55"/>
+      <c r="AB49" s="55"/>
+      <c r="AC49" s="55"/>
+      <c r="AD49" s="55"/>
+      <c r="AE49" s="55"/>
+      <c r="AF49" s="55"/>
+      <c r="AG49" s="55"/>
+      <c r="AH49" s="55"/>
+      <c r="AI49" s="55"/>
       <c r="AJ49" s="8"/>
     </row>
     <row r="50" spans="2:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3968,13 +3965,13 @@
     </row>
     <row r="51" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B51" s="17"/>
-      <c r="C51" s="85" t="s">
+      <c r="C51" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="85"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
       <c r="AJ51" s="8"/>
     </row>
     <row r="52" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
@@ -4039,347 +4036,345 @@
     </row>
     <row r="60" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="17"/>
-      <c r="H60" s="86" t="s">
+      <c r="H60" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="I60" s="87"/>
-      <c r="J60" s="87"/>
-      <c r="K60" s="87"/>
-      <c r="L60" s="87"/>
-      <c r="M60" s="87"/>
-      <c r="N60" s="87"/>
-      <c r="O60" s="87"/>
-      <c r="P60" s="87"/>
-      <c r="Q60" s="87"/>
-      <c r="R60" s="87"/>
-      <c r="S60" s="87"/>
-      <c r="T60" s="87"/>
-      <c r="U60" s="87"/>
-      <c r="V60" s="87"/>
-      <c r="W60" s="87"/>
-      <c r="X60" s="87"/>
-      <c r="Y60" s="87"/>
-      <c r="Z60" s="87"/>
-      <c r="AA60" s="87"/>
-      <c r="AB60" s="87"/>
-      <c r="AC60" s="87"/>
-      <c r="AD60" s="87"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="58"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="58"/>
+      <c r="Y60" s="58"/>
+      <c r="Z60" s="58"/>
+      <c r="AA60" s="58"/>
+      <c r="AB60" s="58"/>
+      <c r="AC60" s="58"/>
+      <c r="AD60" s="58"/>
       <c r="AJ60" s="8"/>
     </row>
     <row r="61" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B61" s="17"/>
-      <c r="H61" s="88" t="s">
+      <c r="H61" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="I61" s="88"/>
-      <c r="J61" s="88"/>
-      <c r="K61" s="88"/>
-      <c r="L61" s="88"/>
-      <c r="M61" s="88"/>
-      <c r="N61" s="88"/>
-      <c r="O61" s="88"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="88"/>
-      <c r="R61" s="88"/>
-      <c r="S61" s="88"/>
-      <c r="T61" s="88"/>
-      <c r="U61" s="88"/>
-      <c r="V61" s="88"/>
-      <c r="W61" s="88"/>
-      <c r="X61" s="88"/>
-      <c r="Y61" s="88"/>
-      <c r="Z61" s="88"/>
-      <c r="AA61" s="88"/>
-      <c r="AB61" s="88"/>
-      <c r="AC61" s="88"/>
-      <c r="AD61" s="88"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="59"/>
+      <c r="W61" s="59"/>
+      <c r="X61" s="59"/>
+      <c r="Y61" s="59"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="59"/>
+      <c r="AB61" s="59"/>
+      <c r="AC61" s="59"/>
+      <c r="AD61" s="59"/>
       <c r="AJ61" s="8"/>
     </row>
     <row r="62" spans="2:36" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="17"/>
-      <c r="C62" s="89" t="s">
+      <c r="C62" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="90" t="s">
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="90"/>
-      <c r="J62" s="90"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="90"/>
-      <c r="M62" s="91" t="s">
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N62" s="92"/>
-      <c r="O62" s="92"/>
-      <c r="P62" s="92"/>
-      <c r="Q62" s="92"/>
-      <c r="R62" s="93"/>
-      <c r="S62" s="90" t="s">
+      <c r="N62" s="40"/>
+      <c r="O62" s="40"/>
+      <c r="P62" s="40"/>
+      <c r="Q62" s="40"/>
+      <c r="R62" s="41"/>
+      <c r="S62" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="T62" s="90"/>
-      <c r="U62" s="90"/>
-      <c r="V62" s="90"/>
-      <c r="W62" s="90"/>
-      <c r="X62" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y62" s="95"/>
-      <c r="Z62" s="95"/>
-      <c r="AA62" s="95"/>
-      <c r="AB62" s="95"/>
-      <c r="AC62" s="95"/>
-      <c r="AD62" s="95"/>
-      <c r="AE62" s="95"/>
-      <c r="AF62" s="95"/>
-      <c r="AG62" s="95"/>
-      <c r="AH62" s="95"/>
-      <c r="AI62" s="96"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="38"/>
+      <c r="V62" s="38"/>
+      <c r="W62" s="38"/>
+      <c r="X62" s="42"/>
+      <c r="Y62" s="43"/>
+      <c r="Z62" s="43"/>
+      <c r="AA62" s="43"/>
+      <c r="AB62" s="43"/>
+      <c r="AC62" s="43"/>
+      <c r="AD62" s="43"/>
+      <c r="AE62" s="43"/>
+      <c r="AF62" s="43"/>
+      <c r="AG62" s="43"/>
+      <c r="AH62" s="43"/>
+      <c r="AI62" s="44"/>
       <c r="AJ62" s="8"/>
     </row>
     <row r="63" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B63" s="17"/>
-      <c r="C63" s="97"/>
-      <c r="D63" s="97"/>
-      <c r="E63" s="97"/>
-      <c r="F63" s="97"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="97"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="97"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="97"/>
-      <c r="M63" s="98"/>
-      <c r="N63" s="30"/>
-      <c r="O63" s="30"/>
-      <c r="P63" s="30"/>
-      <c r="Q63" s="30"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="97"/>
-      <c r="T63" s="97"/>
-      <c r="U63" s="97"/>
-      <c r="V63" s="97"/>
-      <c r="W63" s="97"/>
-      <c r="X63" s="99" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y63" s="100"/>
-      <c r="Z63" s="100"/>
-      <c r="AA63" s="100"/>
-      <c r="AB63" s="100"/>
-      <c r="AC63" s="100"/>
-      <c r="AD63" s="100"/>
-      <c r="AE63" s="100"/>
-      <c r="AF63" s="100"/>
-      <c r="AG63" s="100"/>
-      <c r="AH63" s="100"/>
-      <c r="AI63" s="100"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="45"/>
+      <c r="M63" s="46"/>
+      <c r="N63" s="47"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="47"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="48"/>
+      <c r="S63" s="45"/>
+      <c r="T63" s="45"/>
+      <c r="U63" s="45"/>
+      <c r="V63" s="45"/>
+      <c r="W63" s="45"/>
+      <c r="X63" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
+      <c r="AA63" s="50"/>
+      <c r="AB63" s="50"/>
+      <c r="AC63" s="50"/>
+      <c r="AD63" s="50"/>
+      <c r="AE63" s="50"/>
+      <c r="AF63" s="50"/>
+      <c r="AG63" s="50"/>
+      <c r="AH63" s="50"/>
+      <c r="AI63" s="50"/>
       <c r="AJ63" s="8"/>
     </row>
     <row r="64" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B64" s="17"/>
-      <c r="C64" s="97"/>
-      <c r="D64" s="97"/>
-      <c r="E64" s="97"/>
-      <c r="F64" s="97"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="97"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="97"/>
-      <c r="K64" s="97"/>
-      <c r="L64" s="97"/>
-      <c r="M64" s="98"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="97"/>
-      <c r="T64" s="97"/>
-      <c r="U64" s="97"/>
-      <c r="V64" s="97"/>
-      <c r="W64" s="97"/>
-      <c r="X64" s="100"/>
-      <c r="Y64" s="100"/>
-      <c r="Z64" s="100"/>
-      <c r="AA64" s="100"/>
-      <c r="AB64" s="100"/>
-      <c r="AC64" s="100"/>
-      <c r="AD64" s="100"/>
-      <c r="AE64" s="100"/>
-      <c r="AF64" s="100"/>
-      <c r="AG64" s="100"/>
-      <c r="AH64" s="100"/>
-      <c r="AI64" s="100"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="45"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="45"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="47"/>
+      <c r="O64" s="47"/>
+      <c r="P64" s="47"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="48"/>
+      <c r="S64" s="45"/>
+      <c r="T64" s="45"/>
+      <c r="U64" s="45"/>
+      <c r="V64" s="45"/>
+      <c r="W64" s="45"/>
+      <c r="X64" s="50"/>
+      <c r="Y64" s="50"/>
+      <c r="Z64" s="50"/>
+      <c r="AA64" s="50"/>
+      <c r="AB64" s="50"/>
+      <c r="AC64" s="50"/>
+      <c r="AD64" s="50"/>
+      <c r="AE64" s="50"/>
+      <c r="AF64" s="50"/>
+      <c r="AG64" s="50"/>
+      <c r="AH64" s="50"/>
+      <c r="AI64" s="50"/>
       <c r="AJ64" s="8"/>
     </row>
     <row r="65" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B65" s="17"/>
-      <c r="C65" s="97"/>
-      <c r="D65" s="97"/>
-      <c r="E65" s="97"/>
-      <c r="F65" s="97"/>
-      <c r="G65" s="97"/>
-      <c r="H65" s="97"/>
-      <c r="I65" s="97"/>
-      <c r="J65" s="97"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="97"/>
-      <c r="M65" s="98"/>
-      <c r="N65" s="30"/>
-      <c r="O65" s="30"/>
-      <c r="P65" s="30"/>
-      <c r="Q65" s="30"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="97"/>
-      <c r="T65" s="97"/>
-      <c r="U65" s="97"/>
-      <c r="V65" s="97"/>
-      <c r="W65" s="97"/>
-      <c r="X65" s="100"/>
-      <c r="Y65" s="100"/>
-      <c r="Z65" s="100"/>
-      <c r="AA65" s="100"/>
-      <c r="AB65" s="100"/>
-      <c r="AC65" s="100"/>
-      <c r="AD65" s="100"/>
-      <c r="AE65" s="100"/>
-      <c r="AF65" s="100"/>
-      <c r="AG65" s="100"/>
-      <c r="AH65" s="100"/>
-      <c r="AI65" s="100"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="46"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="47"/>
+      <c r="P65" s="47"/>
+      <c r="Q65" s="47"/>
+      <c r="R65" s="48"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="45"/>
+      <c r="U65" s="45"/>
+      <c r="V65" s="45"/>
+      <c r="W65" s="45"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
+      <c r="AA65" s="50"/>
+      <c r="AB65" s="50"/>
+      <c r="AC65" s="50"/>
+      <c r="AD65" s="50"/>
+      <c r="AE65" s="50"/>
+      <c r="AF65" s="50"/>
+      <c r="AG65" s="50"/>
+      <c r="AH65" s="50"/>
+      <c r="AI65" s="50"/>
       <c r="AJ65" s="8"/>
     </row>
     <row r="66" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B66" s="17"/>
-      <c r="C66" s="97"/>
-      <c r="D66" s="97"/>
-      <c r="E66" s="97"/>
-      <c r="F66" s="97"/>
-      <c r="G66" s="97"/>
-      <c r="H66" s="97"/>
-      <c r="I66" s="97"/>
-      <c r="J66" s="97"/>
-      <c r="K66" s="97"/>
-      <c r="L66" s="97"/>
-      <c r="M66" s="98"/>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
-      <c r="P66" s="30"/>
-      <c r="Q66" s="30"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="97"/>
-      <c r="T66" s="97"/>
-      <c r="U66" s="97"/>
-      <c r="V66" s="97"/>
-      <c r="W66" s="97"/>
-      <c r="X66" s="100"/>
-      <c r="Y66" s="100"/>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="100"/>
-      <c r="AB66" s="100"/>
-      <c r="AC66" s="100"/>
-      <c r="AD66" s="100"/>
-      <c r="AE66" s="100"/>
-      <c r="AF66" s="100"/>
-      <c r="AG66" s="100"/>
-      <c r="AH66" s="100"/>
-      <c r="AI66" s="100"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="46"/>
+      <c r="N66" s="47"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="47"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="48"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="45"/>
+      <c r="U66" s="45"/>
+      <c r="V66" s="45"/>
+      <c r="W66" s="45"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
+      <c r="AA66" s="50"/>
+      <c r="AB66" s="50"/>
+      <c r="AC66" s="50"/>
+      <c r="AD66" s="50"/>
+      <c r="AE66" s="50"/>
+      <c r="AF66" s="50"/>
+      <c r="AG66" s="50"/>
+      <c r="AH66" s="50"/>
+      <c r="AI66" s="50"/>
       <c r="AJ66" s="8"/>
     </row>
     <row r="67" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B67" s="17"/>
-      <c r="C67" s="102" t="s">
+      <c r="C67" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="102"/>
-      <c r="E67" s="102"/>
-      <c r="F67" s="102"/>
-      <c r="G67" s="102"/>
-      <c r="H67" s="102" t="s">
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="I67" s="102"/>
-      <c r="J67" s="102"/>
-      <c r="K67" s="102"/>
-      <c r="L67" s="102"/>
-      <c r="M67" s="103" t="s">
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="N67" s="104"/>
-      <c r="O67" s="104"/>
-      <c r="P67" s="104"/>
-      <c r="Q67" s="104"/>
-      <c r="R67" s="105"/>
-      <c r="S67" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="T67" s="54"/>
-      <c r="U67" s="54"/>
-      <c r="V67" s="54"/>
-      <c r="W67" s="54"/>
-      <c r="X67" s="100"/>
-      <c r="Y67" s="100"/>
-      <c r="Z67" s="100"/>
-      <c r="AA67" s="100"/>
-      <c r="AB67" s="100"/>
-      <c r="AC67" s="100"/>
-      <c r="AD67" s="100"/>
-      <c r="AE67" s="100"/>
-      <c r="AF67" s="100"/>
-      <c r="AG67" s="100"/>
-      <c r="AH67" s="100"/>
-      <c r="AI67" s="100"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="50"/>
+      <c r="Y67" s="50"/>
+      <c r="Z67" s="50"/>
+      <c r="AA67" s="50"/>
+      <c r="AB67" s="50"/>
+      <c r="AC67" s="50"/>
+      <c r="AD67" s="50"/>
+      <c r="AE67" s="50"/>
+      <c r="AF67" s="50"/>
+      <c r="AG67" s="50"/>
+      <c r="AH67" s="50"/>
+      <c r="AI67" s="50"/>
       <c r="AJ67" s="8"/>
     </row>
     <row r="68" spans="2:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="17"/>
-      <c r="C68" s="77" t="s">
+      <c r="C68" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="77"/>
-      <c r="E68" s="77"/>
-      <c r="F68" s="77"/>
-      <c r="G68" s="77"/>
-      <c r="H68" s="55" t="s">
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="55"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="70" t="s">
+      <c r="N68" s="35"/>
+      <c r="O68" s="35"/>
+      <c r="P68" s="35"/>
+      <c r="Q68" s="35"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="N68" s="71"/>
-      <c r="O68" s="71"/>
-      <c r="P68" s="71"/>
-      <c r="Q68" s="71"/>
-      <c r="R68" s="72"/>
-      <c r="S68" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="T68" s="77"/>
-      <c r="U68" s="77"/>
-      <c r="V68" s="77"/>
-      <c r="W68" s="77"/>
-      <c r="X68" s="100"/>
-      <c r="Y68" s="100"/>
-      <c r="Z68" s="100"/>
-      <c r="AA68" s="100"/>
-      <c r="AB68" s="100"/>
-      <c r="AC68" s="100"/>
-      <c r="AD68" s="100"/>
-      <c r="AE68" s="100"/>
-      <c r="AF68" s="100"/>
-      <c r="AG68" s="100"/>
-      <c r="AH68" s="100"/>
-      <c r="AI68" s="100"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
+      <c r="X68" s="50"/>
+      <c r="Y68" s="50"/>
+      <c r="Z68" s="50"/>
+      <c r="AA68" s="50"/>
+      <c r="AB68" s="50"/>
+      <c r="AC68" s="50"/>
+      <c r="AD68" s="50"/>
+      <c r="AE68" s="50"/>
+      <c r="AF68" s="50"/>
+      <c r="AG68" s="50"/>
+      <c r="AH68" s="50"/>
+      <c r="AI68" s="50"/>
       <c r="AJ68" s="8"/>
     </row>
     <row r="69" spans="2:36" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4420,175 +4415,38 @@
       <c r="AJ69" s="25"/>
     </row>
     <row r="70" spans="2:36" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="AE70" s="101" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF70" s="101"/>
-      <c r="AG70" s="101"/>
-      <c r="AH70" s="101"/>
-      <c r="AI70" s="101"/>
-      <c r="AJ70" s="101"/>
+      <c r="AE70" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF70" s="26"/>
+      <c r="AG70" s="26"/>
+      <c r="AH70" s="26"/>
+      <c r="AI70" s="26"/>
+      <c r="AJ70" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="202">
-    <mergeCell ref="AE70:AJ70"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:L67"/>
-    <mergeCell ref="M67:R67"/>
-    <mergeCell ref="S67:W67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="H68:L68"/>
-    <mergeCell ref="M68:R68"/>
-    <mergeCell ref="S68:W68"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H62:L62"/>
-    <mergeCell ref="M62:R62"/>
-    <mergeCell ref="S62:W62"/>
-    <mergeCell ref="X62:AI62"/>
-    <mergeCell ref="C63:G66"/>
-    <mergeCell ref="H63:L66"/>
-    <mergeCell ref="M63:R66"/>
-    <mergeCell ref="S63:W66"/>
-    <mergeCell ref="X63:AI68"/>
-    <mergeCell ref="AA40:AC40"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="C41:AI49"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H60:AD60"/>
-    <mergeCell ref="H61:AD61"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="AA39:AC39"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="U40:W40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="O39:Q39"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="U39:W39"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="U38:W38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="AA38:AC38"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="U37:W37"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="AA37:AC37"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X35:Z35"/>
-    <mergeCell ref="AA35:AC35"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="U36:W36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="U35:W35"/>
-    <mergeCell ref="AA36:AC36"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="X34:Z34"/>
-    <mergeCell ref="AA34:AC34"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="X33:Z33"/>
-    <mergeCell ref="AA33:AC33"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="X31:Z31"/>
-    <mergeCell ref="AA31:AC31"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="U31:W31"/>
-    <mergeCell ref="AA32:AC32"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="X29:Z29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="AA28:AC28"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="B2:G5"/>
+    <mergeCell ref="H2:AJ5"/>
+    <mergeCell ref="B6:AJ6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="AA12:AI17"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="S11:Y11"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="R24:T24"/>
@@ -4612,27 +4470,164 @@
     <mergeCell ref="U25:W25"/>
     <mergeCell ref="X25:Z25"/>
     <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="B2:G5"/>
-    <mergeCell ref="H2:AJ5"/>
-    <mergeCell ref="B6:AJ6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="AA12:AI17"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AC27"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="AA28:AC28"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="X31:Z31"/>
+    <mergeCell ref="AA31:AC31"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="X33:Z33"/>
+    <mergeCell ref="AA33:AC33"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="AA34:AC34"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="AA37:AC37"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="U38:W38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="AA38:AC38"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AA40:AC40"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="C41:AI49"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H60:AD60"/>
+    <mergeCell ref="H61:AD61"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="AA39:AC39"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="U40:W40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="O39:Q39"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H62:L62"/>
+    <mergeCell ref="M62:R62"/>
+    <mergeCell ref="S62:W62"/>
+    <mergeCell ref="X62:AI62"/>
+    <mergeCell ref="C63:G66"/>
+    <mergeCell ref="H63:L66"/>
+    <mergeCell ref="M63:R66"/>
+    <mergeCell ref="S63:W66"/>
+    <mergeCell ref="X63:AI68"/>
+    <mergeCell ref="AE70:AJ70"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M67:R67"/>
+    <mergeCell ref="S67:W67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="H68:L68"/>
+    <mergeCell ref="M68:R68"/>
+    <mergeCell ref="S68:W68"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.23999999999999996" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
+++ b/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE243DE-9F21-4870-94CE-174878320EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B600032-21FF-47FF-857B-8FDA15275863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{D57B88DC-6A9D-42A6-BE16-0F559C48DA93}"/>
   </bookViews>
@@ -742,6 +742,231 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -756,231 +981,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1331,7 +1331,6 @@
         <c:axId val="1"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2020,201 +2019,201 @@
   <sheetData>
     <row r="1" spans="2:39" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:39" ht="19" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="87"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="94" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="95"/>
-      <c r="Y2" s="95"/>
-      <c r="Z2" s="95"/>
-      <c r="AA2" s="95"/>
-      <c r="AB2" s="95"/>
-      <c r="AC2" s="95"/>
-      <c r="AD2" s="95"/>
-      <c r="AE2" s="95"/>
-      <c r="AF2" s="95"/>
-      <c r="AG2" s="95"/>
-      <c r="AH2" s="95"/>
-      <c r="AI2" s="95"/>
-      <c r="AJ2" s="96"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="37"/>
     </row>
     <row r="3" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="90"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
-      <c r="V3" s="97"/>
-      <c r="W3" s="97"/>
-      <c r="X3" s="97"/>
-      <c r="Y3" s="97"/>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="97"/>
-      <c r="AC3" s="97"/>
-      <c r="AD3" s="97"/>
-      <c r="AE3" s="97"/>
-      <c r="AF3" s="97"/>
-      <c r="AG3" s="97"/>
-      <c r="AH3" s="97"/>
-      <c r="AI3" s="97"/>
-      <c r="AJ3" s="98"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="39"/>
     </row>
     <row r="4" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="90"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="97"/>
-      <c r="W4" s="97"/>
-      <c r="X4" s="97"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="97"/>
-      <c r="AC4" s="97"/>
-      <c r="AD4" s="97"/>
-      <c r="AE4" s="97"/>
-      <c r="AF4" s="97"/>
-      <c r="AG4" s="97"/>
-      <c r="AH4" s="97"/>
-      <c r="AI4" s="97"/>
-      <c r="AJ4" s="98"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="39"/>
     </row>
     <row r="5" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="99"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="100"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="40"/>
+      <c r="W5" s="40"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="40"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="40"/>
+      <c r="AC5" s="40"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="40"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="40"/>
+      <c r="AI5" s="40"/>
+      <c r="AJ5" s="41"/>
     </row>
     <row r="6" spans="2:39" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="91"/>
-      <c r="C6" s="92"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="92"/>
-      <c r="S6" s="92"/>
-      <c r="T6" s="92"/>
-      <c r="U6" s="92"/>
-      <c r="V6" s="92"/>
-      <c r="W6" s="92"/>
-      <c r="X6" s="92"/>
-      <c r="Y6" s="92"/>
-      <c r="Z6" s="92"/>
-      <c r="AA6" s="92"/>
-      <c r="AB6" s="92"/>
-      <c r="AC6" s="92"/>
-      <c r="AD6" s="92"/>
-      <c r="AE6" s="92"/>
-      <c r="AF6" s="92"/>
-      <c r="AG6" s="92"/>
-      <c r="AH6" s="92"/>
-      <c r="AI6" s="92"/>
-      <c r="AJ6" s="101"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33"/>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="33"/>
+      <c r="AJ6" s="42"/>
     </row>
     <row r="7" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
       <c r="H7" s="4" t="s">
         <v>2</v>
       </c>
@@ -2228,15 +2227,15 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="104" t="s">
+      <c r="S7" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="104"/>
-      <c r="W7" s="104"/>
-      <c r="X7" s="104"/>
-      <c r="Y7" s="104"/>
+      <c r="T7" s="45"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
+      <c r="W7" s="45"/>
+      <c r="X7" s="45"/>
+      <c r="Y7" s="45"/>
       <c r="Z7" s="6" t="s">
         <v>2</v>
       </c>
@@ -2252,14 +2251,14 @@
       <c r="AJ7" s="8"/>
     </row>
     <row r="8" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
       <c r="H8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2273,15 +2272,15 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="104" t="s">
+      <c r="S8" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="T8" s="104"/>
-      <c r="U8" s="104"/>
-      <c r="V8" s="104"/>
-      <c r="W8" s="104"/>
-      <c r="X8" s="104"/>
-      <c r="Y8" s="104"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="45"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="45"/>
+      <c r="X8" s="45"/>
+      <c r="Y8" s="45"/>
       <c r="Z8" s="6" t="s">
         <v>2</v>
       </c>
@@ -2297,14 +2296,14 @@
       <c r="AJ8" s="8"/>
     </row>
     <row r="9" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
       <c r="H9" s="4" t="s">
         <v>2</v>
       </c>
@@ -2318,15 +2317,15 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="103" t="s">
+      <c r="S9" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
       <c r="Z9" s="6" t="s">
         <v>2</v>
       </c>
@@ -2345,14 +2344,14 @@
       <c r="AM9" s="11"/>
     </row>
     <row r="10" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
       <c r="H10" s="4" t="s">
         <v>2</v>
       </c>
@@ -2366,15 +2365,15 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="104" t="s">
+      <c r="S10" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="104"/>
-      <c r="U10" s="104"/>
-      <c r="V10" s="104"/>
-      <c r="W10" s="104"/>
-      <c r="X10" s="104"/>
-      <c r="Y10" s="104"/>
+      <c r="T10" s="45"/>
+      <c r="U10" s="45"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="45"/>
+      <c r="X10" s="45"/>
+      <c r="Y10" s="45"/>
       <c r="Z10" s="6" t="s">
         <v>2</v>
       </c>
@@ -2393,14 +2392,14 @@
       <c r="AM10" s="11"/>
     </row>
     <row r="11" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
       <c r="H11" s="4" t="s">
         <v>2</v>
       </c>
@@ -2414,15 +2413,15 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="104" t="s">
+      <c r="S11" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="104"/>
-      <c r="U11" s="104"/>
-      <c r="V11" s="104"/>
-      <c r="W11" s="104"/>
-      <c r="X11" s="104"/>
-      <c r="Y11" s="104"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
       <c r="Z11" s="6" t="s">
         <v>2</v>
       </c>
@@ -2441,14 +2440,14 @@
       <c r="AM11" s="11"/>
     </row>
     <row r="12" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
       <c r="H12" s="4" t="s">
         <v>2</v>
       </c>
@@ -2462,43 +2461,43 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="104" t="s">
+      <c r="S12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="T12" s="104"/>
-      <c r="U12" s="104"/>
-      <c r="V12" s="104"/>
-      <c r="W12" s="104"/>
-      <c r="X12" s="104"/>
-      <c r="Y12" s="104"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
+      <c r="W12" s="45"/>
+      <c r="X12" s="45"/>
+      <c r="Y12" s="45"/>
       <c r="Z12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="105" t="s">
+      <c r="AA12" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="AB12" s="105"/>
-      <c r="AC12" s="105"/>
-      <c r="AD12" s="105"/>
-      <c r="AE12" s="105"/>
-      <c r="AF12" s="105"/>
-      <c r="AG12" s="105"/>
-      <c r="AH12" s="105"/>
-      <c r="AI12" s="105"/>
+      <c r="AB12" s="46"/>
+      <c r="AC12" s="46"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="46"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="46"/>
+      <c r="AH12" s="46"/>
+      <c r="AI12" s="46"/>
       <c r="AJ12" s="10"/>
       <c r="AK12" s="11"/>
       <c r="AL12" s="11"/>
       <c r="AM12" s="11"/>
     </row>
     <row r="13" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
       <c r="H13" s="4" t="s">
         <v>2</v>
       </c>
@@ -2520,29 +2519,29 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="105"/>
-      <c r="AB13" s="105"/>
-      <c r="AC13" s="105"/>
-      <c r="AD13" s="105"/>
-      <c r="AE13" s="105"/>
-      <c r="AF13" s="105"/>
-      <c r="AG13" s="105"/>
-      <c r="AH13" s="105"/>
-      <c r="AI13" s="105"/>
+      <c r="AA13" s="46"/>
+      <c r="AB13" s="46"/>
+      <c r="AC13" s="46"/>
+      <c r="AD13" s="46"/>
+      <c r="AE13" s="46"/>
+      <c r="AF13" s="46"/>
+      <c r="AG13" s="46"/>
+      <c r="AH13" s="46"/>
+      <c r="AI13" s="46"/>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="11"/>
       <c r="AL13" s="11"/>
       <c r="AM13" s="11"/>
     </row>
     <row r="14" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="4" t="s">
         <v>2</v>
       </c>
@@ -2564,29 +2563,29 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="105"/>
-      <c r="AB14" s="105"/>
-      <c r="AC14" s="105"/>
-      <c r="AD14" s="105"/>
-      <c r="AE14" s="105"/>
-      <c r="AF14" s="105"/>
-      <c r="AG14" s="105"/>
-      <c r="AH14" s="105"/>
-      <c r="AI14" s="105"/>
+      <c r="AA14" s="46"/>
+      <c r="AB14" s="46"/>
+      <c r="AC14" s="46"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
       <c r="AJ14" s="10"/>
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
     </row>
     <row r="15" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="4" t="s">
         <v>2</v>
       </c>
@@ -2608,26 +2607,26 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
-      <c r="AA15" s="105"/>
-      <c r="AB15" s="105"/>
-      <c r="AC15" s="105"/>
-      <c r="AD15" s="105"/>
-      <c r="AE15" s="105"/>
-      <c r="AF15" s="105"/>
-      <c r="AG15" s="105"/>
-      <c r="AH15" s="105"/>
-      <c r="AI15" s="105"/>
+      <c r="AA15" s="46"/>
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="46"/>
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="46"/>
       <c r="AJ15" s="8"/>
     </row>
     <row r="16" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
       <c r="H16" s="4" t="s">
         <v>2</v>
       </c>
@@ -2649,26 +2648,26 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
-      <c r="AA16" s="105"/>
-      <c r="AB16" s="105"/>
-      <c r="AC16" s="105"/>
-      <c r="AD16" s="105"/>
-      <c r="AE16" s="105"/>
-      <c r="AF16" s="105"/>
-      <c r="AG16" s="105"/>
-      <c r="AH16" s="105"/>
-      <c r="AI16" s="105"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="46"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="46"/>
+      <c r="AI16" s="46"/>
       <c r="AJ16" s="8"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="4" t="s">
         <v>2</v>
       </c>
@@ -2690,53 +2689,53 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
-      <c r="AA17" s="105"/>
-      <c r="AB17" s="105"/>
-      <c r="AC17" s="105"/>
-      <c r="AD17" s="105"/>
-      <c r="AE17" s="105"/>
-      <c r="AF17" s="105"/>
-      <c r="AG17" s="105"/>
-      <c r="AH17" s="105"/>
-      <c r="AI17" s="105"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="46"/>
+      <c r="AI17" s="46"/>
       <c r="AJ17" s="8"/>
     </row>
     <row r="18" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="68"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="69"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="69"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="69"/>
-      <c r="X18" s="69"/>
-      <c r="Y18" s="69"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="69"/>
-      <c r="AB18" s="69"/>
-      <c r="AC18" s="69"/>
-      <c r="AD18" s="69"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="69"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="70"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="49"/>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="49"/>
+      <c r="AJ18" s="50"/>
     </row>
     <row r="19" spans="2:36" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="2"/>
@@ -2754,14 +2753,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="15"/>
-      <c r="Q19" s="71" t="s">
+      <c r="Q19" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="72"/>
-      <c r="V19" s="72"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="52"/>
+      <c r="T19" s="52"/>
+      <c r="U19" s="52"/>
+      <c r="V19" s="52"/>
       <c r="W19" s="15"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2783,229 +2782,229 @@
     </row>
     <row r="21" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="17"/>
-      <c r="C21" s="73" t="s">
+      <c r="C21" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="74" t="s">
+      <c r="D21" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
-      <c r="J21" s="75"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="83" t="s">
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83" t="s">
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="S21" s="83"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="65" t="s">
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="Y21" s="65"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="65"/>
-      <c r="AC21" s="65"/>
-      <c r="AD21" s="74" t="s">
+      <c r="Y21" s="66"/>
+      <c r="Z21" s="66"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="66"/>
+      <c r="AC21" s="66"/>
+      <c r="AD21" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="AE21" s="75"/>
-      <c r="AF21" s="75"/>
-      <c r="AG21" s="75"/>
-      <c r="AH21" s="75"/>
-      <c r="AI21" s="76"/>
+      <c r="AE21" s="57"/>
+      <c r="AF21" s="57"/>
+      <c r="AG21" s="57"/>
+      <c r="AH21" s="57"/>
+      <c r="AI21" s="58"/>
       <c r="AJ21" s="8"/>
     </row>
     <row r="22" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="83"/>
-      <c r="T22" s="83"/>
-      <c r="U22" s="83"/>
-      <c r="V22" s="83"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="78"/>
-      <c r="AF22" s="78"/>
-      <c r="AG22" s="78"/>
-      <c r="AH22" s="78"/>
-      <c r="AI22" s="79"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="59"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="61"/>
       <c r="AJ22" s="8"/>
     </row>
     <row r="23" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="17"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-      <c r="U23" s="83"/>
-      <c r="V23" s="83"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="65"/>
-      <c r="Y23" s="65"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="65"/>
-      <c r="AD23" s="77"/>
-      <c r="AE23" s="78"/>
-      <c r="AF23" s="78"/>
-      <c r="AG23" s="78"/>
-      <c r="AH23" s="78"/>
-      <c r="AI23" s="79"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="65"/>
+      <c r="P23" s="65"/>
+      <c r="Q23" s="65"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="65"/>
+      <c r="U23" s="65"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="66"/>
+      <c r="Y23" s="66"/>
+      <c r="Z23" s="66"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="59"/>
+      <c r="AE23" s="60"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="61"/>
       <c r="AJ23" s="8"/>
     </row>
     <row r="24" spans="2:36" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="84" t="s">
+      <c r="C24" s="54"/>
+      <c r="D24" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="85"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="84" t="s">
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="67" t="s">
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="M24" s="67"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="67" t="s">
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="P24" s="67"/>
-      <c r="Q24" s="67"/>
-      <c r="R24" s="67" t="s">
+      <c r="P24" s="47"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S24" s="67"/>
-      <c r="T24" s="67"/>
-      <c r="U24" s="67" t="s">
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67"/>
-      <c r="X24" s="67" t="s">
+      <c r="V24" s="47"/>
+      <c r="W24" s="47"/>
+      <c r="X24" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67" t="s">
+      <c r="Y24" s="47"/>
+      <c r="Z24" s="47"/>
+      <c r="AA24" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="AB24" s="67"/>
-      <c r="AC24" s="67"/>
-      <c r="AD24" s="77"/>
-      <c r="AE24" s="78"/>
-      <c r="AF24" s="78"/>
-      <c r="AG24" s="78"/>
-      <c r="AH24" s="78"/>
-      <c r="AI24" s="79"/>
+      <c r="AB24" s="47"/>
+      <c r="AC24" s="47"/>
+      <c r="AD24" s="59"/>
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="61"/>
       <c r="AJ24" s="8"/>
     </row>
     <row r="25" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="32" t="s">
+      <c r="C25" s="55"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="33" t="s">
+      <c r="M25" s="73"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33" t="s">
+      <c r="P25" s="55"/>
+      <c r="Q25" s="55"/>
+      <c r="R25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33" t="s">
+      <c r="S25" s="55"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33" t="s">
+      <c r="V25" s="55"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="33"/>
-      <c r="AA25" s="33" t="s">
+      <c r="Y25" s="55"/>
+      <c r="Z25" s="55"/>
+      <c r="AA25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="34" t="s">
+      <c r="AB25" s="55"/>
+      <c r="AC25" s="55"/>
+      <c r="AD25" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="AE25" s="35"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25" s="35"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="36"/>
+      <c r="AE25" s="71"/>
+      <c r="AF25" s="71"/>
+      <c r="AG25" s="71"/>
+      <c r="AH25" s="71"/>
+      <c r="AI25" s="72"/>
       <c r="AJ25" s="8"/>
     </row>
     <row r="26" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3013,38 +3012,38 @@
       <c r="C26" s="18">
         <v>1</v>
       </c>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="61"/>
-      <c r="R26" s="61"/>
-      <c r="S26" s="61"/>
-      <c r="T26" s="61"/>
-      <c r="U26" s="61"/>
-      <c r="V26" s="61"/>
-      <c r="W26" s="61"/>
-      <c r="X26" s="61"/>
-      <c r="Y26" s="61"/>
-      <c r="Z26" s="61"/>
-      <c r="AA26" s="61"/>
-      <c r="AB26" s="61"/>
-      <c r="AC26" s="61"/>
-      <c r="AD26" s="62"/>
-      <c r="AE26" s="63"/>
-      <c r="AF26" s="63"/>
-      <c r="AG26" s="63"/>
-      <c r="AH26" s="63"/>
-      <c r="AI26" s="64"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+      <c r="Q26" s="74"/>
+      <c r="R26" s="74"/>
+      <c r="S26" s="74"/>
+      <c r="T26" s="74"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="74"/>
+      <c r="W26" s="74"/>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="74"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="75"/>
+      <c r="AE26" s="76"/>
+      <c r="AF26" s="76"/>
+      <c r="AG26" s="76"/>
+      <c r="AH26" s="76"/>
+      <c r="AI26" s="77"/>
       <c r="AJ26" s="8"/>
     </row>
     <row r="27" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3052,38 +3051,38 @@
       <c r="C27" s="18">
         <v>2</v>
       </c>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
-      <c r="K27" s="61"/>
-      <c r="L27" s="61"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="61"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="61"/>
-      <c r="R27" s="61"/>
-      <c r="S27" s="61"/>
-      <c r="T27" s="61"/>
-      <c r="U27" s="61"/>
-      <c r="V27" s="61"/>
-      <c r="W27" s="61"/>
-      <c r="X27" s="61"/>
-      <c r="Y27" s="61"/>
-      <c r="Z27" s="61"/>
-      <c r="AA27" s="61"/>
-      <c r="AB27" s="61"/>
-      <c r="AC27" s="61"/>
-      <c r="AD27" s="62"/>
-      <c r="AE27" s="63"/>
-      <c r="AF27" s="63"/>
-      <c r="AG27" s="63"/>
-      <c r="AH27" s="63"/>
-      <c r="AI27" s="64"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
+      <c r="J27" s="74"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="74"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="74"/>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="75"/>
+      <c r="AE27" s="76"/>
+      <c r="AF27" s="76"/>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="77"/>
       <c r="AJ27" s="8"/>
     </row>
     <row r="28" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3091,38 +3090,38 @@
       <c r="C28" s="18">
         <v>3</v>
       </c>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="61"/>
-      <c r="L28" s="61"/>
-      <c r="M28" s="61"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="61"/>
-      <c r="Q28" s="61"/>
-      <c r="R28" s="61"/>
-      <c r="S28" s="61"/>
-      <c r="T28" s="61"/>
-      <c r="U28" s="61"/>
-      <c r="V28" s="61"/>
-      <c r="W28" s="61"/>
-      <c r="X28" s="61"/>
-      <c r="Y28" s="61"/>
-      <c r="Z28" s="61"/>
-      <c r="AA28" s="61"/>
-      <c r="AB28" s="61"/>
-      <c r="AC28" s="61"/>
-      <c r="AD28" s="62"/>
-      <c r="AE28" s="63"/>
-      <c r="AF28" s="63"/>
-      <c r="AG28" s="63"/>
-      <c r="AH28" s="63"/>
-      <c r="AI28" s="64"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
+      <c r="J28" s="74"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="74"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="74"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="74"/>
+      <c r="Z28" s="74"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="75"/>
+      <c r="AE28" s="76"/>
+      <c r="AF28" s="76"/>
+      <c r="AG28" s="76"/>
+      <c r="AH28" s="76"/>
+      <c r="AI28" s="77"/>
       <c r="AJ28" s="19"/>
     </row>
     <row r="29" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3130,38 +3129,38 @@
       <c r="C29" s="18">
         <v>4</v>
       </c>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="61"/>
-      <c r="L29" s="61"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="61"/>
-      <c r="Q29" s="61"/>
-      <c r="R29" s="61"/>
-      <c r="S29" s="61"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="61"/>
-      <c r="V29" s="61"/>
-      <c r="W29" s="61"/>
-      <c r="X29" s="61"/>
-      <c r="Y29" s="61"/>
-      <c r="Z29" s="61"/>
-      <c r="AA29" s="61"/>
-      <c r="AB29" s="61"/>
-      <c r="AC29" s="61"/>
-      <c r="AD29" s="62"/>
-      <c r="AE29" s="63"/>
-      <c r="AF29" s="63"/>
-      <c r="AG29" s="63"/>
-      <c r="AH29" s="63"/>
-      <c r="AI29" s="64"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
+      <c r="J29" s="74"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
+      <c r="U29" s="74"/>
+      <c r="V29" s="74"/>
+      <c r="W29" s="74"/>
+      <c r="X29" s="74"/>
+      <c r="Y29" s="74"/>
+      <c r="Z29" s="74"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="75"/>
+      <c r="AE29" s="76"/>
+      <c r="AF29" s="76"/>
+      <c r="AG29" s="76"/>
+      <c r="AH29" s="76"/>
+      <c r="AI29" s="77"/>
       <c r="AJ29" s="19"/>
     </row>
     <row r="30" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3169,38 +3168,38 @@
       <c r="C30" s="18">
         <v>5</v>
       </c>
-      <c r="D30" s="65"/>
-      <c r="E30" s="65"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
-      <c r="S30" s="61"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="61"/>
-      <c r="V30" s="61"/>
-      <c r="W30" s="61"/>
-      <c r="X30" s="61"/>
-      <c r="Y30" s="61"/>
-      <c r="Z30" s="61"/>
-      <c r="AA30" s="66"/>
-      <c r="AB30" s="66"/>
-      <c r="AC30" s="66"/>
-      <c r="AD30" s="62"/>
-      <c r="AE30" s="63"/>
-      <c r="AF30" s="63"/>
-      <c r="AG30" s="63"/>
-      <c r="AH30" s="63"/>
-      <c r="AI30" s="64"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
+      <c r="U30" s="74"/>
+      <c r="V30" s="74"/>
+      <c r="W30" s="74"/>
+      <c r="X30" s="74"/>
+      <c r="Y30" s="74"/>
+      <c r="Z30" s="74"/>
+      <c r="AA30" s="78"/>
+      <c r="AB30" s="78"/>
+      <c r="AC30" s="78"/>
+      <c r="AD30" s="75"/>
+      <c r="AE30" s="76"/>
+      <c r="AF30" s="76"/>
+      <c r="AG30" s="76"/>
+      <c r="AH30" s="76"/>
+      <c r="AI30" s="77"/>
       <c r="AJ30" s="19"/>
     </row>
     <row r="31" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3208,38 +3207,38 @@
       <c r="C31" s="18">
         <v>6</v>
       </c>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
-      <c r="K31" s="61"/>
-      <c r="L31" s="61"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="61"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="61"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="61"/>
-      <c r="Y31" s="61"/>
-      <c r="Z31" s="61"/>
-      <c r="AA31" s="61"/>
-      <c r="AB31" s="61"/>
-      <c r="AC31" s="61"/>
-      <c r="AD31" s="62"/>
-      <c r="AE31" s="63"/>
-      <c r="AF31" s="63"/>
-      <c r="AG31" s="63"/>
-      <c r="AH31" s="63"/>
-      <c r="AI31" s="64"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="66"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="74"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="74"/>
+      <c r="X31" s="74"/>
+      <c r="Y31" s="74"/>
+      <c r="Z31" s="74"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="74"/>
+      <c r="AD31" s="75"/>
+      <c r="AE31" s="76"/>
+      <c r="AF31" s="76"/>
+      <c r="AG31" s="76"/>
+      <c r="AH31" s="76"/>
+      <c r="AI31" s="77"/>
       <c r="AJ31" s="19"/>
     </row>
     <row r="32" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3247,38 +3246,38 @@
       <c r="C32" s="18">
         <v>7</v>
       </c>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
-      <c r="N32" s="61"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="61"/>
-      <c r="Q32" s="61"/>
-      <c r="R32" s="61"/>
-      <c r="S32" s="61"/>
-      <c r="T32" s="61"/>
-      <c r="U32" s="61"/>
-      <c r="V32" s="61"/>
-      <c r="W32" s="61"/>
-      <c r="X32" s="61"/>
-      <c r="Y32" s="61"/>
-      <c r="Z32" s="61"/>
-      <c r="AA32" s="61"/>
-      <c r="AB32" s="61"/>
-      <c r="AC32" s="61"/>
-      <c r="AD32" s="62"/>
-      <c r="AE32" s="63"/>
-      <c r="AF32" s="63"/>
-      <c r="AG32" s="63"/>
-      <c r="AH32" s="63"/>
-      <c r="AI32" s="64"/>
+      <c r="D32" s="66"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="66"/>
+      <c r="G32" s="66"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="74"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="74"/>
+      <c r="Q32" s="74"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
+      <c r="U32" s="74"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="74"/>
+      <c r="X32" s="74"/>
+      <c r="Y32" s="74"/>
+      <c r="Z32" s="74"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="74"/>
+      <c r="AD32" s="75"/>
+      <c r="AE32" s="76"/>
+      <c r="AF32" s="76"/>
+      <c r="AG32" s="76"/>
+      <c r="AH32" s="76"/>
+      <c r="AI32" s="77"/>
       <c r="AJ32" s="8"/>
     </row>
     <row r="33" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3286,38 +3285,38 @@
       <c r="C33" s="18">
         <v>8</v>
       </c>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
-      <c r="N33" s="65"/>
-      <c r="O33" s="65"/>
-      <c r="P33" s="65"/>
-      <c r="Q33" s="65"/>
-      <c r="R33" s="61"/>
-      <c r="S33" s="61"/>
-      <c r="T33" s="61"/>
-      <c r="U33" s="61"/>
-      <c r="V33" s="61"/>
-      <c r="W33" s="61"/>
-      <c r="X33" s="61"/>
-      <c r="Y33" s="61"/>
-      <c r="Z33" s="61"/>
-      <c r="AA33" s="61"/>
-      <c r="AB33" s="61"/>
-      <c r="AC33" s="61"/>
-      <c r="AD33" s="62"/>
-      <c r="AE33" s="63"/>
-      <c r="AF33" s="63"/>
-      <c r="AG33" s="63"/>
-      <c r="AH33" s="63"/>
-      <c r="AI33" s="64"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
+      <c r="N33" s="66"/>
+      <c r="O33" s="66"/>
+      <c r="P33" s="66"/>
+      <c r="Q33" s="66"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
+      <c r="U33" s="74"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="74"/>
+      <c r="X33" s="74"/>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="75"/>
+      <c r="AE33" s="76"/>
+      <c r="AF33" s="76"/>
+      <c r="AG33" s="76"/>
+      <c r="AH33" s="76"/>
+      <c r="AI33" s="77"/>
       <c r="AJ33" s="8"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3325,38 +3324,38 @@
       <c r="C34" s="18">
         <v>9</v>
       </c>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65"/>
-      <c r="L34" s="65"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="65"/>
-      <c r="O34" s="65"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="61"/>
-      <c r="S34" s="61"/>
-      <c r="T34" s="61"/>
-      <c r="U34" s="61"/>
-      <c r="V34" s="61"/>
-      <c r="W34" s="61"/>
-      <c r="X34" s="61"/>
-      <c r="Y34" s="61"/>
-      <c r="Z34" s="61"/>
-      <c r="AA34" s="61"/>
-      <c r="AB34" s="61"/>
-      <c r="AC34" s="61"/>
-      <c r="AD34" s="62"/>
-      <c r="AE34" s="63"/>
-      <c r="AF34" s="63"/>
-      <c r="AG34" s="63"/>
-      <c r="AH34" s="63"/>
-      <c r="AI34" s="64"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="66"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="66"/>
+      <c r="M34" s="66"/>
+      <c r="N34" s="66"/>
+      <c r="O34" s="66"/>
+      <c r="P34" s="66"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="74"/>
+      <c r="S34" s="74"/>
+      <c r="T34" s="74"/>
+      <c r="U34" s="74"/>
+      <c r="V34" s="74"/>
+      <c r="W34" s="74"/>
+      <c r="X34" s="74"/>
+      <c r="Y34" s="74"/>
+      <c r="Z34" s="74"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="74"/>
+      <c r="AC34" s="74"/>
+      <c r="AD34" s="75"/>
+      <c r="AE34" s="76"/>
+      <c r="AF34" s="76"/>
+      <c r="AG34" s="76"/>
+      <c r="AH34" s="76"/>
+      <c r="AI34" s="77"/>
       <c r="AJ34" s="8"/>
     </row>
     <row r="35" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3364,38 +3363,38 @@
       <c r="C35" s="18">
         <v>10</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="60"/>
-      <c r="G35" s="60"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="61"/>
-      <c r="S35" s="61"/>
-      <c r="T35" s="61"/>
-      <c r="U35" s="61"/>
-      <c r="V35" s="61"/>
-      <c r="W35" s="61"/>
-      <c r="X35" s="61"/>
-      <c r="Y35" s="61"/>
-      <c r="Z35" s="61"/>
-      <c r="AA35" s="61"/>
-      <c r="AB35" s="61"/>
-      <c r="AC35" s="61"/>
-      <c r="AD35" s="62"/>
-      <c r="AE35" s="63"/>
-      <c r="AF35" s="63"/>
-      <c r="AG35" s="63"/>
-      <c r="AH35" s="63"/>
-      <c r="AI35" s="64"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="66"/>
+      <c r="N35" s="66"/>
+      <c r="O35" s="66"/>
+      <c r="P35" s="66"/>
+      <c r="Q35" s="66"/>
+      <c r="R35" s="74"/>
+      <c r="S35" s="74"/>
+      <c r="T35" s="74"/>
+      <c r="U35" s="74"/>
+      <c r="V35" s="74"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="74"/>
+      <c r="Y35" s="74"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="74"/>
+      <c r="AD35" s="75"/>
+      <c r="AE35" s="76"/>
+      <c r="AF35" s="76"/>
+      <c r="AG35" s="76"/>
+      <c r="AH35" s="76"/>
+      <c r="AI35" s="77"/>
       <c r="AJ35" s="8"/>
     </row>
     <row r="36" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3403,38 +3402,38 @@
       <c r="C36" s="18">
         <v>11</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60"/>
-      <c r="F36" s="60"/>
-      <c r="G36" s="60"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="65"/>
-      <c r="L36" s="65"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-      <c r="O36" s="65"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="65"/>
-      <c r="R36" s="61"/>
-      <c r="S36" s="61"/>
-      <c r="T36" s="61"/>
-      <c r="U36" s="61"/>
-      <c r="V36" s="61"/>
-      <c r="W36" s="61"/>
-      <c r="X36" s="61"/>
-      <c r="Y36" s="61"/>
-      <c r="Z36" s="61"/>
-      <c r="AA36" s="61"/>
-      <c r="AB36" s="61"/>
-      <c r="AC36" s="61"/>
-      <c r="AD36" s="62"/>
-      <c r="AE36" s="63"/>
-      <c r="AF36" s="63"/>
-      <c r="AG36" s="63"/>
-      <c r="AH36" s="63"/>
-      <c r="AI36" s="64"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="66"/>
+      <c r="J36" s="66"/>
+      <c r="K36" s="66"/>
+      <c r="L36" s="66"/>
+      <c r="M36" s="66"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="66"/>
+      <c r="P36" s="66"/>
+      <c r="Q36" s="66"/>
+      <c r="R36" s="74"/>
+      <c r="S36" s="74"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="74"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="74"/>
+      <c r="X36" s="74"/>
+      <c r="Y36" s="74"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="74"/>
+      <c r="AD36" s="75"/>
+      <c r="AE36" s="76"/>
+      <c r="AF36" s="76"/>
+      <c r="AG36" s="76"/>
+      <c r="AH36" s="76"/>
+      <c r="AI36" s="77"/>
       <c r="AJ36" s="8"/>
     </row>
     <row r="37" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3442,38 +3441,38 @@
       <c r="C37" s="18">
         <v>12</v>
       </c>
-      <c r="D37" s="60"/>
-      <c r="E37" s="60"/>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="51"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="51"/>
-      <c r="X37" s="51"/>
-      <c r="Y37" s="51"/>
-      <c r="Z37" s="51"/>
-      <c r="AA37" s="51"/>
-      <c r="AB37" s="51"/>
-      <c r="AC37" s="51"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="53"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="54"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="80"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="80"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="80"/>
+      <c r="O37" s="80"/>
+      <c r="P37" s="80"/>
+      <c r="Q37" s="80"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="80"/>
+      <c r="U37" s="80"/>
+      <c r="V37" s="80"/>
+      <c r="W37" s="80"/>
+      <c r="X37" s="80"/>
+      <c r="Y37" s="80"/>
+      <c r="Z37" s="80"/>
+      <c r="AA37" s="80"/>
+      <c r="AB37" s="80"/>
+      <c r="AC37" s="80"/>
+      <c r="AD37" s="81"/>
+      <c r="AE37" s="82"/>
+      <c r="AF37" s="82"/>
+      <c r="AG37" s="82"/>
+      <c r="AH37" s="82"/>
+      <c r="AI37" s="83"/>
       <c r="AJ37" s="8"/>
     </row>
     <row r="38" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3481,38 +3480,38 @@
       <c r="C38" s="18">
         <v>13</v>
       </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51"/>
-      <c r="U38" s="51"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="51"/>
-      <c r="X38" s="51"/>
-      <c r="Y38" s="51"/>
-      <c r="Z38" s="51"/>
-      <c r="AA38" s="51"/>
-      <c r="AB38" s="51"/>
-      <c r="AC38" s="51"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="53"/>
-      <c r="AF38" s="53"/>
-      <c r="AG38" s="53"/>
-      <c r="AH38" s="53"/>
-      <c r="AI38" s="54"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="80"/>
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+      <c r="R38" s="80"/>
+      <c r="S38" s="80"/>
+      <c r="T38" s="80"/>
+      <c r="U38" s="80"/>
+      <c r="V38" s="80"/>
+      <c r="W38" s="80"/>
+      <c r="X38" s="80"/>
+      <c r="Y38" s="80"/>
+      <c r="Z38" s="80"/>
+      <c r="AA38" s="80"/>
+      <c r="AB38" s="80"/>
+      <c r="AC38" s="80"/>
+      <c r="AD38" s="81"/>
+      <c r="AE38" s="82"/>
+      <c r="AF38" s="82"/>
+      <c r="AG38" s="82"/>
+      <c r="AH38" s="82"/>
+      <c r="AI38" s="83"/>
       <c r="AJ38" s="8"/>
     </row>
     <row r="39" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3520,38 +3519,38 @@
       <c r="C39" s="18">
         <v>14</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="51"/>
-      <c r="V39" s="51"/>
-      <c r="W39" s="51"/>
-      <c r="X39" s="51"/>
-      <c r="Y39" s="51"/>
-      <c r="Z39" s="51"/>
-      <c r="AA39" s="51"/>
-      <c r="AB39" s="51"/>
-      <c r="AC39" s="51"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="54"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+      <c r="J39" s="80"/>
+      <c r="K39" s="80"/>
+      <c r="L39" s="80"/>
+      <c r="M39" s="80"/>
+      <c r="N39" s="80"/>
+      <c r="O39" s="80"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="80"/>
+      <c r="U39" s="80"/>
+      <c r="V39" s="80"/>
+      <c r="W39" s="80"/>
+      <c r="X39" s="80"/>
+      <c r="Y39" s="80"/>
+      <c r="Z39" s="80"/>
+      <c r="AA39" s="80"/>
+      <c r="AB39" s="80"/>
+      <c r="AC39" s="80"/>
+      <c r="AD39" s="81"/>
+      <c r="AE39" s="82"/>
+      <c r="AF39" s="82"/>
+      <c r="AG39" s="82"/>
+      <c r="AH39" s="82"/>
+      <c r="AI39" s="83"/>
       <c r="AJ39" s="8"/>
     </row>
     <row r="40" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3559,373 +3558,373 @@
       <c r="C40" s="18">
         <v>15</v>
       </c>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="51"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="51"/>
-      <c r="X40" s="51"/>
-      <c r="Y40" s="51"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="51"/>
-      <c r="AB40" s="51"/>
-      <c r="AC40" s="51"/>
-      <c r="AD40" s="52"/>
-      <c r="AE40" s="53"/>
-      <c r="AF40" s="53"/>
-      <c r="AG40" s="53"/>
-      <c r="AH40" s="53"/>
-      <c r="AI40" s="54"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+      <c r="J40" s="80"/>
+      <c r="K40" s="80"/>
+      <c r="L40" s="80"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="80"/>
+      <c r="O40" s="80"/>
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80"/>
+      <c r="R40" s="80"/>
+      <c r="S40" s="80"/>
+      <c r="T40" s="80"/>
+      <c r="U40" s="80"/>
+      <c r="V40" s="80"/>
+      <c r="W40" s="80"/>
+      <c r="X40" s="80"/>
+      <c r="Y40" s="80"/>
+      <c r="Z40" s="80"/>
+      <c r="AA40" s="80"/>
+      <c r="AB40" s="80"/>
+      <c r="AC40" s="80"/>
+      <c r="AD40" s="81"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="82"/>
+      <c r="AG40" s="82"/>
+      <c r="AH40" s="82"/>
+      <c r="AI40" s="83"/>
       <c r="AJ40" s="8"/>
     </row>
     <row r="41" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="17"/>
-      <c r="C41" s="55" t="s">
+      <c r="C41" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="55"/>
-      <c r="T41" s="55"/>
-      <c r="U41" s="55"/>
-      <c r="V41" s="55"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="55"/>
-      <c r="Y41" s="55"/>
-      <c r="Z41" s="55"/>
-      <c r="AA41" s="55"/>
-      <c r="AB41" s="55"/>
-      <c r="AC41" s="55"/>
-      <c r="AD41" s="55"/>
-      <c r="AE41" s="55"/>
-      <c r="AF41" s="55"/>
-      <c r="AG41" s="55"/>
-      <c r="AH41" s="55"/>
-      <c r="AI41" s="55"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="84"/>
+      <c r="K41" s="84"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="84"/>
+      <c r="N41" s="84"/>
+      <c r="O41" s="84"/>
+      <c r="P41" s="84"/>
+      <c r="Q41" s="84"/>
+      <c r="R41" s="84"/>
+      <c r="S41" s="84"/>
+      <c r="T41" s="84"/>
+      <c r="U41" s="84"/>
+      <c r="V41" s="84"/>
+      <c r="W41" s="84"/>
+      <c r="X41" s="84"/>
+      <c r="Y41" s="84"/>
+      <c r="Z41" s="84"/>
+      <c r="AA41" s="84"/>
+      <c r="AB41" s="84"/>
+      <c r="AC41" s="84"/>
+      <c r="AD41" s="84"/>
+      <c r="AE41" s="84"/>
+      <c r="AF41" s="84"/>
+      <c r="AG41" s="84"/>
+      <c r="AH41" s="84"/>
+      <c r="AI41" s="84"/>
       <c r="AJ41" s="8"/>
     </row>
     <row r="42" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="17"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="55"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="55"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="55"/>
-      <c r="N42" s="55"/>
-      <c r="O42" s="55"/>
-      <c r="P42" s="55"/>
-      <c r="Q42" s="55"/>
-      <c r="R42" s="55"/>
-      <c r="S42" s="55"/>
-      <c r="T42" s="55"/>
-      <c r="U42" s="55"/>
-      <c r="V42" s="55"/>
-      <c r="W42" s="55"/>
-      <c r="X42" s="55"/>
-      <c r="Y42" s="55"/>
-      <c r="Z42" s="55"/>
-      <c r="AA42" s="55"/>
-      <c r="AB42" s="55"/>
-      <c r="AC42" s="55"/>
-      <c r="AD42" s="55"/>
-      <c r="AE42" s="55"/>
-      <c r="AF42" s="55"/>
-      <c r="AG42" s="55"/>
-      <c r="AH42" s="55"/>
-      <c r="AI42" s="55"/>
+      <c r="C42" s="84"/>
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="84"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+      <c r="O42" s="84"/>
+      <c r="P42" s="84"/>
+      <c r="Q42" s="84"/>
+      <c r="R42" s="84"/>
+      <c r="S42" s="84"/>
+      <c r="T42" s="84"/>
+      <c r="U42" s="84"/>
+      <c r="V42" s="84"/>
+      <c r="W42" s="84"/>
+      <c r="X42" s="84"/>
+      <c r="Y42" s="84"/>
+      <c r="Z42" s="84"/>
+      <c r="AA42" s="84"/>
+      <c r="AB42" s="84"/>
+      <c r="AC42" s="84"/>
+      <c r="AD42" s="84"/>
+      <c r="AE42" s="84"/>
+      <c r="AF42" s="84"/>
+      <c r="AG42" s="84"/>
+      <c r="AH42" s="84"/>
+      <c r="AI42" s="84"/>
       <c r="AJ42" s="8"/>
     </row>
     <row r="43" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="17"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="55"/>
-      <c r="P43" s="55"/>
-      <c r="Q43" s="55"/>
-      <c r="R43" s="55"/>
-      <c r="S43" s="55"/>
-      <c r="T43" s="55"/>
-      <c r="U43" s="55"/>
-      <c r="V43" s="55"/>
-      <c r="W43" s="55"/>
-      <c r="X43" s="55"/>
-      <c r="Y43" s="55"/>
-      <c r="Z43" s="55"/>
-      <c r="AA43" s="55"/>
-      <c r="AB43" s="55"/>
-      <c r="AC43" s="55"/>
-      <c r="AD43" s="55"/>
-      <c r="AE43" s="55"/>
-      <c r="AF43" s="55"/>
-      <c r="AG43" s="55"/>
-      <c r="AH43" s="55"/>
-      <c r="AI43" s="55"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="84"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="84"/>
+      <c r="R43" s="84"/>
+      <c r="S43" s="84"/>
+      <c r="T43" s="84"/>
+      <c r="U43" s="84"/>
+      <c r="V43" s="84"/>
+      <c r="W43" s="84"/>
+      <c r="X43" s="84"/>
+      <c r="Y43" s="84"/>
+      <c r="Z43" s="84"/>
+      <c r="AA43" s="84"/>
+      <c r="AB43" s="84"/>
+      <c r="AC43" s="84"/>
+      <c r="AD43" s="84"/>
+      <c r="AE43" s="84"/>
+      <c r="AF43" s="84"/>
+      <c r="AG43" s="84"/>
+      <c r="AH43" s="84"/>
+      <c r="AI43" s="84"/>
       <c r="AJ43" s="8"/>
     </row>
     <row r="44" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="17"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="55"/>
-      <c r="J44" s="55"/>
-      <c r="K44" s="55"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="55"/>
-      <c r="N44" s="55"/>
-      <c r="O44" s="55"/>
-      <c r="P44" s="55"/>
-      <c r="Q44" s="55"/>
-      <c r="R44" s="55"/>
-      <c r="S44" s="55"/>
-      <c r="T44" s="55"/>
-      <c r="U44" s="55"/>
-      <c r="V44" s="55"/>
-      <c r="W44" s="55"/>
-      <c r="X44" s="55"/>
-      <c r="Y44" s="55"/>
-      <c r="Z44" s="55"/>
-      <c r="AA44" s="55"/>
-      <c r="AB44" s="55"/>
-      <c r="AC44" s="55"/>
-      <c r="AD44" s="55"/>
-      <c r="AE44" s="55"/>
-      <c r="AF44" s="55"/>
-      <c r="AG44" s="55"/>
-      <c r="AH44" s="55"/>
-      <c r="AI44" s="55"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84"/>
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="84"/>
+      <c r="K44" s="84"/>
+      <c r="L44" s="84"/>
+      <c r="M44" s="84"/>
+      <c r="N44" s="84"/>
+      <c r="O44" s="84"/>
+      <c r="P44" s="84"/>
+      <c r="Q44" s="84"/>
+      <c r="R44" s="84"/>
+      <c r="S44" s="84"/>
+      <c r="T44" s="84"/>
+      <c r="U44" s="84"/>
+      <c r="V44" s="84"/>
+      <c r="W44" s="84"/>
+      <c r="X44" s="84"/>
+      <c r="Y44" s="84"/>
+      <c r="Z44" s="84"/>
+      <c r="AA44" s="84"/>
+      <c r="AB44" s="84"/>
+      <c r="AC44" s="84"/>
+      <c r="AD44" s="84"/>
+      <c r="AE44" s="84"/>
+      <c r="AF44" s="84"/>
+      <c r="AG44" s="84"/>
+      <c r="AH44" s="84"/>
+      <c r="AI44" s="84"/>
       <c r="AJ44" s="8"/>
     </row>
     <row r="45" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="17"/>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
-      <c r="Q45" s="55"/>
-      <c r="R45" s="55"/>
-      <c r="S45" s="55"/>
-      <c r="T45" s="55"/>
-      <c r="U45" s="55"/>
-      <c r="V45" s="55"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="55"/>
-      <c r="Y45" s="55"/>
-      <c r="Z45" s="55"/>
-      <c r="AA45" s="55"/>
-      <c r="AB45" s="55"/>
-      <c r="AC45" s="55"/>
-      <c r="AD45" s="55"/>
-      <c r="AE45" s="55"/>
-      <c r="AF45" s="55"/>
-      <c r="AG45" s="55"/>
-      <c r="AH45" s="55"/>
-      <c r="AI45" s="55"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="84"/>
+      <c r="O45" s="84"/>
+      <c r="P45" s="84"/>
+      <c r="Q45" s="84"/>
+      <c r="R45" s="84"/>
+      <c r="S45" s="84"/>
+      <c r="T45" s="84"/>
+      <c r="U45" s="84"/>
+      <c r="V45" s="84"/>
+      <c r="W45" s="84"/>
+      <c r="X45" s="84"/>
+      <c r="Y45" s="84"/>
+      <c r="Z45" s="84"/>
+      <c r="AA45" s="84"/>
+      <c r="AB45" s="84"/>
+      <c r="AC45" s="84"/>
+      <c r="AD45" s="84"/>
+      <c r="AE45" s="84"/>
+      <c r="AF45" s="84"/>
+      <c r="AG45" s="84"/>
+      <c r="AH45" s="84"/>
+      <c r="AI45" s="84"/>
       <c r="AJ45" s="8"/>
     </row>
     <row r="46" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="17"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="55"/>
-      <c r="E46" s="55"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="55"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="55"/>
-      <c r="J46" s="55"/>
-      <c r="K46" s="55"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="55"/>
-      <c r="N46" s="55"/>
-      <c r="O46" s="55"/>
-      <c r="P46" s="55"/>
-      <c r="Q46" s="55"/>
-      <c r="R46" s="55"/>
-      <c r="S46" s="55"/>
-      <c r="T46" s="55"/>
-      <c r="U46" s="55"/>
-      <c r="V46" s="55"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="55"/>
-      <c r="Y46" s="55"/>
-      <c r="Z46" s="55"/>
-      <c r="AA46" s="55"/>
-      <c r="AB46" s="55"/>
-      <c r="AC46" s="55"/>
-      <c r="AD46" s="55"/>
-      <c r="AE46" s="55"/>
-      <c r="AF46" s="55"/>
-      <c r="AG46" s="55"/>
-      <c r="AH46" s="55"/>
-      <c r="AI46" s="55"/>
+      <c r="C46" s="84"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="84"/>
+      <c r="F46" s="84"/>
+      <c r="G46" s="84"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="84"/>
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="84"/>
+      <c r="O46" s="84"/>
+      <c r="P46" s="84"/>
+      <c r="Q46" s="84"/>
+      <c r="R46" s="84"/>
+      <c r="S46" s="84"/>
+      <c r="T46" s="84"/>
+      <c r="U46" s="84"/>
+      <c r="V46" s="84"/>
+      <c r="W46" s="84"/>
+      <c r="X46" s="84"/>
+      <c r="Y46" s="84"/>
+      <c r="Z46" s="84"/>
+      <c r="AA46" s="84"/>
+      <c r="AB46" s="84"/>
+      <c r="AC46" s="84"/>
+      <c r="AD46" s="84"/>
+      <c r="AE46" s="84"/>
+      <c r="AF46" s="84"/>
+      <c r="AG46" s="84"/>
+      <c r="AH46" s="84"/>
+      <c r="AI46" s="84"/>
       <c r="AJ46" s="8"/>
     </row>
     <row r="47" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="17"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="55"/>
-      <c r="E47" s="55"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="55"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="55"/>
-      <c r="J47" s="55"/>
-      <c r="K47" s="55"/>
-      <c r="L47" s="55"/>
-      <c r="M47" s="55"/>
-      <c r="N47" s="55"/>
-      <c r="O47" s="55"/>
-      <c r="P47" s="55"/>
-      <c r="Q47" s="55"/>
-      <c r="R47" s="55"/>
-      <c r="S47" s="55"/>
-      <c r="T47" s="55"/>
-      <c r="U47" s="55"/>
-      <c r="V47" s="55"/>
-      <c r="W47" s="55"/>
-      <c r="X47" s="55"/>
-      <c r="Y47" s="55"/>
-      <c r="Z47" s="55"/>
-      <c r="AA47" s="55"/>
-      <c r="AB47" s="55"/>
-      <c r="AC47" s="55"/>
-      <c r="AD47" s="55"/>
-      <c r="AE47" s="55"/>
-      <c r="AF47" s="55"/>
-      <c r="AG47" s="55"/>
-      <c r="AH47" s="55"/>
-      <c r="AI47" s="55"/>
+      <c r="C47" s="84"/>
+      <c r="D47" s="84"/>
+      <c r="E47" s="84"/>
+      <c r="F47" s="84"/>
+      <c r="G47" s="84"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="84"/>
+      <c r="J47" s="84"/>
+      <c r="K47" s="84"/>
+      <c r="L47" s="84"/>
+      <c r="M47" s="84"/>
+      <c r="N47" s="84"/>
+      <c r="O47" s="84"/>
+      <c r="P47" s="84"/>
+      <c r="Q47" s="84"/>
+      <c r="R47" s="84"/>
+      <c r="S47" s="84"/>
+      <c r="T47" s="84"/>
+      <c r="U47" s="84"/>
+      <c r="V47" s="84"/>
+      <c r="W47" s="84"/>
+      <c r="X47" s="84"/>
+      <c r="Y47" s="84"/>
+      <c r="Z47" s="84"/>
+      <c r="AA47" s="84"/>
+      <c r="AB47" s="84"/>
+      <c r="AC47" s="84"/>
+      <c r="AD47" s="84"/>
+      <c r="AE47" s="84"/>
+      <c r="AF47" s="84"/>
+      <c r="AG47" s="84"/>
+      <c r="AH47" s="84"/>
+      <c r="AI47" s="84"/>
       <c r="AJ47" s="8"/>
     </row>
     <row r="48" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="17"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="55"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="55"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="55"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="55"/>
-      <c r="N48" s="55"/>
-      <c r="O48" s="55"/>
-      <c r="P48" s="55"/>
-      <c r="Q48" s="55"/>
-      <c r="R48" s="55"/>
-      <c r="S48" s="55"/>
-      <c r="T48" s="55"/>
-      <c r="U48" s="55"/>
-      <c r="V48" s="55"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
-      <c r="AB48" s="55"/>
-      <c r="AC48" s="55"/>
-      <c r="AD48" s="55"/>
-      <c r="AE48" s="55"/>
-      <c r="AF48" s="55"/>
-      <c r="AG48" s="55"/>
-      <c r="AH48" s="55"/>
-      <c r="AI48" s="55"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="84"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="84"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
+      <c r="M48" s="84"/>
+      <c r="N48" s="84"/>
+      <c r="O48" s="84"/>
+      <c r="P48" s="84"/>
+      <c r="Q48" s="84"/>
+      <c r="R48" s="84"/>
+      <c r="S48" s="84"/>
+      <c r="T48" s="84"/>
+      <c r="U48" s="84"/>
+      <c r="V48" s="84"/>
+      <c r="W48" s="84"/>
+      <c r="X48" s="84"/>
+      <c r="Y48" s="84"/>
+      <c r="Z48" s="84"/>
+      <c r="AA48" s="84"/>
+      <c r="AB48" s="84"/>
+      <c r="AC48" s="84"/>
+      <c r="AD48" s="84"/>
+      <c r="AE48" s="84"/>
+      <c r="AF48" s="84"/>
+      <c r="AG48" s="84"/>
+      <c r="AH48" s="84"/>
+      <c r="AI48" s="84"/>
       <c r="AJ48" s="8"/>
     </row>
     <row r="49" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="17"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="55"/>
-      <c r="N49" s="55"/>
-      <c r="O49" s="55"/>
-      <c r="P49" s="55"/>
-      <c r="Q49" s="55"/>
-      <c r="R49" s="55"/>
-      <c r="S49" s="55"/>
-      <c r="T49" s="55"/>
-      <c r="U49" s="55"/>
-      <c r="V49" s="55"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="55"/>
-      <c r="Y49" s="55"/>
-      <c r="Z49" s="55"/>
-      <c r="AA49" s="55"/>
-      <c r="AB49" s="55"/>
-      <c r="AC49" s="55"/>
-      <c r="AD49" s="55"/>
-      <c r="AE49" s="55"/>
-      <c r="AF49" s="55"/>
-      <c r="AG49" s="55"/>
-      <c r="AH49" s="55"/>
-      <c r="AI49" s="55"/>
+      <c r="C49" s="84"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="84"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="84"/>
+      <c r="Q49" s="84"/>
+      <c r="R49" s="84"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="84"/>
+      <c r="U49" s="84"/>
+      <c r="V49" s="84"/>
+      <c r="W49" s="84"/>
+      <c r="X49" s="84"/>
+      <c r="Y49" s="84"/>
+      <c r="Z49" s="84"/>
+      <c r="AA49" s="84"/>
+      <c r="AB49" s="84"/>
+      <c r="AC49" s="84"/>
+      <c r="AD49" s="84"/>
+      <c r="AE49" s="84"/>
+      <c r="AF49" s="84"/>
+      <c r="AG49" s="84"/>
+      <c r="AH49" s="84"/>
+      <c r="AI49" s="84"/>
       <c r="AJ49" s="8"/>
     </row>
     <row r="50" spans="2:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3965,13 +3964,13 @@
     </row>
     <row r="51" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B51" s="17"/>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
+      <c r="D51" s="85"/>
+      <c r="E51" s="85"/>
+      <c r="F51" s="85"/>
+      <c r="G51" s="85"/>
       <c r="AJ51" s="8"/>
     </row>
     <row r="52" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
@@ -4036,345 +4035,345 @@
     </row>
     <row r="60" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="17"/>
-      <c r="H60" s="57" t="s">
+      <c r="H60" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="I60" s="58"/>
-      <c r="J60" s="58"/>
-      <c r="K60" s="58"/>
-      <c r="L60" s="58"/>
-      <c r="M60" s="58"/>
-      <c r="N60" s="58"/>
-      <c r="O60" s="58"/>
-      <c r="P60" s="58"/>
-      <c r="Q60" s="58"/>
-      <c r="R60" s="58"/>
-      <c r="S60" s="58"/>
-      <c r="T60" s="58"/>
-      <c r="U60" s="58"/>
-      <c r="V60" s="58"/>
-      <c r="W60" s="58"/>
-      <c r="X60" s="58"/>
-      <c r="Y60" s="58"/>
-      <c r="Z60" s="58"/>
-      <c r="AA60" s="58"/>
-      <c r="AB60" s="58"/>
-      <c r="AC60" s="58"/>
-      <c r="AD60" s="58"/>
+      <c r="I60" s="87"/>
+      <c r="J60" s="87"/>
+      <c r="K60" s="87"/>
+      <c r="L60" s="87"/>
+      <c r="M60" s="87"/>
+      <c r="N60" s="87"/>
+      <c r="O60" s="87"/>
+      <c r="P60" s="87"/>
+      <c r="Q60" s="87"/>
+      <c r="R60" s="87"/>
+      <c r="S60" s="87"/>
+      <c r="T60" s="87"/>
+      <c r="U60" s="87"/>
+      <c r="V60" s="87"/>
+      <c r="W60" s="87"/>
+      <c r="X60" s="87"/>
+      <c r="Y60" s="87"/>
+      <c r="Z60" s="87"/>
+      <c r="AA60" s="87"/>
+      <c r="AB60" s="87"/>
+      <c r="AC60" s="87"/>
+      <c r="AD60" s="87"/>
       <c r="AJ60" s="8"/>
     </row>
     <row r="61" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B61" s="17"/>
-      <c r="H61" s="59" t="s">
+      <c r="H61" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="I61" s="59"/>
-      <c r="J61" s="59"/>
-      <c r="K61" s="59"/>
-      <c r="L61" s="59"/>
-      <c r="M61" s="59"/>
-      <c r="N61" s="59"/>
-      <c r="O61" s="59"/>
-      <c r="P61" s="59"/>
-      <c r="Q61" s="59"/>
-      <c r="R61" s="59"/>
-      <c r="S61" s="59"/>
-      <c r="T61" s="59"/>
-      <c r="U61" s="59"/>
-      <c r="V61" s="59"/>
-      <c r="W61" s="59"/>
-      <c r="X61" s="59"/>
-      <c r="Y61" s="59"/>
-      <c r="Z61" s="59"/>
-      <c r="AA61" s="59"/>
-      <c r="AB61" s="59"/>
-      <c r="AC61" s="59"/>
-      <c r="AD61" s="59"/>
+      <c r="I61" s="88"/>
+      <c r="J61" s="88"/>
+      <c r="K61" s="88"/>
+      <c r="L61" s="88"/>
+      <c r="M61" s="88"/>
+      <c r="N61" s="88"/>
+      <c r="O61" s="88"/>
+      <c r="P61" s="88"/>
+      <c r="Q61" s="88"/>
+      <c r="R61" s="88"/>
+      <c r="S61" s="88"/>
+      <c r="T61" s="88"/>
+      <c r="U61" s="88"/>
+      <c r="V61" s="88"/>
+      <c r="W61" s="88"/>
+      <c r="X61" s="88"/>
+      <c r="Y61" s="88"/>
+      <c r="Z61" s="88"/>
+      <c r="AA61" s="88"/>
+      <c r="AB61" s="88"/>
+      <c r="AC61" s="88"/>
+      <c r="AD61" s="88"/>
       <c r="AJ61" s="8"/>
     </row>
     <row r="62" spans="2:36" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="17"/>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="38" t="s">
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
+      <c r="H62" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="38"/>
-      <c r="M62" s="39" t="s">
+      <c r="I62" s="90"/>
+      <c r="J62" s="90"/>
+      <c r="K62" s="90"/>
+      <c r="L62" s="90"/>
+      <c r="M62" s="91" t="s">
         <v>43</v>
       </c>
-      <c r="N62" s="40"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="40"/>
-      <c r="Q62" s="40"/>
-      <c r="R62" s="41"/>
-      <c r="S62" s="38" t="s">
+      <c r="N62" s="92"/>
+      <c r="O62" s="92"/>
+      <c r="P62" s="92"/>
+      <c r="Q62" s="92"/>
+      <c r="R62" s="93"/>
+      <c r="S62" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="T62" s="38"/>
-      <c r="U62" s="38"/>
-      <c r="V62" s="38"/>
-      <c r="W62" s="38"/>
-      <c r="X62" s="42"/>
-      <c r="Y62" s="43"/>
-      <c r="Z62" s="43"/>
-      <c r="AA62" s="43"/>
-      <c r="AB62" s="43"/>
-      <c r="AC62" s="43"/>
-      <c r="AD62" s="43"/>
-      <c r="AE62" s="43"/>
-      <c r="AF62" s="43"/>
-      <c r="AG62" s="43"/>
-      <c r="AH62" s="43"/>
-      <c r="AI62" s="44"/>
+      <c r="T62" s="90"/>
+      <c r="U62" s="90"/>
+      <c r="V62" s="90"/>
+      <c r="W62" s="90"/>
+      <c r="X62" s="94"/>
+      <c r="Y62" s="95"/>
+      <c r="Z62" s="95"/>
+      <c r="AA62" s="95"/>
+      <c r="AB62" s="95"/>
+      <c r="AC62" s="95"/>
+      <c r="AD62" s="95"/>
+      <c r="AE62" s="95"/>
+      <c r="AF62" s="95"/>
+      <c r="AG62" s="95"/>
+      <c r="AH62" s="95"/>
+      <c r="AI62" s="96"/>
       <c r="AJ62" s="8"/>
     </row>
     <row r="63" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B63" s="17"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="45"/>
-      <c r="K63" s="45"/>
-      <c r="L63" s="45"/>
-      <c r="M63" s="46"/>
-      <c r="N63" s="47"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="47"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="48"/>
-      <c r="S63" s="45"/>
-      <c r="T63" s="45"/>
-      <c r="U63" s="45"/>
-      <c r="V63" s="45"/>
-      <c r="W63" s="45"/>
-      <c r="X63" s="49" t="s">
+      <c r="C63" s="97"/>
+      <c r="D63" s="97"/>
+      <c r="E63" s="97"/>
+      <c r="F63" s="97"/>
+      <c r="G63" s="97"/>
+      <c r="H63" s="97"/>
+      <c r="I63" s="97"/>
+      <c r="J63" s="97"/>
+      <c r="K63" s="97"/>
+      <c r="L63" s="97"/>
+      <c r="M63" s="98"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="30"/>
+      <c r="P63" s="30"/>
+      <c r="Q63" s="30"/>
+      <c r="R63" s="31"/>
+      <c r="S63" s="97"/>
+      <c r="T63" s="97"/>
+      <c r="U63" s="97"/>
+      <c r="V63" s="97"/>
+      <c r="W63" s="97"/>
+      <c r="X63" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
-      <c r="AA63" s="50"/>
-      <c r="AB63" s="50"/>
-      <c r="AC63" s="50"/>
-      <c r="AD63" s="50"/>
-      <c r="AE63" s="50"/>
-      <c r="AF63" s="50"/>
-      <c r="AG63" s="50"/>
-      <c r="AH63" s="50"/>
-      <c r="AI63" s="50"/>
+      <c r="Y63" s="100"/>
+      <c r="Z63" s="100"/>
+      <c r="AA63" s="100"/>
+      <c r="AB63" s="100"/>
+      <c r="AC63" s="100"/>
+      <c r="AD63" s="100"/>
+      <c r="AE63" s="100"/>
+      <c r="AF63" s="100"/>
+      <c r="AG63" s="100"/>
+      <c r="AH63" s="100"/>
+      <c r="AI63" s="100"/>
       <c r="AJ63" s="8"/>
     </row>
     <row r="64" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B64" s="17"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45"/>
-      <c r="J64" s="45"/>
-      <c r="K64" s="45"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="46"/>
-      <c r="N64" s="47"/>
-      <c r="O64" s="47"/>
-      <c r="P64" s="47"/>
-      <c r="Q64" s="47"/>
-      <c r="R64" s="48"/>
-      <c r="S64" s="45"/>
-      <c r="T64" s="45"/>
-      <c r="U64" s="45"/>
-      <c r="V64" s="45"/>
-      <c r="W64" s="45"/>
-      <c r="X64" s="50"/>
-      <c r="Y64" s="50"/>
-      <c r="Z64" s="50"/>
-      <c r="AA64" s="50"/>
-      <c r="AB64" s="50"/>
-      <c r="AC64" s="50"/>
-      <c r="AD64" s="50"/>
-      <c r="AE64" s="50"/>
-      <c r="AF64" s="50"/>
-      <c r="AG64" s="50"/>
-      <c r="AH64" s="50"/>
-      <c r="AI64" s="50"/>
+      <c r="C64" s="97"/>
+      <c r="D64" s="97"/>
+      <c r="E64" s="97"/>
+      <c r="F64" s="97"/>
+      <c r="G64" s="97"/>
+      <c r="H64" s="97"/>
+      <c r="I64" s="97"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="97"/>
+      <c r="L64" s="97"/>
+      <c r="M64" s="98"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="97"/>
+      <c r="T64" s="97"/>
+      <c r="U64" s="97"/>
+      <c r="V64" s="97"/>
+      <c r="W64" s="97"/>
+      <c r="X64" s="100"/>
+      <c r="Y64" s="100"/>
+      <c r="Z64" s="100"/>
+      <c r="AA64" s="100"/>
+      <c r="AB64" s="100"/>
+      <c r="AC64" s="100"/>
+      <c r="AD64" s="100"/>
+      <c r="AE64" s="100"/>
+      <c r="AF64" s="100"/>
+      <c r="AG64" s="100"/>
+      <c r="AH64" s="100"/>
+      <c r="AI64" s="100"/>
       <c r="AJ64" s="8"/>
     </row>
     <row r="65" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B65" s="17"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="45"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="46"/>
-      <c r="N65" s="47"/>
-      <c r="O65" s="47"/>
-      <c r="P65" s="47"/>
-      <c r="Q65" s="47"/>
-      <c r="R65" s="48"/>
-      <c r="S65" s="45"/>
-      <c r="T65" s="45"/>
-      <c r="U65" s="45"/>
-      <c r="V65" s="45"/>
-      <c r="W65" s="45"/>
-      <c r="X65" s="50"/>
-      <c r="Y65" s="50"/>
-      <c r="Z65" s="50"/>
-      <c r="AA65" s="50"/>
-      <c r="AB65" s="50"/>
-      <c r="AC65" s="50"/>
-      <c r="AD65" s="50"/>
-      <c r="AE65" s="50"/>
-      <c r="AF65" s="50"/>
-      <c r="AG65" s="50"/>
-      <c r="AH65" s="50"/>
-      <c r="AI65" s="50"/>
+      <c r="C65" s="97"/>
+      <c r="D65" s="97"/>
+      <c r="E65" s="97"/>
+      <c r="F65" s="97"/>
+      <c r="G65" s="97"/>
+      <c r="H65" s="97"/>
+      <c r="I65" s="97"/>
+      <c r="J65" s="97"/>
+      <c r="K65" s="97"/>
+      <c r="L65" s="97"/>
+      <c r="M65" s="98"/>
+      <c r="N65" s="30"/>
+      <c r="O65" s="30"/>
+      <c r="P65" s="30"/>
+      <c r="Q65" s="30"/>
+      <c r="R65" s="31"/>
+      <c r="S65" s="97"/>
+      <c r="T65" s="97"/>
+      <c r="U65" s="97"/>
+      <c r="V65" s="97"/>
+      <c r="W65" s="97"/>
+      <c r="X65" s="100"/>
+      <c r="Y65" s="100"/>
+      <c r="Z65" s="100"/>
+      <c r="AA65" s="100"/>
+      <c r="AB65" s="100"/>
+      <c r="AC65" s="100"/>
+      <c r="AD65" s="100"/>
+      <c r="AE65" s="100"/>
+      <c r="AF65" s="100"/>
+      <c r="AG65" s="100"/>
+      <c r="AH65" s="100"/>
+      <c r="AI65" s="100"/>
       <c r="AJ65" s="8"/>
     </row>
     <row r="66" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B66" s="17"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="45"/>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45"/>
-      <c r="J66" s="45"/>
-      <c r="K66" s="45"/>
-      <c r="L66" s="45"/>
-      <c r="M66" s="46"/>
-      <c r="N66" s="47"/>
-      <c r="O66" s="47"/>
-      <c r="P66" s="47"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="48"/>
-      <c r="S66" s="45"/>
-      <c r="T66" s="45"/>
-      <c r="U66" s="45"/>
-      <c r="V66" s="45"/>
-      <c r="W66" s="45"/>
-      <c r="X66" s="50"/>
-      <c r="Y66" s="50"/>
-      <c r="Z66" s="50"/>
-      <c r="AA66" s="50"/>
-      <c r="AB66" s="50"/>
-      <c r="AC66" s="50"/>
-      <c r="AD66" s="50"/>
-      <c r="AE66" s="50"/>
-      <c r="AF66" s="50"/>
-      <c r="AG66" s="50"/>
-      <c r="AH66" s="50"/>
-      <c r="AI66" s="50"/>
+      <c r="C66" s="97"/>
+      <c r="D66" s="97"/>
+      <c r="E66" s="97"/>
+      <c r="F66" s="97"/>
+      <c r="G66" s="97"/>
+      <c r="H66" s="97"/>
+      <c r="I66" s="97"/>
+      <c r="J66" s="97"/>
+      <c r="K66" s="97"/>
+      <c r="L66" s="97"/>
+      <c r="M66" s="98"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="30"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="30"/>
+      <c r="R66" s="31"/>
+      <c r="S66" s="97"/>
+      <c r="T66" s="97"/>
+      <c r="U66" s="97"/>
+      <c r="V66" s="97"/>
+      <c r="W66" s="97"/>
+      <c r="X66" s="100"/>
+      <c r="Y66" s="100"/>
+      <c r="Z66" s="100"/>
+      <c r="AA66" s="100"/>
+      <c r="AB66" s="100"/>
+      <c r="AC66" s="100"/>
+      <c r="AD66" s="100"/>
+      <c r="AE66" s="100"/>
+      <c r="AF66" s="100"/>
+      <c r="AG66" s="100"/>
+      <c r="AH66" s="100"/>
+      <c r="AI66" s="100"/>
       <c r="AJ66" s="8"/>
     </row>
     <row r="67" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B67" s="17"/>
-      <c r="C67" s="27" t="s">
+      <c r="C67" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27" t="s">
+      <c r="D67" s="102"/>
+      <c r="E67" s="102"/>
+      <c r="F67" s="102"/>
+      <c r="G67" s="102"/>
+      <c r="H67" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="28" t="s">
+      <c r="I67" s="102"/>
+      <c r="J67" s="102"/>
+      <c r="K67" s="102"/>
+      <c r="L67" s="102"/>
+      <c r="M67" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="31" t="s">
+      <c r="N67" s="104"/>
+      <c r="O67" s="104"/>
+      <c r="P67" s="104"/>
+      <c r="Q67" s="104"/>
+      <c r="R67" s="105"/>
+      <c r="S67" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
-      <c r="X67" s="50"/>
-      <c r="Y67" s="50"/>
-      <c r="Z67" s="50"/>
-      <c r="AA67" s="50"/>
-      <c r="AB67" s="50"/>
-      <c r="AC67" s="50"/>
-      <c r="AD67" s="50"/>
-      <c r="AE67" s="50"/>
-      <c r="AF67" s="50"/>
-      <c r="AG67" s="50"/>
-      <c r="AH67" s="50"/>
-      <c r="AI67" s="50"/>
+      <c r="T67" s="54"/>
+      <c r="U67" s="54"/>
+      <c r="V67" s="54"/>
+      <c r="W67" s="54"/>
+      <c r="X67" s="100"/>
+      <c r="Y67" s="100"/>
+      <c r="Z67" s="100"/>
+      <c r="AA67" s="100"/>
+      <c r="AB67" s="100"/>
+      <c r="AC67" s="100"/>
+      <c r="AD67" s="100"/>
+      <c r="AE67" s="100"/>
+      <c r="AF67" s="100"/>
+      <c r="AG67" s="100"/>
+      <c r="AH67" s="100"/>
+      <c r="AI67" s="100"/>
       <c r="AJ67" s="8"/>
     </row>
     <row r="68" spans="2:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="17"/>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="33" t="s">
+      <c r="D68" s="73"/>
+      <c r="E68" s="73"/>
+      <c r="F68" s="73"/>
+      <c r="G68" s="73"/>
+      <c r="H68" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="I68" s="33"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="33"/>
-      <c r="L68" s="33"/>
-      <c r="M68" s="34" t="s">
+      <c r="I68" s="55"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+      <c r="L68" s="55"/>
+      <c r="M68" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="N68" s="35"/>
-      <c r="O68" s="35"/>
-      <c r="P68" s="35"/>
-      <c r="Q68" s="35"/>
-      <c r="R68" s="36"/>
-      <c r="S68" s="32" t="s">
+      <c r="N68" s="71"/>
+      <c r="O68" s="71"/>
+      <c r="P68" s="71"/>
+      <c r="Q68" s="71"/>
+      <c r="R68" s="72"/>
+      <c r="S68" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="32"/>
-      <c r="W68" s="32"/>
-      <c r="X68" s="50"/>
-      <c r="Y68" s="50"/>
-      <c r="Z68" s="50"/>
-      <c r="AA68" s="50"/>
-      <c r="AB68" s="50"/>
-      <c r="AC68" s="50"/>
-      <c r="AD68" s="50"/>
-      <c r="AE68" s="50"/>
-      <c r="AF68" s="50"/>
-      <c r="AG68" s="50"/>
-      <c r="AH68" s="50"/>
-      <c r="AI68" s="50"/>
+      <c r="T68" s="73"/>
+      <c r="U68" s="73"/>
+      <c r="V68" s="73"/>
+      <c r="W68" s="73"/>
+      <c r="X68" s="100"/>
+      <c r="Y68" s="100"/>
+      <c r="Z68" s="100"/>
+      <c r="AA68" s="100"/>
+      <c r="AB68" s="100"/>
+      <c r="AC68" s="100"/>
+      <c r="AD68" s="100"/>
+      <c r="AE68" s="100"/>
+      <c r="AF68" s="100"/>
+      <c r="AG68" s="100"/>
+      <c r="AH68" s="100"/>
+      <c r="AI68" s="100"/>
       <c r="AJ68" s="8"/>
     </row>
     <row r="69" spans="2:36" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4415,38 +4414,175 @@
       <c r="AJ69" s="25"/>
     </row>
     <row r="70" spans="2:36" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="AE70" s="26" t="s">
+      <c r="AE70" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="AF70" s="26"/>
-      <c r="AG70" s="26"/>
-      <c r="AH70" s="26"/>
-      <c r="AI70" s="26"/>
-      <c r="AJ70" s="26"/>
+      <c r="AF70" s="101"/>
+      <c r="AG70" s="101"/>
+      <c r="AH70" s="101"/>
+      <c r="AI70" s="101"/>
+      <c r="AJ70" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="202">
-    <mergeCell ref="B2:G5"/>
-    <mergeCell ref="H2:AJ5"/>
-    <mergeCell ref="B6:AJ6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="AA12:AI17"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="AE70:AJ70"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M67:R67"/>
+    <mergeCell ref="S67:W67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="H68:L68"/>
+    <mergeCell ref="M68:R68"/>
+    <mergeCell ref="S68:W68"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H62:L62"/>
+    <mergeCell ref="M62:R62"/>
+    <mergeCell ref="S62:W62"/>
+    <mergeCell ref="X62:AI62"/>
+    <mergeCell ref="C63:G66"/>
+    <mergeCell ref="H63:L66"/>
+    <mergeCell ref="M63:R66"/>
+    <mergeCell ref="S63:W66"/>
+    <mergeCell ref="X63:AI68"/>
+    <mergeCell ref="AA40:AC40"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="C41:AI49"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H60:AD60"/>
+    <mergeCell ref="H61:AD61"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="AA39:AC39"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="U40:W40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="O39:Q39"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="U38:W38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="AA38:AC38"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="AA37:AC37"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="AA34:AC34"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="X33:Z33"/>
+    <mergeCell ref="AA33:AC33"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="X31:Z31"/>
+    <mergeCell ref="AA31:AC31"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AC27"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="AA28:AC28"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="AD26:AI26"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="R24:T24"/>
@@ -4470,164 +4606,27 @@
     <mergeCell ref="U25:W25"/>
     <mergeCell ref="X25:Z25"/>
     <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="AD26:AI26"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="AA28:AC28"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="X29:Z29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="X31:Z31"/>
-    <mergeCell ref="AA31:AC31"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="U31:W31"/>
-    <mergeCell ref="AA32:AC32"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="X33:Z33"/>
-    <mergeCell ref="AA33:AC33"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="X34:Z34"/>
-    <mergeCell ref="AA34:AC34"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="X35:Z35"/>
-    <mergeCell ref="AA35:AC35"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="U36:W36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="U35:W35"/>
-    <mergeCell ref="AA36:AC36"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="U37:W37"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="AA37:AC37"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="U38:W38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="AA38:AC38"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="AA40:AC40"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="C41:AI49"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H60:AD60"/>
-    <mergeCell ref="H61:AD61"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="AA39:AC39"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="U40:W40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="O39:Q39"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="U39:W39"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H62:L62"/>
-    <mergeCell ref="M62:R62"/>
-    <mergeCell ref="S62:W62"/>
-    <mergeCell ref="X62:AI62"/>
-    <mergeCell ref="C63:G66"/>
-    <mergeCell ref="H63:L66"/>
-    <mergeCell ref="M63:R66"/>
-    <mergeCell ref="S63:W66"/>
-    <mergeCell ref="X63:AI68"/>
-    <mergeCell ref="AE70:AJ70"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:L67"/>
-    <mergeCell ref="M67:R67"/>
-    <mergeCell ref="S67:W67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="H68:L68"/>
-    <mergeCell ref="M68:R68"/>
-    <mergeCell ref="S68:W68"/>
+    <mergeCell ref="B2:G5"/>
+    <mergeCell ref="H2:AJ5"/>
+    <mergeCell ref="B6:AJ6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="AA12:AI17"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="S11:Y11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.23999999999999996" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
+++ b/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B600032-21FF-47FF-857B-8FDA15275863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54A0909-951D-4DF1-853A-955D6D5604AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{D57B88DC-6A9D-42A6-BE16-0F559C48DA93}"/>
   </bookViews>
@@ -679,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -742,6 +742,186 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -754,12 +934,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -805,182 +979,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,7 +1111,7 @@
             <c:numRef>
               <c:f>Sertifikat!$L$26:$L$32</c:f>
               <c:numCache>
-                <c:formatCode>0.0_ </c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
@@ -1154,7 +1160,7 @@
             <c:numRef>
               <c:f>Sertifikat!$O$26:$O$32</c:f>
               <c:numCache>
-                <c:formatCode>0.0_ </c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
@@ -1201,7 +1207,7 @@
             <c:numRef>
               <c:f>Sertifikat!$R$26:$R$32</c:f>
               <c:numCache>
-                <c:formatCode>0.0_ </c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
@@ -1252,7 +1258,7 @@
             <c:numRef>
               <c:f>Sertifikat!$U$26:$U$32</c:f>
               <c:numCache>
-                <c:formatCode>0.0_ </c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
               </c:numCache>
             </c:numRef>
@@ -2019,201 +2025,201 @@
   <sheetData>
     <row r="1" spans="2:39" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:39" ht="19" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="35" t="s">
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="36"/>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="37"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
+      <c r="W2" s="94"/>
+      <c r="X2" s="94"/>
+      <c r="Y2" s="94"/>
+      <c r="Z2" s="94"/>
+      <c r="AA2" s="94"/>
+      <c r="AB2" s="94"/>
+      <c r="AC2" s="94"/>
+      <c r="AD2" s="94"/>
+      <c r="AE2" s="94"/>
+      <c r="AF2" s="94"/>
+      <c r="AG2" s="94"/>
+      <c r="AH2" s="94"/>
+      <c r="AI2" s="94"/>
+      <c r="AJ2" s="95"/>
     </row>
     <row r="3" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="39"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="96"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="96"/>
+      <c r="AC3" s="96"/>
+      <c r="AD3" s="96"/>
+      <c r="AE3" s="96"/>
+      <c r="AF3" s="96"/>
+      <c r="AG3" s="96"/>
+      <c r="AH3" s="96"/>
+      <c r="AI3" s="96"/>
+      <c r="AJ3" s="97"/>
     </row>
     <row r="4" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-      <c r="AC4" s="38"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="39"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="96"/>
+      <c r="W4" s="96"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="96"/>
+      <c r="AE4" s="96"/>
+      <c r="AF4" s="96"/>
+      <c r="AG4" s="96"/>
+      <c r="AH4" s="96"/>
+      <c r="AI4" s="96"/>
+      <c r="AJ4" s="97"/>
     </row>
     <row r="5" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="40"/>
-      <c r="W5" s="40"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="40"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="40"/>
-      <c r="AB5" s="40"/>
-      <c r="AC5" s="40"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="40"/>
-      <c r="AF5" s="40"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="40"/>
-      <c r="AI5" s="40"/>
-      <c r="AJ5" s="41"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="98"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="98"/>
+      <c r="T5" s="98"/>
+      <c r="U5" s="98"/>
+      <c r="V5" s="98"/>
+      <c r="W5" s="98"/>
+      <c r="X5" s="98"/>
+      <c r="Y5" s="98"/>
+      <c r="Z5" s="98"/>
+      <c r="AA5" s="98"/>
+      <c r="AB5" s="98"/>
+      <c r="AC5" s="98"/>
+      <c r="AD5" s="98"/>
+      <c r="AE5" s="98"/>
+      <c r="AF5" s="98"/>
+      <c r="AG5" s="98"/>
+      <c r="AH5" s="98"/>
+      <c r="AI5" s="98"/>
+      <c r="AJ5" s="99"/>
     </row>
     <row r="6" spans="2:39" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="42"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="100"/>
     </row>
     <row r="7" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
       <c r="H7" s="4" t="s">
         <v>2</v>
       </c>
@@ -2227,15 +2233,15 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="45" t="s">
+      <c r="S7" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="T7" s="45"/>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="45"/>
-      <c r="X7" s="45"/>
-      <c r="Y7" s="45"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
       <c r="Z7" s="6" t="s">
         <v>2</v>
       </c>
@@ -2251,14 +2257,14 @@
       <c r="AJ7" s="8"/>
     </row>
     <row r="8" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
       <c r="H8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2272,15 +2278,15 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="45" t="s">
+      <c r="S8" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
+      <c r="T8" s="103"/>
+      <c r="U8" s="103"/>
+      <c r="V8" s="103"/>
+      <c r="W8" s="103"/>
+      <c r="X8" s="103"/>
+      <c r="Y8" s="103"/>
       <c r="Z8" s="6" t="s">
         <v>2</v>
       </c>
@@ -2296,14 +2302,14 @@
       <c r="AJ8" s="8"/>
     </row>
     <row r="9" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
       <c r="H9" s="4" t="s">
         <v>2</v>
       </c>
@@ -2317,15 +2323,15 @@
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="44" t="s">
+      <c r="S9" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="102"/>
+      <c r="V9" s="102"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="102"/>
+      <c r="Y9" s="102"/>
       <c r="Z9" s="6" t="s">
         <v>2</v>
       </c>
@@ -2344,14 +2350,14 @@
       <c r="AM9" s="11"/>
     </row>
     <row r="10" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
       <c r="H10" s="4" t="s">
         <v>2</v>
       </c>
@@ -2365,15 +2371,15 @@
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="45" t="s">
+      <c r="S10" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
+      <c r="Y10" s="103"/>
       <c r="Z10" s="6" t="s">
         <v>2</v>
       </c>
@@ -2392,14 +2398,14 @@
       <c r="AM10" s="11"/>
     </row>
     <row r="11" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
       <c r="H11" s="4" t="s">
         <v>2</v>
       </c>
@@ -2413,15 +2419,15 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="45" t="s">
+      <c r="S11" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
+      <c r="Y11" s="103"/>
       <c r="Z11" s="6" t="s">
         <v>2</v>
       </c>
@@ -2440,14 +2446,14 @@
       <c r="AM11" s="11"/>
     </row>
     <row r="12" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
       <c r="H12" s="4" t="s">
         <v>2</v>
       </c>
@@ -2461,43 +2467,43 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="45" t="s">
+      <c r="S12" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
+      <c r="Y12" s="103"/>
       <c r="Z12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="46" t="s">
+      <c r="AA12" s="104" t="s">
         <v>13</v>
       </c>
-      <c r="AB12" s="46"/>
-      <c r="AC12" s="46"/>
-      <c r="AD12" s="46"/>
-      <c r="AE12" s="46"/>
-      <c r="AF12" s="46"/>
-      <c r="AG12" s="46"/>
-      <c r="AH12" s="46"/>
-      <c r="AI12" s="46"/>
+      <c r="AB12" s="104"/>
+      <c r="AC12" s="104"/>
+      <c r="AD12" s="104"/>
+      <c r="AE12" s="104"/>
+      <c r="AF12" s="104"/>
+      <c r="AG12" s="104"/>
+      <c r="AH12" s="104"/>
+      <c r="AI12" s="104"/>
       <c r="AJ12" s="10"/>
       <c r="AK12" s="11"/>
       <c r="AL12" s="11"/>
       <c r="AM12" s="11"/>
     </row>
     <row r="13" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
       <c r="H13" s="4" t="s">
         <v>2</v>
       </c>
@@ -2519,29 +2525,29 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="46"/>
-      <c r="AB13" s="46"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="46"/>
-      <c r="AE13" s="46"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="46"/>
-      <c r="AH13" s="46"/>
-      <c r="AI13" s="46"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
+      <c r="AC13" s="104"/>
+      <c r="AD13" s="104"/>
+      <c r="AE13" s="104"/>
+      <c r="AF13" s="104"/>
+      <c r="AG13" s="104"/>
+      <c r="AH13" s="104"/>
+      <c r="AI13" s="104"/>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="11"/>
       <c r="AL13" s="11"/>
       <c r="AM13" s="11"/>
     </row>
     <row r="14" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
       <c r="H14" s="4" t="s">
         <v>2</v>
       </c>
@@ -2563,29 +2569,29 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="46"/>
-      <c r="AB14" s="46"/>
-      <c r="AC14" s="46"/>
-      <c r="AD14" s="46"/>
-      <c r="AE14" s="46"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="46"/>
-      <c r="AH14" s="46"/>
-      <c r="AI14" s="46"/>
+      <c r="AA14" s="104"/>
+      <c r="AB14" s="104"/>
+      <c r="AC14" s="104"/>
+      <c r="AD14" s="104"/>
+      <c r="AE14" s="104"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104"/>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="104"/>
       <c r="AJ14" s="10"/>
       <c r="AK14" s="14"/>
       <c r="AL14" s="14"/>
       <c r="AM14" s="14"/>
     </row>
     <row r="15" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
       <c r="H15" s="4" t="s">
         <v>2</v>
       </c>
@@ -2607,26 +2613,26 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
-      <c r="AA15" s="46"/>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="46"/>
-      <c r="AE15" s="46"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="46"/>
-      <c r="AI15" s="46"/>
+      <c r="AA15" s="104"/>
+      <c r="AB15" s="104"/>
+      <c r="AC15" s="104"/>
+      <c r="AD15" s="104"/>
+      <c r="AE15" s="104"/>
+      <c r="AF15" s="104"/>
+      <c r="AG15" s="104"/>
+      <c r="AH15" s="104"/>
+      <c r="AI15" s="104"/>
       <c r="AJ15" s="8"/>
     </row>
     <row r="16" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
       <c r="H16" s="4" t="s">
         <v>2</v>
       </c>
@@ -2648,26 +2654,26 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
-      <c r="AA16" s="46"/>
-      <c r="AB16" s="46"/>
-      <c r="AC16" s="46"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="46"/>
-      <c r="AF16" s="46"/>
-      <c r="AG16" s="46"/>
-      <c r="AH16" s="46"/>
-      <c r="AI16" s="46"/>
+      <c r="AA16" s="104"/>
+      <c r="AB16" s="104"/>
+      <c r="AC16" s="104"/>
+      <c r="AD16" s="104"/>
+      <c r="AE16" s="104"/>
+      <c r="AF16" s="104"/>
+      <c r="AG16" s="104"/>
+      <c r="AH16" s="104"/>
+      <c r="AI16" s="104"/>
       <c r="AJ16" s="8"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
+      <c r="C17" s="102"/>
+      <c r="D17" s="102"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
       <c r="H17" s="4" t="s">
         <v>2</v>
       </c>
@@ -2689,53 +2695,53 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="46"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AH17" s="46"/>
-      <c r="AI17" s="46"/>
+      <c r="AA17" s="104"/>
+      <c r="AB17" s="104"/>
+      <c r="AC17" s="104"/>
+      <c r="AD17" s="104"/>
+      <c r="AE17" s="104"/>
+      <c r="AF17" s="104"/>
+      <c r="AG17" s="104"/>
+      <c r="AH17" s="104"/>
+      <c r="AI17" s="104"/>
       <c r="AJ17" s="8"/>
     </row>
     <row r="18" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="49"/>
-      <c r="R18" s="49"/>
-      <c r="S18" s="49"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="49"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="49"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="49"/>
-      <c r="AG18" s="49"/>
-      <c r="AH18" s="49"/>
-      <c r="AI18" s="49"/>
-      <c r="AJ18" s="50"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
+      <c r="R18" s="68"/>
+      <c r="S18" s="68"/>
+      <c r="T18" s="68"/>
+      <c r="U18" s="68"/>
+      <c r="V18" s="68"/>
+      <c r="W18" s="68"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="68"/>
+      <c r="Z18" s="68"/>
+      <c r="AA18" s="68"/>
+      <c r="AB18" s="68"/>
+      <c r="AC18" s="68"/>
+      <c r="AD18" s="68"/>
+      <c r="AE18" s="68"/>
+      <c r="AF18" s="68"/>
+      <c r="AG18" s="68"/>
+      <c r="AH18" s="68"/>
+      <c r="AI18" s="68"/>
+      <c r="AJ18" s="69"/>
     </row>
     <row r="19" spans="2:36" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="2"/>
@@ -2753,14 +2759,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="15"/>
-      <c r="Q19" s="51" t="s">
+      <c r="Q19" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
-      <c r="T19" s="52"/>
-      <c r="U19" s="52"/>
-      <c r="V19" s="52"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="71"/>
       <c r="W19" s="15"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2782,229 +2788,229 @@
     </row>
     <row r="21" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="17"/>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="56" t="s">
+      <c r="D21" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="57"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="65" t="s">
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="65"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="65"/>
-      <c r="P21" s="65"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="65" t="s">
+      <c r="M21" s="82"/>
+      <c r="N21" s="82"/>
+      <c r="O21" s="82"/>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82"/>
+      <c r="R21" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="S21" s="65"/>
-      <c r="T21" s="65"/>
-      <c r="U21" s="65"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="65"/>
-      <c r="X21" s="66" t="s">
+      <c r="S21" s="82"/>
+      <c r="T21" s="82"/>
+      <c r="U21" s="82"/>
+      <c r="V21" s="82"/>
+      <c r="W21" s="82"/>
+      <c r="X21" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="Y21" s="66"/>
-      <c r="Z21" s="66"/>
-      <c r="AA21" s="66"/>
-      <c r="AB21" s="66"/>
-      <c r="AC21" s="66"/>
-      <c r="AD21" s="56" t="s">
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="AE21" s="57"/>
-      <c r="AF21" s="57"/>
-      <c r="AG21" s="57"/>
-      <c r="AH21" s="57"/>
-      <c r="AI21" s="58"/>
+      <c r="AE21" s="74"/>
+      <c r="AF21" s="74"/>
+      <c r="AG21" s="74"/>
+      <c r="AH21" s="74"/>
+      <c r="AI21" s="75"/>
       <c r="AJ21" s="8"/>
     </row>
     <row r="22" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="17"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="60"/>
-      <c r="AF22" s="60"/>
-      <c r="AG22" s="60"/>
-      <c r="AH22" s="60"/>
-      <c r="AI22" s="61"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="82"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="82"/>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82"/>
+      <c r="R22" s="82"/>
+      <c r="S22" s="82"/>
+      <c r="T22" s="82"/>
+      <c r="U22" s="82"/>
+      <c r="V22" s="82"/>
+      <c r="W22" s="82"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="76"/>
+      <c r="AE22" s="77"/>
+      <c r="AF22" s="77"/>
+      <c r="AG22" s="77"/>
+      <c r="AH22" s="77"/>
+      <c r="AI22" s="78"/>
       <c r="AJ22" s="8"/>
     </row>
     <row r="23" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="17"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
-      <c r="W23" s="65"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="59"/>
-      <c r="AE23" s="60"/>
-      <c r="AF23" s="60"/>
-      <c r="AG23" s="60"/>
-      <c r="AH23" s="60"/>
-      <c r="AI23" s="61"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
+      <c r="J23" s="80"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="82"/>
+      <c r="M23" s="82"/>
+      <c r="N23" s="82"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="82"/>
+      <c r="T23" s="82"/>
+      <c r="U23" s="82"/>
+      <c r="V23" s="82"/>
+      <c r="W23" s="82"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="65"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="76"/>
+      <c r="AE23" s="77"/>
+      <c r="AF23" s="77"/>
+      <c r="AG23" s="77"/>
+      <c r="AH23" s="77"/>
+      <c r="AI23" s="78"/>
       <c r="AJ23" s="8"/>
     </row>
     <row r="24" spans="2:36" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="17"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="67" t="s">
+      <c r="C24" s="31"/>
+      <c r="D24" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67" t="s">
+      <c r="E24" s="84"/>
+      <c r="F24" s="84"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="47" t="s">
+      <c r="I24" s="84"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47" t="s">
+      <c r="M24" s="66"/>
+      <c r="N24" s="66"/>
+      <c r="O24" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47" t="s">
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="S24" s="47"/>
-      <c r="T24" s="47"/>
-      <c r="U24" s="47" t="s">
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="V24" s="47"/>
-      <c r="W24" s="47"/>
-      <c r="X24" s="47" t="s">
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="Y24" s="47"/>
-      <c r="Z24" s="47"/>
-      <c r="AA24" s="47" t="s">
+      <c r="Y24" s="66"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="AB24" s="47"/>
-      <c r="AC24" s="47"/>
-      <c r="AD24" s="59"/>
-      <c r="AE24" s="60"/>
-      <c r="AF24" s="60"/>
-      <c r="AG24" s="60"/>
-      <c r="AH24" s="60"/>
-      <c r="AI24" s="61"/>
+      <c r="AB24" s="66"/>
+      <c r="AC24" s="66"/>
+      <c r="AD24" s="76"/>
+      <c r="AE24" s="77"/>
+      <c r="AF24" s="77"/>
+      <c r="AG24" s="77"/>
+      <c r="AH24" s="77"/>
+      <c r="AI24" s="78"/>
       <c r="AJ24" s="8"/>
     </row>
     <row r="25" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="17"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="73" t="s">
+      <c r="C25" s="33"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="M25" s="73"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="55" t="s">
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55" t="s">
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55" t="s">
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55" t="s">
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="Y25" s="55"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="55" t="s">
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="AB25" s="55"/>
-      <c r="AC25" s="55"/>
-      <c r="AD25" s="70" t="s">
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="AE25" s="71"/>
-      <c r="AF25" s="71"/>
-      <c r="AG25" s="71"/>
-      <c r="AH25" s="71"/>
-      <c r="AI25" s="72"/>
+      <c r="AE25" s="35"/>
+      <c r="AF25" s="35"/>
+      <c r="AG25" s="35"/>
+      <c r="AH25" s="35"/>
+      <c r="AI25" s="36"/>
       <c r="AJ25" s="8"/>
     </row>
     <row r="26" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3012,38 +3018,38 @@
       <c r="C26" s="18">
         <v>1</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="66"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
-      <c r="Q26" s="74"/>
-      <c r="R26" s="74"/>
-      <c r="S26" s="74"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-      <c r="AA26" s="74"/>
-      <c r="AB26" s="74"/>
-      <c r="AC26" s="74"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="76"/>
-      <c r="AF26" s="76"/>
-      <c r="AG26" s="76"/>
-      <c r="AH26" s="76"/>
-      <c r="AI26" s="77"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="61"/>
+      <c r="R26" s="61"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="61"/>
+      <c r="X26" s="61"/>
+      <c r="Y26" s="61"/>
+      <c r="Z26" s="61"/>
+      <c r="AA26" s="61"/>
+      <c r="AB26" s="61"/>
+      <c r="AC26" s="61"/>
+      <c r="AD26" s="62"/>
+      <c r="AE26" s="63"/>
+      <c r="AF26" s="63"/>
+      <c r="AG26" s="63"/>
+      <c r="AH26" s="63"/>
+      <c r="AI26" s="64"/>
       <c r="AJ26" s="8"/>
     </row>
     <row r="27" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3051,38 +3057,38 @@
       <c r="C27" s="18">
         <v>2</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
-      <c r="J27" s="74"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="74"/>
-      <c r="M27" s="74"/>
-      <c r="N27" s="74"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="74"/>
-      <c r="Q27" s="74"/>
-      <c r="R27" s="74"/>
-      <c r="S27" s="74"/>
-      <c r="T27" s="74"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="74"/>
-      <c r="W27" s="74"/>
-      <c r="X27" s="74"/>
-      <c r="Y27" s="74"/>
-      <c r="Z27" s="74"/>
-      <c r="AA27" s="74"/>
-      <c r="AB27" s="74"/>
-      <c r="AC27" s="74"/>
-      <c r="AD27" s="75"/>
-      <c r="AE27" s="76"/>
-      <c r="AF27" s="76"/>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="76"/>
-      <c r="AI27" s="77"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="105"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="105"/>
+      <c r="Q27" s="105"/>
+      <c r="R27" s="105"/>
+      <c r="S27" s="105"/>
+      <c r="T27" s="105"/>
+      <c r="U27" s="105"/>
+      <c r="V27" s="105"/>
+      <c r="W27" s="105"/>
+      <c r="X27" s="105"/>
+      <c r="Y27" s="105"/>
+      <c r="Z27" s="105"/>
+      <c r="AA27" s="105"/>
+      <c r="AB27" s="105"/>
+      <c r="AC27" s="105"/>
+      <c r="AD27" s="62"/>
+      <c r="AE27" s="63"/>
+      <c r="AF27" s="63"/>
+      <c r="AG27" s="63"/>
+      <c r="AH27" s="63"/>
+      <c r="AI27" s="64"/>
       <c r="AJ27" s="8"/>
     </row>
     <row r="28" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3090,38 +3096,38 @@
       <c r="C28" s="18">
         <v>3</v>
       </c>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
-      <c r="J28" s="74"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="74"/>
-      <c r="M28" s="74"/>
-      <c r="N28" s="74"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="74"/>
-      <c r="Q28" s="74"/>
-      <c r="R28" s="74"/>
-      <c r="S28" s="74"/>
-      <c r="T28" s="74"/>
-      <c r="U28" s="74"/>
-      <c r="V28" s="74"/>
-      <c r="W28" s="74"/>
-      <c r="X28" s="74"/>
-      <c r="Y28" s="74"/>
-      <c r="Z28" s="74"/>
-      <c r="AA28" s="74"/>
-      <c r="AB28" s="74"/>
-      <c r="AC28" s="74"/>
-      <c r="AD28" s="75"/>
-      <c r="AE28" s="76"/>
-      <c r="AF28" s="76"/>
-      <c r="AG28" s="76"/>
-      <c r="AH28" s="76"/>
-      <c r="AI28" s="77"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="105"/>
+      <c r="N28" s="105"/>
+      <c r="O28" s="105"/>
+      <c r="P28" s="105"/>
+      <c r="Q28" s="105"/>
+      <c r="R28" s="105"/>
+      <c r="S28" s="105"/>
+      <c r="T28" s="105"/>
+      <c r="U28" s="105"/>
+      <c r="V28" s="105"/>
+      <c r="W28" s="105"/>
+      <c r="X28" s="105"/>
+      <c r="Y28" s="105"/>
+      <c r="Z28" s="105"/>
+      <c r="AA28" s="105"/>
+      <c r="AB28" s="105"/>
+      <c r="AC28" s="105"/>
+      <c r="AD28" s="62"/>
+      <c r="AE28" s="63"/>
+      <c r="AF28" s="63"/>
+      <c r="AG28" s="63"/>
+      <c r="AH28" s="63"/>
+      <c r="AI28" s="64"/>
       <c r="AJ28" s="19"/>
     </row>
     <row r="29" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3129,38 +3135,38 @@
       <c r="C29" s="18">
         <v>4</v>
       </c>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="74"/>
-      <c r="M29" s="74"/>
-      <c r="N29" s="74"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="74"/>
-      <c r="Q29" s="74"/>
-      <c r="R29" s="74"/>
-      <c r="S29" s="74"/>
-      <c r="T29" s="74"/>
-      <c r="U29" s="74"/>
-      <c r="V29" s="74"/>
-      <c r="W29" s="74"/>
-      <c r="X29" s="74"/>
-      <c r="Y29" s="74"/>
-      <c r="Z29" s="74"/>
-      <c r="AA29" s="74"/>
-      <c r="AB29" s="74"/>
-      <c r="AC29" s="74"/>
-      <c r="AD29" s="75"/>
-      <c r="AE29" s="76"/>
-      <c r="AF29" s="76"/>
-      <c r="AG29" s="76"/>
-      <c r="AH29" s="76"/>
-      <c r="AI29" s="77"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="105"/>
+      <c r="N29" s="105"/>
+      <c r="O29" s="105"/>
+      <c r="P29" s="105"/>
+      <c r="Q29" s="105"/>
+      <c r="R29" s="105"/>
+      <c r="S29" s="105"/>
+      <c r="T29" s="105"/>
+      <c r="U29" s="105"/>
+      <c r="V29" s="105"/>
+      <c r="W29" s="105"/>
+      <c r="X29" s="105"/>
+      <c r="Y29" s="105"/>
+      <c r="Z29" s="105"/>
+      <c r="AA29" s="105"/>
+      <c r="AB29" s="105"/>
+      <c r="AC29" s="105"/>
+      <c r="AD29" s="62"/>
+      <c r="AE29" s="63"/>
+      <c r="AF29" s="63"/>
+      <c r="AG29" s="63"/>
+      <c r="AH29" s="63"/>
+      <c r="AI29" s="64"/>
       <c r="AJ29" s="19"/>
     </row>
     <row r="30" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3168,38 +3174,38 @@
       <c r="C30" s="18">
         <v>5</v>
       </c>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
-      <c r="L30" s="74"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="74"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="74"/>
-      <c r="Q30" s="74"/>
-      <c r="R30" s="74"/>
-      <c r="S30" s="74"/>
-      <c r="T30" s="74"/>
-      <c r="U30" s="74"/>
-      <c r="V30" s="74"/>
-      <c r="W30" s="74"/>
-      <c r="X30" s="74"/>
-      <c r="Y30" s="74"/>
-      <c r="Z30" s="74"/>
-      <c r="AA30" s="78"/>
-      <c r="AB30" s="78"/>
-      <c r="AC30" s="78"/>
-      <c r="AD30" s="75"/>
-      <c r="AE30" s="76"/>
-      <c r="AF30" s="76"/>
-      <c r="AG30" s="76"/>
-      <c r="AH30" s="76"/>
-      <c r="AI30" s="77"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="105"/>
+      <c r="M30" s="105"/>
+      <c r="N30" s="105"/>
+      <c r="O30" s="105"/>
+      <c r="P30" s="105"/>
+      <c r="Q30" s="105"/>
+      <c r="R30" s="105"/>
+      <c r="S30" s="105"/>
+      <c r="T30" s="105"/>
+      <c r="U30" s="105"/>
+      <c r="V30" s="105"/>
+      <c r="W30" s="105"/>
+      <c r="X30" s="105"/>
+      <c r="Y30" s="105"/>
+      <c r="Z30" s="105"/>
+      <c r="AA30" s="106"/>
+      <c r="AB30" s="106"/>
+      <c r="AC30" s="106"/>
+      <c r="AD30" s="62"/>
+      <c r="AE30" s="63"/>
+      <c r="AF30" s="63"/>
+      <c r="AG30" s="63"/>
+      <c r="AH30" s="63"/>
+      <c r="AI30" s="64"/>
       <c r="AJ30" s="19"/>
     </row>
     <row r="31" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3207,38 +3213,38 @@
       <c r="C31" s="18">
         <v>6</v>
       </c>
-      <c r="D31" s="66"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="66"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="74"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="74"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="74"/>
-      <c r="Q31" s="74"/>
-      <c r="R31" s="74"/>
-      <c r="S31" s="74"/>
-      <c r="T31" s="74"/>
-      <c r="U31" s="74"/>
-      <c r="V31" s="74"/>
-      <c r="W31" s="74"/>
-      <c r="X31" s="74"/>
-      <c r="Y31" s="74"/>
-      <c r="Z31" s="74"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="74"/>
-      <c r="AC31" s="74"/>
-      <c r="AD31" s="75"/>
-      <c r="AE31" s="76"/>
-      <c r="AF31" s="76"/>
-      <c r="AG31" s="76"/>
-      <c r="AH31" s="76"/>
-      <c r="AI31" s="77"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="61"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="105"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="105"/>
+      <c r="R31" s="105"/>
+      <c r="S31" s="105"/>
+      <c r="T31" s="105"/>
+      <c r="U31" s="105"/>
+      <c r="V31" s="105"/>
+      <c r="W31" s="105"/>
+      <c r="X31" s="105"/>
+      <c r="Y31" s="105"/>
+      <c r="Z31" s="105"/>
+      <c r="AA31" s="105"/>
+      <c r="AB31" s="105"/>
+      <c r="AC31" s="105"/>
+      <c r="AD31" s="62"/>
+      <c r="AE31" s="63"/>
+      <c r="AF31" s="63"/>
+      <c r="AG31" s="63"/>
+      <c r="AH31" s="63"/>
+      <c r="AI31" s="64"/>
       <c r="AJ31" s="19"/>
     </row>
     <row r="32" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3246,38 +3252,38 @@
       <c r="C32" s="18">
         <v>7</v>
       </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="74"/>
-      <c r="L32" s="74"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="74"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="74"/>
-      <c r="Q32" s="74"/>
-      <c r="R32" s="74"/>
-      <c r="S32" s="74"/>
-      <c r="T32" s="74"/>
-      <c r="U32" s="74"/>
-      <c r="V32" s="74"/>
-      <c r="W32" s="74"/>
-      <c r="X32" s="74"/>
-      <c r="Y32" s="74"/>
-      <c r="Z32" s="74"/>
-      <c r="AA32" s="74"/>
-      <c r="AB32" s="74"/>
-      <c r="AC32" s="74"/>
-      <c r="AD32" s="75"/>
-      <c r="AE32" s="76"/>
-      <c r="AF32" s="76"/>
-      <c r="AG32" s="76"/>
-      <c r="AH32" s="76"/>
-      <c r="AI32" s="77"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="105"/>
+      <c r="S32" s="105"/>
+      <c r="T32" s="105"/>
+      <c r="U32" s="105"/>
+      <c r="V32" s="105"/>
+      <c r="W32" s="105"/>
+      <c r="X32" s="105"/>
+      <c r="Y32" s="105"/>
+      <c r="Z32" s="105"/>
+      <c r="AA32" s="105"/>
+      <c r="AB32" s="105"/>
+      <c r="AC32" s="105"/>
+      <c r="AD32" s="62"/>
+      <c r="AE32" s="63"/>
+      <c r="AF32" s="63"/>
+      <c r="AG32" s="63"/>
+      <c r="AH32" s="63"/>
+      <c r="AI32" s="64"/>
       <c r="AJ32" s="8"/>
     </row>
     <row r="33" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3285,38 +3291,38 @@
       <c r="C33" s="18">
         <v>8</v>
       </c>
-      <c r="D33" s="66"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="66"/>
-      <c r="M33" s="66"/>
-      <c r="N33" s="66"/>
-      <c r="O33" s="66"/>
-      <c r="P33" s="66"/>
-      <c r="Q33" s="66"/>
-      <c r="R33" s="74"/>
-      <c r="S33" s="74"/>
-      <c r="T33" s="74"/>
-      <c r="U33" s="74"/>
-      <c r="V33" s="74"/>
-      <c r="W33" s="74"/>
-      <c r="X33" s="74"/>
-      <c r="Y33" s="74"/>
-      <c r="Z33" s="74"/>
-      <c r="AA33" s="74"/>
-      <c r="AB33" s="74"/>
-      <c r="AC33" s="74"/>
-      <c r="AD33" s="75"/>
-      <c r="AE33" s="76"/>
-      <c r="AF33" s="76"/>
-      <c r="AG33" s="76"/>
-      <c r="AH33" s="76"/>
-      <c r="AI33" s="77"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="65"/>
+      <c r="K33" s="65"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="105"/>
+      <c r="O33" s="105"/>
+      <c r="P33" s="105"/>
+      <c r="Q33" s="105"/>
+      <c r="R33" s="105"/>
+      <c r="S33" s="105"/>
+      <c r="T33" s="105"/>
+      <c r="U33" s="105"/>
+      <c r="V33" s="105"/>
+      <c r="W33" s="105"/>
+      <c r="X33" s="105"/>
+      <c r="Y33" s="105"/>
+      <c r="Z33" s="105"/>
+      <c r="AA33" s="105"/>
+      <c r="AB33" s="105"/>
+      <c r="AC33" s="105"/>
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="63"/>
+      <c r="AF33" s="63"/>
+      <c r="AG33" s="63"/>
+      <c r="AH33" s="63"/>
+      <c r="AI33" s="64"/>
       <c r="AJ33" s="8"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3324,38 +3330,38 @@
       <c r="C34" s="18">
         <v>9</v>
       </c>
-      <c r="D34" s="66"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="66"/>
-      <c r="H34" s="66"/>
-      <c r="I34" s="66"/>
-      <c r="J34" s="66"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="66"/>
-      <c r="M34" s="66"/>
-      <c r="N34" s="66"/>
-      <c r="O34" s="66"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="74"/>
-      <c r="S34" s="74"/>
-      <c r="T34" s="74"/>
-      <c r="U34" s="74"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="74"/>
-      <c r="X34" s="74"/>
-      <c r="Y34" s="74"/>
-      <c r="Z34" s="74"/>
-      <c r="AA34" s="74"/>
-      <c r="AB34" s="74"/>
-      <c r="AC34" s="74"/>
-      <c r="AD34" s="75"/>
-      <c r="AE34" s="76"/>
-      <c r="AF34" s="76"/>
-      <c r="AG34" s="76"/>
-      <c r="AH34" s="76"/>
-      <c r="AI34" s="77"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="105"/>
+      <c r="M34" s="105"/>
+      <c r="N34" s="105"/>
+      <c r="O34" s="105"/>
+      <c r="P34" s="105"/>
+      <c r="Q34" s="105"/>
+      <c r="R34" s="105"/>
+      <c r="S34" s="105"/>
+      <c r="T34" s="105"/>
+      <c r="U34" s="105"/>
+      <c r="V34" s="105"/>
+      <c r="W34" s="105"/>
+      <c r="X34" s="105"/>
+      <c r="Y34" s="105"/>
+      <c r="Z34" s="105"/>
+      <c r="AA34" s="105"/>
+      <c r="AB34" s="105"/>
+      <c r="AC34" s="105"/>
+      <c r="AD34" s="62"/>
+      <c r="AE34" s="63"/>
+      <c r="AF34" s="63"/>
+      <c r="AG34" s="63"/>
+      <c r="AH34" s="63"/>
+      <c r="AI34" s="64"/>
       <c r="AJ34" s="8"/>
     </row>
     <row r="35" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3363,38 +3369,38 @@
       <c r="C35" s="18">
         <v>10</v>
       </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="66"/>
-      <c r="M35" s="66"/>
-      <c r="N35" s="66"/>
-      <c r="O35" s="66"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="66"/>
-      <c r="R35" s="74"/>
-      <c r="S35" s="74"/>
-      <c r="T35" s="74"/>
-      <c r="U35" s="74"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="74"/>
-      <c r="X35" s="74"/>
-      <c r="Y35" s="74"/>
-      <c r="Z35" s="74"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="74"/>
-      <c r="AC35" s="74"/>
-      <c r="AD35" s="75"/>
-      <c r="AE35" s="76"/>
-      <c r="AF35" s="76"/>
-      <c r="AG35" s="76"/>
-      <c r="AH35" s="76"/>
-      <c r="AI35" s="77"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="65"/>
+      <c r="K35" s="65"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105"/>
+      <c r="O35" s="105"/>
+      <c r="P35" s="105"/>
+      <c r="Q35" s="105"/>
+      <c r="R35" s="105"/>
+      <c r="S35" s="105"/>
+      <c r="T35" s="105"/>
+      <c r="U35" s="105"/>
+      <c r="V35" s="105"/>
+      <c r="W35" s="105"/>
+      <c r="X35" s="105"/>
+      <c r="Y35" s="105"/>
+      <c r="Z35" s="105"/>
+      <c r="AA35" s="105"/>
+      <c r="AB35" s="105"/>
+      <c r="AC35" s="105"/>
+      <c r="AD35" s="62"/>
+      <c r="AE35" s="63"/>
+      <c r="AF35" s="63"/>
+      <c r="AG35" s="63"/>
+      <c r="AH35" s="63"/>
+      <c r="AI35" s="64"/>
       <c r="AJ35" s="8"/>
     </row>
     <row r="36" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3402,38 +3408,38 @@
       <c r="C36" s="18">
         <v>11</v>
       </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="66"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="66"/>
-      <c r="O36" s="66"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="66"/>
-      <c r="R36" s="74"/>
-      <c r="S36" s="74"/>
-      <c r="T36" s="74"/>
-      <c r="U36" s="74"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="74"/>
-      <c r="X36" s="74"/>
-      <c r="Y36" s="74"/>
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="74"/>
-      <c r="AC36" s="74"/>
-      <c r="AD36" s="75"/>
-      <c r="AE36" s="76"/>
-      <c r="AF36" s="76"/>
-      <c r="AG36" s="76"/>
-      <c r="AH36" s="76"/>
-      <c r="AI36" s="77"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="105"/>
+      <c r="M36" s="105"/>
+      <c r="N36" s="105"/>
+      <c r="O36" s="105"/>
+      <c r="P36" s="105"/>
+      <c r="Q36" s="105"/>
+      <c r="R36" s="105"/>
+      <c r="S36" s="105"/>
+      <c r="T36" s="105"/>
+      <c r="U36" s="105"/>
+      <c r="V36" s="105"/>
+      <c r="W36" s="105"/>
+      <c r="X36" s="105"/>
+      <c r="Y36" s="105"/>
+      <c r="Z36" s="105"/>
+      <c r="AA36" s="105"/>
+      <c r="AB36" s="105"/>
+      <c r="AC36" s="105"/>
+      <c r="AD36" s="62"/>
+      <c r="AE36" s="63"/>
+      <c r="AF36" s="63"/>
+      <c r="AG36" s="63"/>
+      <c r="AH36" s="63"/>
+      <c r="AI36" s="64"/>
       <c r="AJ36" s="8"/>
     </row>
     <row r="37" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3441,38 +3447,38 @@
       <c r="C37" s="18">
         <v>12</v>
       </c>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80"/>
-      <c r="M37" s="80"/>
-      <c r="N37" s="80"/>
-      <c r="O37" s="80"/>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="80"/>
-      <c r="R37" s="80"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="80"/>
-      <c r="U37" s="80"/>
-      <c r="V37" s="80"/>
-      <c r="W37" s="80"/>
-      <c r="X37" s="80"/>
-      <c r="Y37" s="80"/>
-      <c r="Z37" s="80"/>
-      <c r="AA37" s="80"/>
-      <c r="AB37" s="80"/>
-      <c r="AC37" s="80"/>
-      <c r="AD37" s="81"/>
-      <c r="AE37" s="82"/>
-      <c r="AF37" s="82"/>
-      <c r="AG37" s="82"/>
-      <c r="AH37" s="82"/>
-      <c r="AI37" s="83"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="107"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="107"/>
+      <c r="P37" s="107"/>
+      <c r="Q37" s="107"/>
+      <c r="R37" s="107"/>
+      <c r="S37" s="107"/>
+      <c r="T37" s="107"/>
+      <c r="U37" s="107"/>
+      <c r="V37" s="107"/>
+      <c r="W37" s="107"/>
+      <c r="X37" s="107"/>
+      <c r="Y37" s="107"/>
+      <c r="Z37" s="107"/>
+      <c r="AA37" s="107"/>
+      <c r="AB37" s="107"/>
+      <c r="AC37" s="107"/>
+      <c r="AD37" s="52"/>
+      <c r="AE37" s="53"/>
+      <c r="AF37" s="53"/>
+      <c r="AG37" s="53"/>
+      <c r="AH37" s="53"/>
+      <c r="AI37" s="54"/>
       <c r="AJ37" s="8"/>
     </row>
     <row r="38" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3480,38 +3486,38 @@
       <c r="C38" s="18">
         <v>13</v>
       </c>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
-      <c r="J38" s="80"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="80"/>
-      <c r="M38" s="80"/>
-      <c r="N38" s="80"/>
-      <c r="O38" s="80"/>
-      <c r="P38" s="80"/>
-      <c r="Q38" s="80"/>
-      <c r="R38" s="80"/>
-      <c r="S38" s="80"/>
-      <c r="T38" s="80"/>
-      <c r="U38" s="80"/>
-      <c r="V38" s="80"/>
-      <c r="W38" s="80"/>
-      <c r="X38" s="80"/>
-      <c r="Y38" s="80"/>
-      <c r="Z38" s="80"/>
-      <c r="AA38" s="80"/>
-      <c r="AB38" s="80"/>
-      <c r="AC38" s="80"/>
-      <c r="AD38" s="81"/>
-      <c r="AE38" s="82"/>
-      <c r="AF38" s="82"/>
-      <c r="AG38" s="82"/>
-      <c r="AH38" s="82"/>
-      <c r="AI38" s="83"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="107"/>
+      <c r="M38" s="107"/>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="107"/>
+      <c r="S38" s="107"/>
+      <c r="T38" s="107"/>
+      <c r="U38" s="107"/>
+      <c r="V38" s="107"/>
+      <c r="W38" s="107"/>
+      <c r="X38" s="107"/>
+      <c r="Y38" s="107"/>
+      <c r="Z38" s="107"/>
+      <c r="AA38" s="107"/>
+      <c r="AB38" s="107"/>
+      <c r="AC38" s="107"/>
+      <c r="AD38" s="52"/>
+      <c r="AE38" s="53"/>
+      <c r="AF38" s="53"/>
+      <c r="AG38" s="53"/>
+      <c r="AH38" s="53"/>
+      <c r="AI38" s="54"/>
       <c r="AJ38" s="8"/>
     </row>
     <row r="39" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3519,38 +3525,38 @@
       <c r="C39" s="18">
         <v>14</v>
       </c>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
-      <c r="J39" s="80"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="80"/>
-      <c r="M39" s="80"/>
-      <c r="N39" s="80"/>
-      <c r="O39" s="80"/>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="80"/>
-      <c r="R39" s="80"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="80"/>
-      <c r="U39" s="80"/>
-      <c r="V39" s="80"/>
-      <c r="W39" s="80"/>
-      <c r="X39" s="80"/>
-      <c r="Y39" s="80"/>
-      <c r="Z39" s="80"/>
-      <c r="AA39" s="80"/>
-      <c r="AB39" s="80"/>
-      <c r="AC39" s="80"/>
-      <c r="AD39" s="81"/>
-      <c r="AE39" s="82"/>
-      <c r="AF39" s="82"/>
-      <c r="AG39" s="82"/>
-      <c r="AH39" s="82"/>
-      <c r="AI39" s="83"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="51"/>
+      <c r="L39" s="107"/>
+      <c r="M39" s="107"/>
+      <c r="N39" s="107"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="107"/>
+      <c r="S39" s="107"/>
+      <c r="T39" s="107"/>
+      <c r="U39" s="107"/>
+      <c r="V39" s="107"/>
+      <c r="W39" s="107"/>
+      <c r="X39" s="107"/>
+      <c r="Y39" s="107"/>
+      <c r="Z39" s="107"/>
+      <c r="AA39" s="107"/>
+      <c r="AB39" s="107"/>
+      <c r="AC39" s="107"/>
+      <c r="AD39" s="52"/>
+      <c r="AE39" s="53"/>
+      <c r="AF39" s="53"/>
+      <c r="AG39" s="53"/>
+      <c r="AH39" s="53"/>
+      <c r="AI39" s="54"/>
       <c r="AJ39" s="8"/>
     </row>
     <row r="40" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3558,373 +3564,373 @@
       <c r="C40" s="18">
         <v>15</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
-      <c r="J40" s="80"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="80"/>
-      <c r="M40" s="80"/>
-      <c r="N40" s="80"/>
-      <c r="O40" s="80"/>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="80"/>
-      <c r="R40" s="80"/>
-      <c r="S40" s="80"/>
-      <c r="T40" s="80"/>
-      <c r="U40" s="80"/>
-      <c r="V40" s="80"/>
-      <c r="W40" s="80"/>
-      <c r="X40" s="80"/>
-      <c r="Y40" s="80"/>
-      <c r="Z40" s="80"/>
-      <c r="AA40" s="80"/>
-      <c r="AB40" s="80"/>
-      <c r="AC40" s="80"/>
-      <c r="AD40" s="81"/>
-      <c r="AE40" s="82"/>
-      <c r="AF40" s="82"/>
-      <c r="AG40" s="82"/>
-      <c r="AH40" s="82"/>
-      <c r="AI40" s="83"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+      <c r="L40" s="107"/>
+      <c r="M40" s="107"/>
+      <c r="N40" s="107"/>
+      <c r="O40" s="107"/>
+      <c r="P40" s="107"/>
+      <c r="Q40" s="107"/>
+      <c r="R40" s="107"/>
+      <c r="S40" s="107"/>
+      <c r="T40" s="107"/>
+      <c r="U40" s="107"/>
+      <c r="V40" s="107"/>
+      <c r="W40" s="107"/>
+      <c r="X40" s="107"/>
+      <c r="Y40" s="107"/>
+      <c r="Z40" s="107"/>
+      <c r="AA40" s="107"/>
+      <c r="AB40" s="107"/>
+      <c r="AC40" s="107"/>
+      <c r="AD40" s="52"/>
+      <c r="AE40" s="53"/>
+      <c r="AF40" s="53"/>
+      <c r="AG40" s="53"/>
+      <c r="AH40" s="53"/>
+      <c r="AI40" s="54"/>
       <c r="AJ40" s="8"/>
     </row>
     <row r="41" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="17"/>
-      <c r="C41" s="84" t="s">
+      <c r="C41" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
-      <c r="N41" s="84"/>
-      <c r="O41" s="84"/>
-      <c r="P41" s="84"/>
-      <c r="Q41" s="84"/>
-      <c r="R41" s="84"/>
-      <c r="S41" s="84"/>
-      <c r="T41" s="84"/>
-      <c r="U41" s="84"/>
-      <c r="V41" s="84"/>
-      <c r="W41" s="84"/>
-      <c r="X41" s="84"/>
-      <c r="Y41" s="84"/>
-      <c r="Z41" s="84"/>
-      <c r="AA41" s="84"/>
-      <c r="AB41" s="84"/>
-      <c r="AC41" s="84"/>
-      <c r="AD41" s="84"/>
-      <c r="AE41" s="84"/>
-      <c r="AF41" s="84"/>
-      <c r="AG41" s="84"/>
-      <c r="AH41" s="84"/>
-      <c r="AI41" s="84"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="55"/>
+      <c r="V41" s="55"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="55"/>
+      <c r="Y41" s="55"/>
+      <c r="Z41" s="55"/>
+      <c r="AA41" s="55"/>
+      <c r="AB41" s="55"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="55"/>
+      <c r="AE41" s="55"/>
+      <c r="AF41" s="55"/>
+      <c r="AG41" s="55"/>
+      <c r="AH41" s="55"/>
+      <c r="AI41" s="55"/>
       <c r="AJ41" s="8"/>
     </row>
     <row r="42" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="17"/>
-      <c r="C42" s="84"/>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-      <c r="R42" s="84"/>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
-      <c r="V42" s="84"/>
-      <c r="W42" s="84"/>
-      <c r="X42" s="84"/>
-      <c r="Y42" s="84"/>
-      <c r="Z42" s="84"/>
-      <c r="AA42" s="84"/>
-      <c r="AB42" s="84"/>
-      <c r="AC42" s="84"/>
-      <c r="AD42" s="84"/>
-      <c r="AE42" s="84"/>
-      <c r="AF42" s="84"/>
-      <c r="AG42" s="84"/>
-      <c r="AH42" s="84"/>
-      <c r="AI42" s="84"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="55"/>
+      <c r="Q42" s="55"/>
+      <c r="R42" s="55"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="55"/>
+      <c r="U42" s="55"/>
+      <c r="V42" s="55"/>
+      <c r="W42" s="55"/>
+      <c r="X42" s="55"/>
+      <c r="Y42" s="55"/>
+      <c r="Z42" s="55"/>
+      <c r="AA42" s="55"/>
+      <c r="AB42" s="55"/>
+      <c r="AC42" s="55"/>
+      <c r="AD42" s="55"/>
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="55"/>
+      <c r="AG42" s="55"/>
+      <c r="AH42" s="55"/>
+      <c r="AI42" s="55"/>
       <c r="AJ42" s="8"/>
     </row>
     <row r="43" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="17"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="84"/>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="84"/>
-      <c r="P43" s="84"/>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="84"/>
-      <c r="S43" s="84"/>
-      <c r="T43" s="84"/>
-      <c r="U43" s="84"/>
-      <c r="V43" s="84"/>
-      <c r="W43" s="84"/>
-      <c r="X43" s="84"/>
-      <c r="Y43" s="84"/>
-      <c r="Z43" s="84"/>
-      <c r="AA43" s="84"/>
-      <c r="AB43" s="84"/>
-      <c r="AC43" s="84"/>
-      <c r="AD43" s="84"/>
-      <c r="AE43" s="84"/>
-      <c r="AF43" s="84"/>
-      <c r="AG43" s="84"/>
-      <c r="AH43" s="84"/>
-      <c r="AI43" s="84"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="55"/>
+      <c r="Q43" s="55"/>
+      <c r="R43" s="55"/>
+      <c r="S43" s="55"/>
+      <c r="T43" s="55"/>
+      <c r="U43" s="55"/>
+      <c r="V43" s="55"/>
+      <c r="W43" s="55"/>
+      <c r="X43" s="55"/>
+      <c r="Y43" s="55"/>
+      <c r="Z43" s="55"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="55"/>
+      <c r="AC43" s="55"/>
+      <c r="AD43" s="55"/>
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="55"/>
+      <c r="AG43" s="55"/>
+      <c r="AH43" s="55"/>
+      <c r="AI43" s="55"/>
       <c r="AJ43" s="8"/>
     </row>
     <row r="44" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="17"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84"/>
-      <c r="G44" s="84"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="84"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="84"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="84"/>
-      <c r="R44" s="84"/>
-      <c r="S44" s="84"/>
-      <c r="T44" s="84"/>
-      <c r="U44" s="84"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="84"/>
-      <c r="X44" s="84"/>
-      <c r="Y44" s="84"/>
-      <c r="Z44" s="84"/>
-      <c r="AA44" s="84"/>
-      <c r="AB44" s="84"/>
-      <c r="AC44" s="84"/>
-      <c r="AD44" s="84"/>
-      <c r="AE44" s="84"/>
-      <c r="AF44" s="84"/>
-      <c r="AG44" s="84"/>
-      <c r="AH44" s="84"/>
-      <c r="AI44" s="84"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="55"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="55"/>
+      <c r="Q44" s="55"/>
+      <c r="R44" s="55"/>
+      <c r="S44" s="55"/>
+      <c r="T44" s="55"/>
+      <c r="U44" s="55"/>
+      <c r="V44" s="55"/>
+      <c r="W44" s="55"/>
+      <c r="X44" s="55"/>
+      <c r="Y44" s="55"/>
+      <c r="Z44" s="55"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="55"/>
+      <c r="AC44" s="55"/>
+      <c r="AD44" s="55"/>
+      <c r="AE44" s="55"/>
+      <c r="AF44" s="55"/>
+      <c r="AG44" s="55"/>
+      <c r="AH44" s="55"/>
+      <c r="AI44" s="55"/>
       <c r="AJ44" s="8"/>
     </row>
     <row r="45" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="17"/>
-      <c r="C45" s="84"/>
-      <c r="D45" s="84"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="84"/>
-      <c r="G45" s="84"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="84"/>
-      <c r="L45" s="84"/>
-      <c r="M45" s="84"/>
-      <c r="N45" s="84"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="84"/>
-      <c r="Q45" s="84"/>
-      <c r="R45" s="84"/>
-      <c r="S45" s="84"/>
-      <c r="T45" s="84"/>
-      <c r="U45" s="84"/>
-      <c r="V45" s="84"/>
-      <c r="W45" s="84"/>
-      <c r="X45" s="84"/>
-      <c r="Y45" s="84"/>
-      <c r="Z45" s="84"/>
-      <c r="AA45" s="84"/>
-      <c r="AB45" s="84"/>
-      <c r="AC45" s="84"/>
-      <c r="AD45" s="84"/>
-      <c r="AE45" s="84"/>
-      <c r="AF45" s="84"/>
-      <c r="AG45" s="84"/>
-      <c r="AH45" s="84"/>
-      <c r="AI45" s="84"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="55"/>
+      <c r="Q45" s="55"/>
+      <c r="R45" s="55"/>
+      <c r="S45" s="55"/>
+      <c r="T45" s="55"/>
+      <c r="U45" s="55"/>
+      <c r="V45" s="55"/>
+      <c r="W45" s="55"/>
+      <c r="X45" s="55"/>
+      <c r="Y45" s="55"/>
+      <c r="Z45" s="55"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="55"/>
+      <c r="AC45" s="55"/>
+      <c r="AD45" s="55"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="55"/>
+      <c r="AH45" s="55"/>
+      <c r="AI45" s="55"/>
       <c r="AJ45" s="8"/>
     </row>
     <row r="46" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="17"/>
-      <c r="C46" s="84"/>
-      <c r="D46" s="84"/>
-      <c r="E46" s="84"/>
-      <c r="F46" s="84"/>
-      <c r="G46" s="84"/>
-      <c r="H46" s="84"/>
-      <c r="I46" s="84"/>
-      <c r="J46" s="84"/>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84"/>
-      <c r="M46" s="84"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="84"/>
-      <c r="P46" s="84"/>
-      <c r="Q46" s="84"/>
-      <c r="R46" s="84"/>
-      <c r="S46" s="84"/>
-      <c r="T46" s="84"/>
-      <c r="U46" s="84"/>
-      <c r="V46" s="84"/>
-      <c r="W46" s="84"/>
-      <c r="X46" s="84"/>
-      <c r="Y46" s="84"/>
-      <c r="Z46" s="84"/>
-      <c r="AA46" s="84"/>
-      <c r="AB46" s="84"/>
-      <c r="AC46" s="84"/>
-      <c r="AD46" s="84"/>
-      <c r="AE46" s="84"/>
-      <c r="AF46" s="84"/>
-      <c r="AG46" s="84"/>
-      <c r="AH46" s="84"/>
-      <c r="AI46" s="84"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="55"/>
+      <c r="P46" s="55"/>
+      <c r="Q46" s="55"/>
+      <c r="R46" s="55"/>
+      <c r="S46" s="55"/>
+      <c r="T46" s="55"/>
+      <c r="U46" s="55"/>
+      <c r="V46" s="55"/>
+      <c r="W46" s="55"/>
+      <c r="X46" s="55"/>
+      <c r="Y46" s="55"/>
+      <c r="Z46" s="55"/>
+      <c r="AA46" s="55"/>
+      <c r="AB46" s="55"/>
+      <c r="AC46" s="55"/>
+      <c r="AD46" s="55"/>
+      <c r="AE46" s="55"/>
+      <c r="AF46" s="55"/>
+      <c r="AG46" s="55"/>
+      <c r="AH46" s="55"/>
+      <c r="AI46" s="55"/>
       <c r="AJ46" s="8"/>
     </row>
     <row r="47" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="17"/>
-      <c r="C47" s="84"/>
-      <c r="D47" s="84"/>
-      <c r="E47" s="84"/>
-      <c r="F47" s="84"/>
-      <c r="G47" s="84"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="84"/>
-      <c r="J47" s="84"/>
-      <c r="K47" s="84"/>
-      <c r="L47" s="84"/>
-      <c r="M47" s="84"/>
-      <c r="N47" s="84"/>
-      <c r="O47" s="84"/>
-      <c r="P47" s="84"/>
-      <c r="Q47" s="84"/>
-      <c r="R47" s="84"/>
-      <c r="S47" s="84"/>
-      <c r="T47" s="84"/>
-      <c r="U47" s="84"/>
-      <c r="V47" s="84"/>
-      <c r="W47" s="84"/>
-      <c r="X47" s="84"/>
-      <c r="Y47" s="84"/>
-      <c r="Z47" s="84"/>
-      <c r="AA47" s="84"/>
-      <c r="AB47" s="84"/>
-      <c r="AC47" s="84"/>
-      <c r="AD47" s="84"/>
-      <c r="AE47" s="84"/>
-      <c r="AF47" s="84"/>
-      <c r="AG47" s="84"/>
-      <c r="AH47" s="84"/>
-      <c r="AI47" s="84"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="55"/>
+      <c r="N47" s="55"/>
+      <c r="O47" s="55"/>
+      <c r="P47" s="55"/>
+      <c r="Q47" s="55"/>
+      <c r="R47" s="55"/>
+      <c r="S47" s="55"/>
+      <c r="T47" s="55"/>
+      <c r="U47" s="55"/>
+      <c r="V47" s="55"/>
+      <c r="W47" s="55"/>
+      <c r="X47" s="55"/>
+      <c r="Y47" s="55"/>
+      <c r="Z47" s="55"/>
+      <c r="AA47" s="55"/>
+      <c r="AB47" s="55"/>
+      <c r="AC47" s="55"/>
+      <c r="AD47" s="55"/>
+      <c r="AE47" s="55"/>
+      <c r="AF47" s="55"/>
+      <c r="AG47" s="55"/>
+      <c r="AH47" s="55"/>
+      <c r="AI47" s="55"/>
       <c r="AJ47" s="8"/>
     </row>
     <row r="48" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="17"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="84"/>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84"/>
-      <c r="H48" s="84"/>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84"/>
-      <c r="M48" s="84"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
-      <c r="P48" s="84"/>
-      <c r="Q48" s="84"/>
-      <c r="R48" s="84"/>
-      <c r="S48" s="84"/>
-      <c r="T48" s="84"/>
-      <c r="U48" s="84"/>
-      <c r="V48" s="84"/>
-      <c r="W48" s="84"/>
-      <c r="X48" s="84"/>
-      <c r="Y48" s="84"/>
-      <c r="Z48" s="84"/>
-      <c r="AA48" s="84"/>
-      <c r="AB48" s="84"/>
-      <c r="AC48" s="84"/>
-      <c r="AD48" s="84"/>
-      <c r="AE48" s="84"/>
-      <c r="AF48" s="84"/>
-      <c r="AG48" s="84"/>
-      <c r="AH48" s="84"/>
-      <c r="AI48" s="84"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="55"/>
+      <c r="P48" s="55"/>
+      <c r="Q48" s="55"/>
+      <c r="R48" s="55"/>
+      <c r="S48" s="55"/>
+      <c r="T48" s="55"/>
+      <c r="U48" s="55"/>
+      <c r="V48" s="55"/>
+      <c r="W48" s="55"/>
+      <c r="X48" s="55"/>
+      <c r="Y48" s="55"/>
+      <c r="Z48" s="55"/>
+      <c r="AA48" s="55"/>
+      <c r="AB48" s="55"/>
+      <c r="AC48" s="55"/>
+      <c r="AD48" s="55"/>
+      <c r="AE48" s="55"/>
+      <c r="AF48" s="55"/>
+      <c r="AG48" s="55"/>
+      <c r="AH48" s="55"/>
+      <c r="AI48" s="55"/>
       <c r="AJ48" s="8"/>
     </row>
     <row r="49" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="17"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="84"/>
-      <c r="E49" s="84"/>
-      <c r="F49" s="84"/>
-      <c r="G49" s="84"/>
-      <c r="H49" s="84"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="84"/>
-      <c r="K49" s="84"/>
-      <c r="L49" s="84"/>
-      <c r="M49" s="84"/>
-      <c r="N49" s="84"/>
-      <c r="O49" s="84"/>
-      <c r="P49" s="84"/>
-      <c r="Q49" s="84"/>
-      <c r="R49" s="84"/>
-      <c r="S49" s="84"/>
-      <c r="T49" s="84"/>
-      <c r="U49" s="84"/>
-      <c r="V49" s="84"/>
-      <c r="W49" s="84"/>
-      <c r="X49" s="84"/>
-      <c r="Y49" s="84"/>
-      <c r="Z49" s="84"/>
-      <c r="AA49" s="84"/>
-      <c r="AB49" s="84"/>
-      <c r="AC49" s="84"/>
-      <c r="AD49" s="84"/>
-      <c r="AE49" s="84"/>
-      <c r="AF49" s="84"/>
-      <c r="AG49" s="84"/>
-      <c r="AH49" s="84"/>
-      <c r="AI49" s="84"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="55"/>
+      <c r="P49" s="55"/>
+      <c r="Q49" s="55"/>
+      <c r="R49" s="55"/>
+      <c r="S49" s="55"/>
+      <c r="T49" s="55"/>
+      <c r="U49" s="55"/>
+      <c r="V49" s="55"/>
+      <c r="W49" s="55"/>
+      <c r="X49" s="55"/>
+      <c r="Y49" s="55"/>
+      <c r="Z49" s="55"/>
+      <c r="AA49" s="55"/>
+      <c r="AB49" s="55"/>
+      <c r="AC49" s="55"/>
+      <c r="AD49" s="55"/>
+      <c r="AE49" s="55"/>
+      <c r="AF49" s="55"/>
+      <c r="AG49" s="55"/>
+      <c r="AH49" s="55"/>
+      <c r="AI49" s="55"/>
       <c r="AJ49" s="8"/>
     </row>
     <row r="50" spans="2:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3964,13 +3970,13 @@
     </row>
     <row r="51" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B51" s="17"/>
-      <c r="C51" s="85" t="s">
+      <c r="C51" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="85"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
       <c r="AJ51" s="8"/>
     </row>
     <row r="52" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
@@ -4035,345 +4041,345 @@
     </row>
     <row r="60" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="17"/>
-      <c r="H60" s="86" t="s">
+      <c r="H60" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="I60" s="87"/>
-      <c r="J60" s="87"/>
-      <c r="K60" s="87"/>
-      <c r="L60" s="87"/>
-      <c r="M60" s="87"/>
-      <c r="N60" s="87"/>
-      <c r="O60" s="87"/>
-      <c r="P60" s="87"/>
-      <c r="Q60" s="87"/>
-      <c r="R60" s="87"/>
-      <c r="S60" s="87"/>
-      <c r="T60" s="87"/>
-      <c r="U60" s="87"/>
-      <c r="V60" s="87"/>
-      <c r="W60" s="87"/>
-      <c r="X60" s="87"/>
-      <c r="Y60" s="87"/>
-      <c r="Z60" s="87"/>
-      <c r="AA60" s="87"/>
-      <c r="AB60" s="87"/>
-      <c r="AC60" s="87"/>
-      <c r="AD60" s="87"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="58"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="58"/>
+      <c r="Y60" s="58"/>
+      <c r="Z60" s="58"/>
+      <c r="AA60" s="58"/>
+      <c r="AB60" s="58"/>
+      <c r="AC60" s="58"/>
+      <c r="AD60" s="58"/>
       <c r="AJ60" s="8"/>
     </row>
     <row r="61" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B61" s="17"/>
-      <c r="H61" s="88" t="s">
+      <c r="H61" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="I61" s="88"/>
-      <c r="J61" s="88"/>
-      <c r="K61" s="88"/>
-      <c r="L61" s="88"/>
-      <c r="M61" s="88"/>
-      <c r="N61" s="88"/>
-      <c r="O61" s="88"/>
-      <c r="P61" s="88"/>
-      <c r="Q61" s="88"/>
-      <c r="R61" s="88"/>
-      <c r="S61" s="88"/>
-      <c r="T61" s="88"/>
-      <c r="U61" s="88"/>
-      <c r="V61" s="88"/>
-      <c r="W61" s="88"/>
-      <c r="X61" s="88"/>
-      <c r="Y61" s="88"/>
-      <c r="Z61" s="88"/>
-      <c r="AA61" s="88"/>
-      <c r="AB61" s="88"/>
-      <c r="AC61" s="88"/>
-      <c r="AD61" s="88"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="59"/>
+      <c r="W61" s="59"/>
+      <c r="X61" s="59"/>
+      <c r="Y61" s="59"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="59"/>
+      <c r="AB61" s="59"/>
+      <c r="AC61" s="59"/>
+      <c r="AD61" s="59"/>
       <c r="AJ61" s="8"/>
     </row>
     <row r="62" spans="2:36" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="17"/>
-      <c r="C62" s="89" t="s">
+      <c r="C62" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="89"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="89"/>
-      <c r="H62" s="90" t="s">
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="90"/>
-      <c r="J62" s="90"/>
-      <c r="K62" s="90"/>
-      <c r="L62" s="90"/>
-      <c r="M62" s="91" t="s">
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="N62" s="92"/>
-      <c r="O62" s="92"/>
-      <c r="P62" s="92"/>
-      <c r="Q62" s="92"/>
-      <c r="R62" s="93"/>
-      <c r="S62" s="90" t="s">
+      <c r="N62" s="40"/>
+      <c r="O62" s="40"/>
+      <c r="P62" s="40"/>
+      <c r="Q62" s="40"/>
+      <c r="R62" s="41"/>
+      <c r="S62" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="T62" s="90"/>
-      <c r="U62" s="90"/>
-      <c r="V62" s="90"/>
-      <c r="W62" s="90"/>
-      <c r="X62" s="94"/>
-      <c r="Y62" s="95"/>
-      <c r="Z62" s="95"/>
-      <c r="AA62" s="95"/>
-      <c r="AB62" s="95"/>
-      <c r="AC62" s="95"/>
-      <c r="AD62" s="95"/>
-      <c r="AE62" s="95"/>
-      <c r="AF62" s="95"/>
-      <c r="AG62" s="95"/>
-      <c r="AH62" s="95"/>
-      <c r="AI62" s="96"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="38"/>
+      <c r="V62" s="38"/>
+      <c r="W62" s="38"/>
+      <c r="X62" s="42"/>
+      <c r="Y62" s="43"/>
+      <c r="Z62" s="43"/>
+      <c r="AA62" s="43"/>
+      <c r="AB62" s="43"/>
+      <c r="AC62" s="43"/>
+      <c r="AD62" s="43"/>
+      <c r="AE62" s="43"/>
+      <c r="AF62" s="43"/>
+      <c r="AG62" s="43"/>
+      <c r="AH62" s="43"/>
+      <c r="AI62" s="44"/>
       <c r="AJ62" s="8"/>
     </row>
     <row r="63" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B63" s="17"/>
-      <c r="C63" s="97"/>
-      <c r="D63" s="97"/>
-      <c r="E63" s="97"/>
-      <c r="F63" s="97"/>
-      <c r="G63" s="97"/>
-      <c r="H63" s="97"/>
-      <c r="I63" s="97"/>
-      <c r="J63" s="97"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="97"/>
-      <c r="M63" s="98"/>
-      <c r="N63" s="30"/>
-      <c r="O63" s="30"/>
-      <c r="P63" s="30"/>
-      <c r="Q63" s="30"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="97"/>
-      <c r="T63" s="97"/>
-      <c r="U63" s="97"/>
-      <c r="V63" s="97"/>
-      <c r="W63" s="97"/>
-      <c r="X63" s="99" t="s">
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
+      <c r="I63" s="45"/>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="45"/>
+      <c r="M63" s="46"/>
+      <c r="N63" s="47"/>
+      <c r="O63" s="47"/>
+      <c r="P63" s="47"/>
+      <c r="Q63" s="47"/>
+      <c r="R63" s="48"/>
+      <c r="S63" s="45"/>
+      <c r="T63" s="45"/>
+      <c r="U63" s="45"/>
+      <c r="V63" s="45"/>
+      <c r="W63" s="45"/>
+      <c r="X63" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="Y63" s="100"/>
-      <c r="Z63" s="100"/>
-      <c r="AA63" s="100"/>
-      <c r="AB63" s="100"/>
-      <c r="AC63" s="100"/>
-      <c r="AD63" s="100"/>
-      <c r="AE63" s="100"/>
-      <c r="AF63" s="100"/>
-      <c r="AG63" s="100"/>
-      <c r="AH63" s="100"/>
-      <c r="AI63" s="100"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
+      <c r="AA63" s="50"/>
+      <c r="AB63" s="50"/>
+      <c r="AC63" s="50"/>
+      <c r="AD63" s="50"/>
+      <c r="AE63" s="50"/>
+      <c r="AF63" s="50"/>
+      <c r="AG63" s="50"/>
+      <c r="AH63" s="50"/>
+      <c r="AI63" s="50"/>
       <c r="AJ63" s="8"/>
     </row>
     <row r="64" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B64" s="17"/>
-      <c r="C64" s="97"/>
-      <c r="D64" s="97"/>
-      <c r="E64" s="97"/>
-      <c r="F64" s="97"/>
-      <c r="G64" s="97"/>
-      <c r="H64" s="97"/>
-      <c r="I64" s="97"/>
-      <c r="J64" s="97"/>
-      <c r="K64" s="97"/>
-      <c r="L64" s="97"/>
-      <c r="M64" s="98"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="97"/>
-      <c r="T64" s="97"/>
-      <c r="U64" s="97"/>
-      <c r="V64" s="97"/>
-      <c r="W64" s="97"/>
-      <c r="X64" s="100"/>
-      <c r="Y64" s="100"/>
-      <c r="Z64" s="100"/>
-      <c r="AA64" s="100"/>
-      <c r="AB64" s="100"/>
-      <c r="AC64" s="100"/>
-      <c r="AD64" s="100"/>
-      <c r="AE64" s="100"/>
-      <c r="AF64" s="100"/>
-      <c r="AG64" s="100"/>
-      <c r="AH64" s="100"/>
-      <c r="AI64" s="100"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="45"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="45"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="47"/>
+      <c r="O64" s="47"/>
+      <c r="P64" s="47"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="48"/>
+      <c r="S64" s="45"/>
+      <c r="T64" s="45"/>
+      <c r="U64" s="45"/>
+      <c r="V64" s="45"/>
+      <c r="W64" s="45"/>
+      <c r="X64" s="50"/>
+      <c r="Y64" s="50"/>
+      <c r="Z64" s="50"/>
+      <c r="AA64" s="50"/>
+      <c r="AB64" s="50"/>
+      <c r="AC64" s="50"/>
+      <c r="AD64" s="50"/>
+      <c r="AE64" s="50"/>
+      <c r="AF64" s="50"/>
+      <c r="AG64" s="50"/>
+      <c r="AH64" s="50"/>
+      <c r="AI64" s="50"/>
       <c r="AJ64" s="8"/>
     </row>
     <row r="65" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B65" s="17"/>
-      <c r="C65" s="97"/>
-      <c r="D65" s="97"/>
-      <c r="E65" s="97"/>
-      <c r="F65" s="97"/>
-      <c r="G65" s="97"/>
-      <c r="H65" s="97"/>
-      <c r="I65" s="97"/>
-      <c r="J65" s="97"/>
-      <c r="K65" s="97"/>
-      <c r="L65" s="97"/>
-      <c r="M65" s="98"/>
-      <c r="N65" s="30"/>
-      <c r="O65" s="30"/>
-      <c r="P65" s="30"/>
-      <c r="Q65" s="30"/>
-      <c r="R65" s="31"/>
-      <c r="S65" s="97"/>
-      <c r="T65" s="97"/>
-      <c r="U65" s="97"/>
-      <c r="V65" s="97"/>
-      <c r="W65" s="97"/>
-      <c r="X65" s="100"/>
-      <c r="Y65" s="100"/>
-      <c r="Z65" s="100"/>
-      <c r="AA65" s="100"/>
-      <c r="AB65" s="100"/>
-      <c r="AC65" s="100"/>
-      <c r="AD65" s="100"/>
-      <c r="AE65" s="100"/>
-      <c r="AF65" s="100"/>
-      <c r="AG65" s="100"/>
-      <c r="AH65" s="100"/>
-      <c r="AI65" s="100"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
+      <c r="I65" s="45"/>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="46"/>
+      <c r="N65" s="47"/>
+      <c r="O65" s="47"/>
+      <c r="P65" s="47"/>
+      <c r="Q65" s="47"/>
+      <c r="R65" s="48"/>
+      <c r="S65" s="45"/>
+      <c r="T65" s="45"/>
+      <c r="U65" s="45"/>
+      <c r="V65" s="45"/>
+      <c r="W65" s="45"/>
+      <c r="X65" s="50"/>
+      <c r="Y65" s="50"/>
+      <c r="Z65" s="50"/>
+      <c r="AA65" s="50"/>
+      <c r="AB65" s="50"/>
+      <c r="AC65" s="50"/>
+      <c r="AD65" s="50"/>
+      <c r="AE65" s="50"/>
+      <c r="AF65" s="50"/>
+      <c r="AG65" s="50"/>
+      <c r="AH65" s="50"/>
+      <c r="AI65" s="50"/>
       <c r="AJ65" s="8"/>
     </row>
     <row r="66" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B66" s="17"/>
-      <c r="C66" s="97"/>
-      <c r="D66" s="97"/>
-      <c r="E66" s="97"/>
-      <c r="F66" s="97"/>
-      <c r="G66" s="97"/>
-      <c r="H66" s="97"/>
-      <c r="I66" s="97"/>
-      <c r="J66" s="97"/>
-      <c r="K66" s="97"/>
-      <c r="L66" s="97"/>
-      <c r="M66" s="98"/>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
-      <c r="P66" s="30"/>
-      <c r="Q66" s="30"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="97"/>
-      <c r="T66" s="97"/>
-      <c r="U66" s="97"/>
-      <c r="V66" s="97"/>
-      <c r="W66" s="97"/>
-      <c r="X66" s="100"/>
-      <c r="Y66" s="100"/>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="100"/>
-      <c r="AB66" s="100"/>
-      <c r="AC66" s="100"/>
-      <c r="AD66" s="100"/>
-      <c r="AE66" s="100"/>
-      <c r="AF66" s="100"/>
-      <c r="AG66" s="100"/>
-      <c r="AH66" s="100"/>
-      <c r="AI66" s="100"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
+      <c r="I66" s="45"/>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="46"/>
+      <c r="N66" s="47"/>
+      <c r="O66" s="47"/>
+      <c r="P66" s="47"/>
+      <c r="Q66" s="47"/>
+      <c r="R66" s="48"/>
+      <c r="S66" s="45"/>
+      <c r="T66" s="45"/>
+      <c r="U66" s="45"/>
+      <c r="V66" s="45"/>
+      <c r="W66" s="45"/>
+      <c r="X66" s="50"/>
+      <c r="Y66" s="50"/>
+      <c r="Z66" s="50"/>
+      <c r="AA66" s="50"/>
+      <c r="AB66" s="50"/>
+      <c r="AC66" s="50"/>
+      <c r="AD66" s="50"/>
+      <c r="AE66" s="50"/>
+      <c r="AF66" s="50"/>
+      <c r="AG66" s="50"/>
+      <c r="AH66" s="50"/>
+      <c r="AI66" s="50"/>
       <c r="AJ66" s="8"/>
     </row>
     <row r="67" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B67" s="17"/>
-      <c r="C67" s="102" t="s">
+      <c r="C67" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D67" s="102"/>
-      <c r="E67" s="102"/>
-      <c r="F67" s="102"/>
-      <c r="G67" s="102"/>
-      <c r="H67" s="102" t="s">
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="I67" s="102"/>
-      <c r="J67" s="102"/>
-      <c r="K67" s="102"/>
-      <c r="L67" s="102"/>
-      <c r="M67" s="103" t="s">
+      <c r="I67" s="27"/>
+      <c r="J67" s="27"/>
+      <c r="K67" s="27"/>
+      <c r="L67" s="27"/>
+      <c r="M67" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="N67" s="104"/>
-      <c r="O67" s="104"/>
-      <c r="P67" s="104"/>
-      <c r="Q67" s="104"/>
-      <c r="R67" s="105"/>
-      <c r="S67" s="54" t="s">
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="T67" s="54"/>
-      <c r="U67" s="54"/>
-      <c r="V67" s="54"/>
-      <c r="W67" s="54"/>
-      <c r="X67" s="100"/>
-      <c r="Y67" s="100"/>
-      <c r="Z67" s="100"/>
-      <c r="AA67" s="100"/>
-      <c r="AB67" s="100"/>
-      <c r="AC67" s="100"/>
-      <c r="AD67" s="100"/>
-      <c r="AE67" s="100"/>
-      <c r="AF67" s="100"/>
-      <c r="AG67" s="100"/>
-      <c r="AH67" s="100"/>
-      <c r="AI67" s="100"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="50"/>
+      <c r="Y67" s="50"/>
+      <c r="Z67" s="50"/>
+      <c r="AA67" s="50"/>
+      <c r="AB67" s="50"/>
+      <c r="AC67" s="50"/>
+      <c r="AD67" s="50"/>
+      <c r="AE67" s="50"/>
+      <c r="AF67" s="50"/>
+      <c r="AG67" s="50"/>
+      <c r="AH67" s="50"/>
+      <c r="AI67" s="50"/>
       <c r="AJ67" s="8"/>
     </row>
     <row r="68" spans="2:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="17"/>
-      <c r="C68" s="73" t="s">
+      <c r="C68" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="73"/>
-      <c r="H68" s="55" t="s">
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="55"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="70" t="s">
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33"/>
+      <c r="M68" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="N68" s="71"/>
-      <c r="O68" s="71"/>
-      <c r="P68" s="71"/>
-      <c r="Q68" s="71"/>
-      <c r="R68" s="72"/>
-      <c r="S68" s="73" t="s">
+      <c r="N68" s="35"/>
+      <c r="O68" s="35"/>
+      <c r="P68" s="35"/>
+      <c r="Q68" s="35"/>
+      <c r="R68" s="36"/>
+      <c r="S68" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="T68" s="73"/>
-      <c r="U68" s="73"/>
-      <c r="V68" s="73"/>
-      <c r="W68" s="73"/>
-      <c r="X68" s="100"/>
-      <c r="Y68" s="100"/>
-      <c r="Z68" s="100"/>
-      <c r="AA68" s="100"/>
-      <c r="AB68" s="100"/>
-      <c r="AC68" s="100"/>
-      <c r="AD68" s="100"/>
-      <c r="AE68" s="100"/>
-      <c r="AF68" s="100"/>
-      <c r="AG68" s="100"/>
-      <c r="AH68" s="100"/>
-      <c r="AI68" s="100"/>
+      <c r="T68" s="32"/>
+      <c r="U68" s="32"/>
+      <c r="V68" s="32"/>
+      <c r="W68" s="32"/>
+      <c r="X68" s="50"/>
+      <c r="Y68" s="50"/>
+      <c r="Z68" s="50"/>
+      <c r="AA68" s="50"/>
+      <c r="AB68" s="50"/>
+      <c r="AC68" s="50"/>
+      <c r="AD68" s="50"/>
+      <c r="AE68" s="50"/>
+      <c r="AF68" s="50"/>
+      <c r="AG68" s="50"/>
+      <c r="AH68" s="50"/>
+      <c r="AI68" s="50"/>
       <c r="AJ68" s="8"/>
     </row>
     <row r="69" spans="2:36" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4414,175 +4420,38 @@
       <c r="AJ69" s="25"/>
     </row>
     <row r="70" spans="2:36" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="AE70" s="101" t="s">
+      <c r="AE70" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="AF70" s="101"/>
-      <c r="AG70" s="101"/>
-      <c r="AH70" s="101"/>
-      <c r="AI70" s="101"/>
-      <c r="AJ70" s="101"/>
+      <c r="AF70" s="26"/>
+      <c r="AG70" s="26"/>
+      <c r="AH70" s="26"/>
+      <c r="AI70" s="26"/>
+      <c r="AJ70" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="202">
-    <mergeCell ref="AE70:AJ70"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:L67"/>
-    <mergeCell ref="M67:R67"/>
-    <mergeCell ref="S67:W67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="H68:L68"/>
-    <mergeCell ref="M68:R68"/>
-    <mergeCell ref="S68:W68"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H62:L62"/>
-    <mergeCell ref="M62:R62"/>
-    <mergeCell ref="S62:W62"/>
-    <mergeCell ref="X62:AI62"/>
-    <mergeCell ref="C63:G66"/>
-    <mergeCell ref="H63:L66"/>
-    <mergeCell ref="M63:R66"/>
-    <mergeCell ref="S63:W66"/>
-    <mergeCell ref="X63:AI68"/>
-    <mergeCell ref="AA40:AC40"/>
-    <mergeCell ref="AD40:AI40"/>
-    <mergeCell ref="C41:AI49"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H60:AD60"/>
-    <mergeCell ref="H61:AD61"/>
-    <mergeCell ref="X39:Z39"/>
-    <mergeCell ref="AA39:AC39"/>
-    <mergeCell ref="AD39:AI39"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="L40:N40"/>
-    <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="U40:W40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="O39:Q39"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="U39:W39"/>
-    <mergeCell ref="D38:G38"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="R38:T38"/>
-    <mergeCell ref="U38:W38"/>
-    <mergeCell ref="X38:Z38"/>
-    <mergeCell ref="AA38:AC38"/>
-    <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="U37:W37"/>
-    <mergeCell ref="X37:Z37"/>
-    <mergeCell ref="AA37:AC37"/>
-    <mergeCell ref="AD37:AI37"/>
-    <mergeCell ref="X35:Z35"/>
-    <mergeCell ref="AA35:AC35"/>
-    <mergeCell ref="AD35:AI35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="R36:T36"/>
-    <mergeCell ref="U36:W36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="R35:T35"/>
-    <mergeCell ref="U35:W35"/>
-    <mergeCell ref="AA36:AC36"/>
-    <mergeCell ref="AD36:AI36"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="R34:T34"/>
-    <mergeCell ref="U34:W34"/>
-    <mergeCell ref="X34:Z34"/>
-    <mergeCell ref="AA34:AC34"/>
-    <mergeCell ref="AD34:AI34"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="O33:Q33"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="X33:Z33"/>
-    <mergeCell ref="AA33:AC33"/>
-    <mergeCell ref="AD33:AI33"/>
-    <mergeCell ref="X31:Z31"/>
-    <mergeCell ref="AA31:AC31"/>
-    <mergeCell ref="AD31:AI31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="U31:W31"/>
-    <mergeCell ref="AA32:AC32"/>
-    <mergeCell ref="AD32:AI32"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="H30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AI30"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="H29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="U29:W29"/>
-    <mergeCell ref="X29:Z29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AI29"/>
-    <mergeCell ref="X27:Z27"/>
-    <mergeCell ref="AA27:AC27"/>
-    <mergeCell ref="AD27:AI27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="H28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="U28:W28"/>
-    <mergeCell ref="X28:Z28"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="H27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="U27:W27"/>
-    <mergeCell ref="AA28:AC28"/>
-    <mergeCell ref="AD28:AI28"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="U26:W26"/>
-    <mergeCell ref="X26:Z26"/>
-    <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="B2:G5"/>
+    <mergeCell ref="H2:AJ5"/>
+    <mergeCell ref="B6:AJ6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="S8:Y8"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="S12:Y12"/>
+    <mergeCell ref="AA12:AI17"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="S9:Y9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="S10:Y10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="S11:Y11"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="R24:T24"/>
@@ -4606,27 +4475,164 @@
     <mergeCell ref="U25:W25"/>
     <mergeCell ref="X25:Z25"/>
     <mergeCell ref="AA25:AC25"/>
-    <mergeCell ref="B2:G5"/>
-    <mergeCell ref="H2:AJ5"/>
-    <mergeCell ref="B6:AJ6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="S7:Y7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="S8:Y8"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="S12:Y12"/>
-    <mergeCell ref="AA12:AI17"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="S9:Y9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="S10:Y10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="U26:W26"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="AA26:AC26"/>
+    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AC27"/>
+    <mergeCell ref="AD27:AI27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="H28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="U28:W28"/>
+    <mergeCell ref="X28:Z28"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="AA28:AC28"/>
+    <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="U29:W29"/>
+    <mergeCell ref="X29:Z29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="H30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AI30"/>
+    <mergeCell ref="X31:Z31"/>
+    <mergeCell ref="AA31:AC31"/>
+    <mergeCell ref="AD31:AI31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="AA32:AC32"/>
+    <mergeCell ref="AD32:AI32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="X33:Z33"/>
+    <mergeCell ref="AA33:AC33"/>
+    <mergeCell ref="AD33:AI33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="R34:T34"/>
+    <mergeCell ref="U34:W34"/>
+    <mergeCell ref="X34:Z34"/>
+    <mergeCell ref="AA34:AC34"/>
+    <mergeCell ref="AD34:AI34"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AI35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AI36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="AA37:AC37"/>
+    <mergeCell ref="AD37:AI37"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="R38:T38"/>
+    <mergeCell ref="U38:W38"/>
+    <mergeCell ref="X38:Z38"/>
+    <mergeCell ref="AA38:AC38"/>
+    <mergeCell ref="AD38:AI38"/>
+    <mergeCell ref="AA40:AC40"/>
+    <mergeCell ref="AD40:AI40"/>
+    <mergeCell ref="C41:AI49"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H60:AD60"/>
+    <mergeCell ref="H61:AD61"/>
+    <mergeCell ref="X39:Z39"/>
+    <mergeCell ref="AA39:AC39"/>
+    <mergeCell ref="AD39:AI39"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="U40:W40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="O39:Q39"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H62:L62"/>
+    <mergeCell ref="M62:R62"/>
+    <mergeCell ref="S62:W62"/>
+    <mergeCell ref="X62:AI62"/>
+    <mergeCell ref="C63:G66"/>
+    <mergeCell ref="H63:L66"/>
+    <mergeCell ref="M63:R66"/>
+    <mergeCell ref="S63:W66"/>
+    <mergeCell ref="X63:AI68"/>
+    <mergeCell ref="AE70:AJ70"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M67:R67"/>
+    <mergeCell ref="S67:W67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="H68:L68"/>
+    <mergeCell ref="M68:R68"/>
+    <mergeCell ref="S68:W68"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.23999999999999996" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
+++ b/public/assets/templates/template_kalibrasi_pressure_sertifikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62395034-1B36-4B65-B877-16786BBD1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C12936-B533-4E43-BDA6-8E12346D8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{D57B88DC-6A9D-42A6-BE16-0F559C48DA93}"/>
   </bookViews>
@@ -204,9 +204,11 @@
     <t>Limits of Permissible Error</t>
   </si>
   <si>
+    <t>Jika tanda koreksi adalah  negatif (-) harus dikurangi pada pembacaan skala untuk menghasilkan nilai sebenarnya koreksi terbesar skala timbangan dan ketidakpastian terbesar</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Diadopsi dari : "The Expression of Uncertainty and Confidence in Measurement"
-</t>
+      <t xml:space="preserve">Diadopsi dari : "The Expression of Uncertainty and Confidence in Measurement" </t>
     </r>
     <r>
       <rPr>
@@ -217,9 +219,6 @@
       </rPr>
       <t>Oleh UKAS (United Kingdom Accreditation Service) M3003, Edition 3, November 2012</t>
     </r>
-  </si>
-  <si>
-    <t>Jika tanda koreksi adalah  negatif (-) harus dikurangi pada pembacaan skala untuk menghasilkan nilai sebenarnya koreksi terbesar skala timbangan dan ketidakpastian terbesar</t>
   </si>
 </sst>
 </file>
@@ -676,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -730,6 +729,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -784,8 +786,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -886,23 +888,77 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -919,77 +975,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1489,7 +1485,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>195263</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>184149</xdr:rowOff>
     </xdr:to>
@@ -1893,336 +1889,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66F67F8-F903-4543-8520-5317DB0C63E4}">
   <dimension ref="B1:AM70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="3.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="36" width="3.90625" style="1" customWidth="1"/>
-    <col min="37" max="257" width="9" style="1"/>
-    <col min="258" max="292" width="3.90625" style="1" customWidth="1"/>
-    <col min="293" max="513" width="9" style="1"/>
-    <col min="514" max="548" width="3.90625" style="1" customWidth="1"/>
-    <col min="549" max="769" width="9" style="1"/>
-    <col min="770" max="804" width="3.90625" style="1" customWidth="1"/>
-    <col min="805" max="1025" width="9" style="1"/>
-    <col min="1026" max="1060" width="3.90625" style="1" customWidth="1"/>
-    <col min="1061" max="1281" width="9" style="1"/>
-    <col min="1282" max="1316" width="3.90625" style="1" customWidth="1"/>
-    <col min="1317" max="1537" width="9" style="1"/>
-    <col min="1538" max="1572" width="3.90625" style="1" customWidth="1"/>
-    <col min="1573" max="1793" width="9" style="1"/>
-    <col min="1794" max="1828" width="3.90625" style="1" customWidth="1"/>
-    <col min="1829" max="2049" width="9" style="1"/>
-    <col min="2050" max="2084" width="3.90625" style="1" customWidth="1"/>
-    <col min="2085" max="2305" width="9" style="1"/>
-    <col min="2306" max="2340" width="3.90625" style="1" customWidth="1"/>
-    <col min="2341" max="2561" width="9" style="1"/>
-    <col min="2562" max="2596" width="3.90625" style="1" customWidth="1"/>
-    <col min="2597" max="2817" width="9" style="1"/>
-    <col min="2818" max="2852" width="3.90625" style="1" customWidth="1"/>
-    <col min="2853" max="3073" width="9" style="1"/>
-    <col min="3074" max="3108" width="3.90625" style="1" customWidth="1"/>
-    <col min="3109" max="3329" width="9" style="1"/>
-    <col min="3330" max="3364" width="3.90625" style="1" customWidth="1"/>
-    <col min="3365" max="3585" width="9" style="1"/>
-    <col min="3586" max="3620" width="3.90625" style="1" customWidth="1"/>
-    <col min="3621" max="3841" width="9" style="1"/>
-    <col min="3842" max="3876" width="3.90625" style="1" customWidth="1"/>
-    <col min="3877" max="4097" width="9" style="1"/>
-    <col min="4098" max="4132" width="3.90625" style="1" customWidth="1"/>
-    <col min="4133" max="4353" width="9" style="1"/>
-    <col min="4354" max="4388" width="3.90625" style="1" customWidth="1"/>
-    <col min="4389" max="4609" width="9" style="1"/>
-    <col min="4610" max="4644" width="3.90625" style="1" customWidth="1"/>
-    <col min="4645" max="4865" width="9" style="1"/>
-    <col min="4866" max="4900" width="3.90625" style="1" customWidth="1"/>
-    <col min="4901" max="5121" width="9" style="1"/>
-    <col min="5122" max="5156" width="3.90625" style="1" customWidth="1"/>
-    <col min="5157" max="5377" width="9" style="1"/>
-    <col min="5378" max="5412" width="3.90625" style="1" customWidth="1"/>
-    <col min="5413" max="5633" width="9" style="1"/>
-    <col min="5634" max="5668" width="3.90625" style="1" customWidth="1"/>
-    <col min="5669" max="5889" width="9" style="1"/>
-    <col min="5890" max="5924" width="3.90625" style="1" customWidth="1"/>
-    <col min="5925" max="6145" width="9" style="1"/>
-    <col min="6146" max="6180" width="3.90625" style="1" customWidth="1"/>
-    <col min="6181" max="6401" width="9" style="1"/>
-    <col min="6402" max="6436" width="3.90625" style="1" customWidth="1"/>
-    <col min="6437" max="6657" width="9" style="1"/>
-    <col min="6658" max="6692" width="3.90625" style="1" customWidth="1"/>
-    <col min="6693" max="6913" width="9" style="1"/>
-    <col min="6914" max="6948" width="3.90625" style="1" customWidth="1"/>
-    <col min="6949" max="7169" width="9" style="1"/>
-    <col min="7170" max="7204" width="3.90625" style="1" customWidth="1"/>
-    <col min="7205" max="7425" width="9" style="1"/>
-    <col min="7426" max="7460" width="3.90625" style="1" customWidth="1"/>
-    <col min="7461" max="7681" width="9" style="1"/>
-    <col min="7682" max="7716" width="3.90625" style="1" customWidth="1"/>
-    <col min="7717" max="7937" width="9" style="1"/>
-    <col min="7938" max="7972" width="3.90625" style="1" customWidth="1"/>
-    <col min="7973" max="8193" width="9" style="1"/>
-    <col min="8194" max="8228" width="3.90625" style="1" customWidth="1"/>
-    <col min="8229" max="8449" width="9" style="1"/>
-    <col min="8450" max="8484" width="3.90625" style="1" customWidth="1"/>
-    <col min="8485" max="8705" width="9" style="1"/>
-    <col min="8706" max="8740" width="3.90625" style="1" customWidth="1"/>
-    <col min="8741" max="8961" width="9" style="1"/>
-    <col min="8962" max="8996" width="3.90625" style="1" customWidth="1"/>
-    <col min="8997" max="9217" width="9" style="1"/>
-    <col min="9218" max="9252" width="3.90625" style="1" customWidth="1"/>
-    <col min="9253" max="9473" width="9" style="1"/>
-    <col min="9474" max="9508" width="3.90625" style="1" customWidth="1"/>
-    <col min="9509" max="9729" width="9" style="1"/>
-    <col min="9730" max="9764" width="3.90625" style="1" customWidth="1"/>
-    <col min="9765" max="9985" width="9" style="1"/>
-    <col min="9986" max="10020" width="3.90625" style="1" customWidth="1"/>
-    <col min="10021" max="10241" width="9" style="1"/>
-    <col min="10242" max="10276" width="3.90625" style="1" customWidth="1"/>
-    <col min="10277" max="10497" width="9" style="1"/>
-    <col min="10498" max="10532" width="3.90625" style="1" customWidth="1"/>
-    <col min="10533" max="10753" width="9" style="1"/>
-    <col min="10754" max="10788" width="3.90625" style="1" customWidth="1"/>
-    <col min="10789" max="11009" width="9" style="1"/>
-    <col min="11010" max="11044" width="3.90625" style="1" customWidth="1"/>
-    <col min="11045" max="11265" width="9" style="1"/>
-    <col min="11266" max="11300" width="3.90625" style="1" customWidth="1"/>
-    <col min="11301" max="11521" width="9" style="1"/>
-    <col min="11522" max="11556" width="3.90625" style="1" customWidth="1"/>
-    <col min="11557" max="11777" width="9" style="1"/>
-    <col min="11778" max="11812" width="3.90625" style="1" customWidth="1"/>
-    <col min="11813" max="12033" width="9" style="1"/>
-    <col min="12034" max="12068" width="3.90625" style="1" customWidth="1"/>
-    <col min="12069" max="12289" width="9" style="1"/>
-    <col min="12290" max="12324" width="3.90625" style="1" customWidth="1"/>
-    <col min="12325" max="12545" width="9" style="1"/>
-    <col min="12546" max="12580" width="3.90625" style="1" customWidth="1"/>
-    <col min="12581" max="12801" width="9" style="1"/>
-    <col min="12802" max="12836" width="3.90625" style="1" customWidth="1"/>
-    <col min="12837" max="13057" width="9" style="1"/>
-    <col min="13058" max="13092" width="3.90625" style="1" customWidth="1"/>
-    <col min="13093" max="13313" width="9" style="1"/>
-    <col min="13314" max="13348" width="3.90625" style="1" customWidth="1"/>
-    <col min="13349" max="13569" width="9" style="1"/>
-    <col min="13570" max="13604" width="3.90625" style="1" customWidth="1"/>
-    <col min="13605" max="13825" width="9" style="1"/>
-    <col min="13826" max="13860" width="3.90625" style="1" customWidth="1"/>
-    <col min="13861" max="14081" width="9" style="1"/>
-    <col min="14082" max="14116" width="3.90625" style="1" customWidth="1"/>
-    <col min="14117" max="14337" width="9" style="1"/>
-    <col min="14338" max="14372" width="3.90625" style="1" customWidth="1"/>
-    <col min="14373" max="14593" width="9" style="1"/>
-    <col min="14594" max="14628" width="3.90625" style="1" customWidth="1"/>
-    <col min="14629" max="14849" width="9" style="1"/>
-    <col min="14850" max="14884" width="3.90625" style="1" customWidth="1"/>
-    <col min="14885" max="15105" width="9" style="1"/>
-    <col min="15106" max="15140" width="3.90625" style="1" customWidth="1"/>
-    <col min="15141" max="15361" width="9" style="1"/>
-    <col min="15362" max="15396" width="3.90625" style="1" customWidth="1"/>
-    <col min="15397" max="15617" width="9" style="1"/>
-    <col min="15618" max="15652" width="3.90625" style="1" customWidth="1"/>
-    <col min="15653" max="15873" width="9" style="1"/>
-    <col min="15874" max="15908" width="3.90625" style="1" customWidth="1"/>
-    <col min="15909" max="16129" width="9" style="1"/>
-    <col min="16130" max="16164" width="3.90625" style="1" customWidth="1"/>
-    <col min="16165" max="16384" width="9" style="1"/>
+    <col min="1" max="16384" width="3.54296875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:39" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:39" ht="19" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="32" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="34"/>
+      <c r="AC2" s="34"/>
+      <c r="AD2" s="34"/>
+      <c r="AE2" s="34"/>
+      <c r="AF2" s="34"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="34"/>
+      <c r="AI2" s="34"/>
+      <c r="AJ2" s="35"/>
     </row>
     <row r="3" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="26"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="36"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="37"/>
     </row>
     <row r="4" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="36"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="37"/>
     </row>
     <row r="5" spans="2:39" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="37"/>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="37"/>
-      <c r="AG5" s="37"/>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="37"/>
-      <c r="AJ5" s="38"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="38"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="38"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="39"/>
     </row>
     <row r="6" spans="2:39" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="39"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="40"/>
     </row>
     <row r="7" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="4" t="s">
         <v>2</v>
       </c>
@@ -2236,15 +2104,15 @@
       <c r="P7" s="106"/>
       <c r="Q7" s="106"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="41" t="s">
+      <c r="S7" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="T7" s="41"/>
-      <c r="U7" s="41"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="41"/>
-      <c r="X7" s="41"/>
-      <c r="Y7" s="41"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
       <c r="Z7" s="6" t="s">
         <v>2</v>
       </c>
@@ -2260,309 +2128,309 @@
       <c r="AJ7" s="8"/>
     </row>
     <row r="8" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="105"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="105"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="105"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="41" t="s">
+      <c r="S8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="41"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
       <c r="Z8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA8" s="105"/>
-      <c r="AB8" s="105"/>
-      <c r="AC8" s="105"/>
-      <c r="AD8" s="105"/>
-      <c r="AE8" s="105"/>
-      <c r="AF8" s="105"/>
-      <c r="AG8" s="105"/>
-      <c r="AH8" s="105"/>
-      <c r="AI8" s="105"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="23"/>
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
       <c r="AJ8" s="8"/>
     </row>
     <row r="9" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="41" t="s">
+      <c r="S9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="41"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
       <c r="Z9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="105"/>
-      <c r="AC9" s="105"/>
-      <c r="AD9" s="105"/>
-      <c r="AE9" s="105"/>
-      <c r="AF9" s="105"/>
-      <c r="AG9" s="105"/>
-      <c r="AH9" s="105"/>
-      <c r="AI9" s="105"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="23"/>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="10"/>
       <c r="AL9" s="10"/>
       <c r="AM9" s="10"/>
     </row>
     <row r="10" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="105"/>
-      <c r="M10" s="105"/>
-      <c r="N10" s="105"/>
-      <c r="O10" s="105"/>
-      <c r="P10" s="105"/>
-      <c r="Q10" s="105"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="41" t="s">
+      <c r="S10" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="41"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
       <c r="Z10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA10" s="104"/>
-      <c r="AB10" s="104"/>
-      <c r="AC10" s="104"/>
-      <c r="AD10" s="104"/>
-      <c r="AE10" s="104"/>
-      <c r="AF10" s="104"/>
-      <c r="AG10" s="104"/>
-      <c r="AH10" s="104"/>
-      <c r="AI10" s="104"/>
+      <c r="AA10" s="107"/>
+      <c r="AB10" s="107"/>
+      <c r="AC10" s="107"/>
+      <c r="AD10" s="107"/>
+      <c r="AE10" s="107"/>
+      <c r="AF10" s="107"/>
+      <c r="AG10" s="107"/>
+      <c r="AH10" s="107"/>
+      <c r="AI10" s="107"/>
       <c r="AJ10" s="9"/>
       <c r="AK10" s="10"/>
       <c r="AL10" s="10"/>
       <c r="AM10" s="10"/>
     </row>
     <row r="11" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
       <c r="H11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="105"/>
-      <c r="M11" s="105"/>
-      <c r="N11" s="105"/>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="41" t="s">
+      <c r="S11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="41"/>
-      <c r="X11" s="41"/>
-      <c r="Y11" s="41"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
       <c r="Z11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA11" s="104"/>
-      <c r="AB11" s="104"/>
-      <c r="AC11" s="104"/>
-      <c r="AD11" s="104"/>
-      <c r="AE11" s="104"/>
-      <c r="AF11" s="104"/>
-      <c r="AG11" s="104"/>
-      <c r="AH11" s="104"/>
-      <c r="AI11" s="104"/>
+      <c r="AA11" s="107"/>
+      <c r="AB11" s="107"/>
+      <c r="AC11" s="107"/>
+      <c r="AD11" s="107"/>
+      <c r="AE11" s="107"/>
+      <c r="AF11" s="107"/>
+      <c r="AG11" s="107"/>
+      <c r="AH11" s="107"/>
+      <c r="AI11" s="107"/>
       <c r="AJ11" s="9"/>
       <c r="AK11" s="10"/>
       <c r="AL11" s="10"/>
       <c r="AM11" s="10"/>
     </row>
     <row r="12" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
       <c r="H12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
-      <c r="M12" s="105"/>
-      <c r="N12" s="105"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="105"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="41" t="s">
+      <c r="S12" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="41"/>
-      <c r="X12" s="41"/>
-      <c r="Y12" s="41"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
       <c r="Z12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="103" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB12" s="103"/>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="103"/>
-      <c r="AE12" s="103"/>
-      <c r="AF12" s="103"/>
-      <c r="AG12" s="103"/>
-      <c r="AH12" s="103"/>
-      <c r="AI12" s="103"/>
+      <c r="AA12" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="42"/>
+      <c r="AD12" s="42"/>
+      <c r="AE12" s="42"/>
+      <c r="AF12" s="42"/>
+      <c r="AG12" s="42"/>
+      <c r="AH12" s="42"/>
+      <c r="AI12" s="42"/>
       <c r="AJ12" s="9"/>
       <c r="AK12" s="10"/>
       <c r="AL12" s="10"/>
       <c r="AM12" s="10"/>
     </row>
     <row r="13" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
       <c r="R13" s="5"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="103"/>
-      <c r="AB13" s="103"/>
-      <c r="AC13" s="103"/>
-      <c r="AD13" s="103"/>
-      <c r="AE13" s="103"/>
-      <c r="AF13" s="103"/>
-      <c r="AG13" s="103"/>
-      <c r="AH13" s="103"/>
-      <c r="AI13" s="103"/>
+      <c r="AA13" s="42"/>
+      <c r="AB13" s="42"/>
+      <c r="AC13" s="42"/>
+      <c r="AD13" s="42"/>
+      <c r="AE13" s="42"/>
+      <c r="AF13" s="42"/>
+      <c r="AG13" s="42"/>
+      <c r="AH13" s="42"/>
+      <c r="AI13" s="42"/>
       <c r="AJ13" s="9"/>
       <c r="AK13" s="10"/>
       <c r="AL13" s="10"/>
       <c r="AM13" s="10"/>
     </row>
     <row r="14" spans="2:39" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
-      <c r="N14" s="105"/>
-      <c r="O14" s="105"/>
-      <c r="P14" s="105"/>
-      <c r="Q14" s="105"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5"/>
@@ -2572,41 +2440,41 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
-      <c r="AA14" s="103"/>
-      <c r="AB14" s="103"/>
-      <c r="AC14" s="103"/>
-      <c r="AD14" s="103"/>
-      <c r="AE14" s="103"/>
-      <c r="AF14" s="103"/>
-      <c r="AG14" s="103"/>
-      <c r="AH14" s="103"/>
-      <c r="AI14" s="103"/>
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="42"/>
+      <c r="AF14" s="42"/>
+      <c r="AG14" s="42"/>
+      <c r="AH14" s="42"/>
+      <c r="AI14" s="42"/>
       <c r="AJ14" s="9"/>
       <c r="AK14" s="11"/>
       <c r="AL14" s="11"/>
       <c r="AM14" s="11"/>
     </row>
     <row r="15" spans="2:39" x14ac:dyDescent="0.35">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5"/>
@@ -2616,38 +2484,38 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
-      <c r="AA15" s="103"/>
-      <c r="AB15" s="103"/>
-      <c r="AC15" s="103"/>
-      <c r="AD15" s="103"/>
-      <c r="AE15" s="103"/>
-      <c r="AF15" s="103"/>
-      <c r="AG15" s="103"/>
-      <c r="AH15" s="103"/>
-      <c r="AI15" s="103"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="42"/>
+      <c r="AG15" s="42"/>
+      <c r="AH15" s="42"/>
+      <c r="AI15" s="42"/>
       <c r="AJ15" s="8"/>
     </row>
     <row r="16" spans="2:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="105"/>
-      <c r="N16" s="105"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="105"/>
-      <c r="Q16" s="105"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5"/>
@@ -2657,38 +2525,38 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
-      <c r="AA16" s="103"/>
-      <c r="AB16" s="103"/>
-      <c r="AC16" s="103"/>
-      <c r="AD16" s="103"/>
-      <c r="AE16" s="103"/>
-      <c r="AF16" s="103"/>
-      <c r="AG16" s="103"/>
-      <c r="AH16" s="103"/>
-      <c r="AI16" s="103"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="42"/>
+      <c r="AD16" s="42"/>
+      <c r="AE16" s="42"/>
+      <c r="AF16" s="42"/>
+      <c r="AG16" s="42"/>
+      <c r="AH16" s="42"/>
+      <c r="AI16" s="42"/>
       <c r="AJ16" s="8"/>
     </row>
     <row r="17" spans="2:36" x14ac:dyDescent="0.35">
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
       <c r="H17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="107"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="107"/>
-      <c r="M17" s="107"/>
-      <c r="N17" s="107"/>
-      <c r="O17" s="107"/>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="107"/>
+      <c r="I17" s="108"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5"/>
@@ -2698,53 +2566,53 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
-      <c r="AA17" s="103"/>
-      <c r="AB17" s="103"/>
-      <c r="AC17" s="103"/>
-      <c r="AD17" s="103"/>
-      <c r="AE17" s="103"/>
-      <c r="AF17" s="103"/>
-      <c r="AG17" s="103"/>
-      <c r="AH17" s="103"/>
-      <c r="AI17" s="103"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
       <c r="AJ17" s="8"/>
     </row>
     <row r="18" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="43"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="44"/>
-      <c r="S18" s="44"/>
-      <c r="T18" s="44"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="44"/>
-      <c r="W18" s="44"/>
-      <c r="X18" s="44"/>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="44"/>
-      <c r="AB18" s="44"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="44"/>
-      <c r="AE18" s="44"/>
-      <c r="AF18" s="44"/>
-      <c r="AG18" s="44"/>
-      <c r="AH18" s="44"/>
-      <c r="AI18" s="44"/>
-      <c r="AJ18" s="45"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="45"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="45"/>
+      <c r="U18" s="45"/>
+      <c r="V18" s="45"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="45"/>
+      <c r="Y18" s="45"/>
+      <c r="Z18" s="45"/>
+      <c r="AA18" s="45"/>
+      <c r="AB18" s="45"/>
+      <c r="AC18" s="45"/>
+      <c r="AD18" s="45"/>
+      <c r="AE18" s="45"/>
+      <c r="AF18" s="45"/>
+      <c r="AG18" s="45"/>
+      <c r="AH18" s="45"/>
+      <c r="AI18" s="45"/>
+      <c r="AJ18" s="46"/>
     </row>
     <row r="19" spans="2:36" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="2"/>
@@ -2762,14 +2630,14 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="12"/>
-      <c r="Q19" s="46" t="s">
+      <c r="Q19" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
       <c r="W19" s="12"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
@@ -2791,229 +2659,229 @@
     </row>
     <row r="21" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="14"/>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="51" t="s">
+      <c r="D21" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="60" t="s">
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60" t="s">
+      <c r="M21" s="61"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="61"/>
+      <c r="P21" s="61"/>
+      <c r="Q21" s="61"/>
+      <c r="R21" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="S21" s="60"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="60"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="61" t="s">
+      <c r="S21" s="61"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="61"/>
+      <c r="V21" s="61"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="Y21" s="61"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="61"/>
-      <c r="AB21" s="61"/>
-      <c r="AC21" s="61"/>
-      <c r="AD21" s="51" t="s">
+      <c r="Y21" s="62"/>
+      <c r="Z21" s="62"/>
+      <c r="AA21" s="62"/>
+      <c r="AB21" s="62"/>
+      <c r="AC21" s="62"/>
+      <c r="AD21" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="AE21" s="52"/>
-      <c r="AF21" s="52"/>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="52"/>
-      <c r="AI21" s="53"/>
+      <c r="AE21" s="53"/>
+      <c r="AF21" s="53"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="53"/>
+      <c r="AI21" s="54"/>
       <c r="AJ21" s="8"/>
     </row>
     <row r="22" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="14"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="55"/>
-      <c r="K22" s="56"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="60"/>
-      <c r="T22" s="60"/>
-      <c r="U22" s="60"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="61"/>
-      <c r="Z22" s="61"/>
-      <c r="AA22" s="61"/>
-      <c r="AB22" s="61"/>
-      <c r="AC22" s="61"/>
-      <c r="AD22" s="54"/>
-      <c r="AE22" s="55"/>
-      <c r="AF22" s="55"/>
-      <c r="AG22" s="55"/>
-      <c r="AH22" s="55"/>
-      <c r="AI22" s="56"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="61"/>
+      <c r="Q22" s="61"/>
+      <c r="R22" s="61"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="62"/>
+      <c r="AB22" s="62"/>
+      <c r="AC22" s="62"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="56"/>
+      <c r="AG22" s="56"/>
+      <c r="AH22" s="56"/>
+      <c r="AI22" s="57"/>
       <c r="AJ22" s="8"/>
     </row>
     <row r="23" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="14"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="60"/>
-      <c r="T23" s="60"/>
-      <c r="U23" s="60"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
-      <c r="Z23" s="61"/>
-      <c r="AA23" s="61"/>
-      <c r="AB23" s="61"/>
-      <c r="AC23" s="61"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="55"/>
-      <c r="AF23" s="55"/>
-      <c r="AG23" s="55"/>
-      <c r="AH23" s="55"/>
-      <c r="AI23" s="56"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="61"/>
+      <c r="O23" s="61"/>
+      <c r="P23" s="61"/>
+      <c r="Q23" s="61"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="61"/>
+      <c r="U23" s="61"/>
+      <c r="V23" s="61"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
+      <c r="Z23" s="62"/>
+      <c r="AA23" s="62"/>
+      <c r="AB23" s="62"/>
+      <c r="AC23" s="62"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="56"/>
+      <c r="AF23" s="56"/>
+      <c r="AG23" s="56"/>
+      <c r="AH23" s="56"/>
+      <c r="AI23" s="57"/>
       <c r="AJ23" s="8"/>
     </row>
     <row r="24" spans="2:36" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="14"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="62" t="s">
+      <c r="C24" s="50"/>
+      <c r="D24" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="62" t="s">
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="63"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="42" t="s">
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42" t="s">
+      <c r="M24" s="43"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42" t="s">
+      <c r="P24" s="43"/>
+      <c r="Q24" s="43"/>
+      <c r="R24" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="S24" s="42"/>
-      <c r="T24" s="42"/>
-      <c r="U24" s="42" t="s">
+      <c r="S24" s="43"/>
+      <c r="T24" s="43"/>
+      <c r="U24" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="V24" s="42"/>
-      <c r="W24" s="42"/>
-      <c r="X24" s="42" t="s">
+      <c r="V24" s="43"/>
+      <c r="W24" s="43"/>
+      <c r="X24" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="Y24" s="42"/>
-      <c r="Z24" s="42"/>
-      <c r="AA24" s="42" t="s">
+      <c r="Y24" s="43"/>
+      <c r="Z24" s="43"/>
+      <c r="AA24" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="AB24" s="42"/>
-      <c r="AC24" s="42"/>
-      <c r="AD24" s="54"/>
-      <c r="AE24" s="55"/>
-      <c r="AF24" s="55"/>
-      <c r="AG24" s="55"/>
-      <c r="AH24" s="55"/>
-      <c r="AI24" s="56"/>
+      <c r="AB24" s="43"/>
+      <c r="AC24" s="43"/>
+      <c r="AD24" s="55"/>
+      <c r="AE24" s="56"/>
+      <c r="AF24" s="56"/>
+      <c r="AG24" s="56"/>
+      <c r="AH24" s="56"/>
+      <c r="AI24" s="57"/>
       <c r="AJ24" s="8"/>
     </row>
     <row r="25" spans="2:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="14"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="67"/>
-      <c r="L25" s="68" t="s">
+      <c r="C25" s="51"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="68"/>
+      <c r="L25" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-      <c r="O25" s="50" t="s">
+      <c r="M25" s="69"/>
+      <c r="N25" s="69"/>
+      <c r="O25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50" t="s">
+      <c r="P25" s="51"/>
+      <c r="Q25" s="51"/>
+      <c r="R25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="50" t="s">
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="V25" s="50"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="50" t="s">
+      <c r="V25" s="51"/>
+      <c r="W25" s="51"/>
+      <c r="X25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Y25" s="50"/>
-      <c r="Z25" s="50"/>
-      <c r="AA25" s="50" t="s">
+      <c r="Y25" s="51"/>
+      <c r="Z25" s="51"/>
+      <c r="AA25" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AB25" s="50"/>
-      <c r="AC25" s="50"/>
-      <c r="AD25" s="65" t="s">
+      <c r="AB25" s="51"/>
+      <c r="AC25" s="51"/>
+      <c r="AD25" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="67"/>
+      <c r="AE25" s="67"/>
+      <c r="AF25" s="67"/>
+      <c r="AG25" s="67"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="68"/>
       <c r="AJ25" s="8"/>
     </row>
     <row r="26" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3021,38 +2889,38 @@
       <c r="C26" s="15">
         <v>1</v>
       </c>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="69"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="69"/>
-      <c r="P26" s="69"/>
-      <c r="Q26" s="69"/>
-      <c r="R26" s="69"/>
-      <c r="S26" s="69"/>
-      <c r="T26" s="69"/>
-      <c r="U26" s="69"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="69"/>
-      <c r="X26" s="69"/>
-      <c r="Y26" s="69"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="69"/>
-      <c r="AB26" s="69"/>
-      <c r="AC26" s="69"/>
-      <c r="AD26" s="70"/>
-      <c r="AE26" s="71"/>
-      <c r="AF26" s="71"/>
-      <c r="AG26" s="71"/>
-      <c r="AH26" s="71"/>
-      <c r="AI26" s="72"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="70"/>
+      <c r="S26" s="70"/>
+      <c r="T26" s="70"/>
+      <c r="U26" s="70"/>
+      <c r="V26" s="70"/>
+      <c r="W26" s="70"/>
+      <c r="X26" s="70"/>
+      <c r="Y26" s="70"/>
+      <c r="Z26" s="70"/>
+      <c r="AA26" s="70"/>
+      <c r="AB26" s="70"/>
+      <c r="AC26" s="70"/>
+      <c r="AD26" s="71"/>
+      <c r="AE26" s="72"/>
+      <c r="AF26" s="72"/>
+      <c r="AG26" s="72"/>
+      <c r="AH26" s="72"/>
+      <c r="AI26" s="73"/>
       <c r="AJ26" s="8"/>
     </row>
     <row r="27" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3060,38 +2928,38 @@
       <c r="C27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="69"/>
-      <c r="L27" s="73"/>
-      <c r="M27" s="73"/>
-      <c r="N27" s="73"/>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="73"/>
-      <c r="R27" s="73"/>
-      <c r="S27" s="73"/>
-      <c r="T27" s="73"/>
-      <c r="U27" s="73"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="73"/>
-      <c r="X27" s="73"/>
-      <c r="Y27" s="73"/>
-      <c r="Z27" s="73"/>
-      <c r="AA27" s="73"/>
-      <c r="AB27" s="73"/>
-      <c r="AC27" s="73"/>
-      <c r="AD27" s="70"/>
-      <c r="AE27" s="71"/>
-      <c r="AF27" s="71"/>
-      <c r="AG27" s="71"/>
-      <c r="AH27" s="71"/>
-      <c r="AI27" s="72"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="74"/>
+      <c r="M27" s="74"/>
+      <c r="N27" s="74"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="74"/>
+      <c r="Q27" s="74"/>
+      <c r="R27" s="74"/>
+      <c r="S27" s="74"/>
+      <c r="T27" s="74"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="74"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="74"/>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="71"/>
+      <c r="AE27" s="72"/>
+      <c r="AF27" s="72"/>
+      <c r="AG27" s="72"/>
+      <c r="AH27" s="72"/>
+      <c r="AI27" s="73"/>
       <c r="AJ27" s="8"/>
     </row>
     <row r="28" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3099,38 +2967,38 @@
       <c r="C28" s="15">
         <v>3</v>
       </c>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="73"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="73"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="73"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="73"/>
-      <c r="S28" s="73"/>
-      <c r="T28" s="73"/>
-      <c r="U28" s="73"/>
-      <c r="V28" s="73"/>
-      <c r="W28" s="73"/>
-      <c r="X28" s="73"/>
-      <c r="Y28" s="73"/>
-      <c r="Z28" s="73"/>
-      <c r="AA28" s="73"/>
-      <c r="AB28" s="73"/>
-      <c r="AC28" s="73"/>
-      <c r="AD28" s="70"/>
-      <c r="AE28" s="71"/>
-      <c r="AF28" s="71"/>
-      <c r="AG28" s="71"/>
-      <c r="AH28" s="71"/>
-      <c r="AI28" s="72"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="74"/>
+      <c r="N28" s="74"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
+      <c r="Q28" s="74"/>
+      <c r="R28" s="74"/>
+      <c r="S28" s="74"/>
+      <c r="T28" s="74"/>
+      <c r="U28" s="74"/>
+      <c r="V28" s="74"/>
+      <c r="W28" s="74"/>
+      <c r="X28" s="74"/>
+      <c r="Y28" s="74"/>
+      <c r="Z28" s="74"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="71"/>
+      <c r="AE28" s="72"/>
+      <c r="AF28" s="72"/>
+      <c r="AG28" s="72"/>
+      <c r="AH28" s="72"/>
+      <c r="AI28" s="73"/>
       <c r="AJ28" s="16"/>
     </row>
     <row r="29" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3138,38 +3006,38 @@
       <c r="C29" s="15">
         <v>4</v>
       </c>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="69"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="69"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="73"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="73"/>
-      <c r="T29" s="73"/>
-      <c r="U29" s="73"/>
-      <c r="V29" s="73"/>
-      <c r="W29" s="73"/>
-      <c r="X29" s="73"/>
-      <c r="Y29" s="73"/>
-      <c r="Z29" s="73"/>
-      <c r="AA29" s="73"/>
-      <c r="AB29" s="73"/>
-      <c r="AC29" s="73"/>
-      <c r="AD29" s="70"/>
-      <c r="AE29" s="71"/>
-      <c r="AF29" s="71"/>
-      <c r="AG29" s="71"/>
-      <c r="AH29" s="71"/>
-      <c r="AI29" s="72"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="74"/>
+      <c r="M29" s="74"/>
+      <c r="N29" s="74"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
+      <c r="U29" s="74"/>
+      <c r="V29" s="74"/>
+      <c r="W29" s="74"/>
+      <c r="X29" s="74"/>
+      <c r="Y29" s="74"/>
+      <c r="Z29" s="74"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="71"/>
+      <c r="AE29" s="72"/>
+      <c r="AF29" s="72"/>
+      <c r="AG29" s="72"/>
+      <c r="AH29" s="72"/>
+      <c r="AI29" s="73"/>
       <c r="AJ29" s="16"/>
     </row>
     <row r="30" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3177,38 +3045,38 @@
       <c r="C30" s="15">
         <v>5</v>
       </c>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="69"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="69"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="73"/>
-      <c r="V30" s="73"/>
-      <c r="W30" s="73"/>
-      <c r="X30" s="73"/>
-      <c r="Y30" s="73"/>
-      <c r="Z30" s="73"/>
-      <c r="AA30" s="74"/>
-      <c r="AB30" s="74"/>
-      <c r="AC30" s="74"/>
-      <c r="AD30" s="70"/>
-      <c r="AE30" s="71"/>
-      <c r="AF30" s="71"/>
-      <c r="AG30" s="71"/>
-      <c r="AH30" s="71"/>
-      <c r="AI30" s="72"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="74"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="74"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="74"/>
+      <c r="Q30" s="74"/>
+      <c r="R30" s="74"/>
+      <c r="S30" s="74"/>
+      <c r="T30" s="74"/>
+      <c r="U30" s="74"/>
+      <c r="V30" s="74"/>
+      <c r="W30" s="74"/>
+      <c r="X30" s="74"/>
+      <c r="Y30" s="74"/>
+      <c r="Z30" s="74"/>
+      <c r="AA30" s="75"/>
+      <c r="AB30" s="75"/>
+      <c r="AC30" s="75"/>
+      <c r="AD30" s="71"/>
+      <c r="AE30" s="72"/>
+      <c r="AF30" s="72"/>
+      <c r="AG30" s="72"/>
+      <c r="AH30" s="72"/>
+      <c r="AI30" s="73"/>
       <c r="AJ30" s="16"/>
     </row>
     <row r="31" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3216,38 +3084,38 @@
       <c r="C31" s="15">
         <v>6</v>
       </c>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="69"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="69"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="73"/>
-      <c r="N31" s="73"/>
-      <c r="O31" s="73"/>
-      <c r="P31" s="73"/>
-      <c r="Q31" s="73"/>
-      <c r="R31" s="73"/>
-      <c r="S31" s="73"/>
-      <c r="T31" s="73"/>
-      <c r="U31" s="73"/>
-      <c r="V31" s="73"/>
-      <c r="W31" s="73"/>
-      <c r="X31" s="73"/>
-      <c r="Y31" s="73"/>
-      <c r="Z31" s="73"/>
-      <c r="AA31" s="73"/>
-      <c r="AB31" s="73"/>
-      <c r="AC31" s="73"/>
-      <c r="AD31" s="70"/>
-      <c r="AE31" s="71"/>
-      <c r="AF31" s="71"/>
-      <c r="AG31" s="71"/>
-      <c r="AH31" s="71"/>
-      <c r="AI31" s="72"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="74"/>
+      <c r="V31" s="74"/>
+      <c r="W31" s="74"/>
+      <c r="X31" s="74"/>
+      <c r="Y31" s="74"/>
+      <c r="Z31" s="74"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="74"/>
+      <c r="AD31" s="71"/>
+      <c r="AE31" s="72"/>
+      <c r="AF31" s="72"/>
+      <c r="AG31" s="72"/>
+      <c r="AH31" s="72"/>
+      <c r="AI31" s="73"/>
       <c r="AJ31" s="16"/>
     </row>
     <row r="32" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3255,38 +3123,38 @@
       <c r="C32" s="15">
         <v>7</v>
       </c>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="U32" s="73"/>
-      <c r="V32" s="73"/>
-      <c r="W32" s="73"/>
-      <c r="X32" s="73"/>
-      <c r="Y32" s="73"/>
-      <c r="Z32" s="73"/>
-      <c r="AA32" s="73"/>
-      <c r="AB32" s="73"/>
-      <c r="AC32" s="73"/>
-      <c r="AD32" s="70"/>
-      <c r="AE32" s="71"/>
-      <c r="AF32" s="71"/>
-      <c r="AG32" s="71"/>
-      <c r="AH32" s="71"/>
-      <c r="AI32" s="72"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="74"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="74"/>
+      <c r="Q32" s="74"/>
+      <c r="R32" s="74"/>
+      <c r="S32" s="74"/>
+      <c r="T32" s="74"/>
+      <c r="U32" s="74"/>
+      <c r="V32" s="74"/>
+      <c r="W32" s="74"/>
+      <c r="X32" s="74"/>
+      <c r="Y32" s="74"/>
+      <c r="Z32" s="74"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="74"/>
+      <c r="AD32" s="71"/>
+      <c r="AE32" s="72"/>
+      <c r="AF32" s="72"/>
+      <c r="AG32" s="72"/>
+      <c r="AH32" s="72"/>
+      <c r="AI32" s="73"/>
       <c r="AJ32" s="8"/>
     </row>
     <row r="33" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3294,38 +3162,38 @@
       <c r="C33" s="15">
         <v>8</v>
       </c>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
-      <c r="K33" s="61"/>
-      <c r="L33" s="73"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="73"/>
-      <c r="O33" s="73"/>
-      <c r="P33" s="73"/>
-      <c r="Q33" s="73"/>
-      <c r="R33" s="73"/>
-      <c r="S33" s="73"/>
-      <c r="T33" s="73"/>
-      <c r="U33" s="73"/>
-      <c r="V33" s="73"/>
-      <c r="W33" s="73"/>
-      <c r="X33" s="73"/>
-      <c r="Y33" s="73"/>
-      <c r="Z33" s="73"/>
-      <c r="AA33" s="73"/>
-      <c r="AB33" s="73"/>
-      <c r="AC33" s="73"/>
-      <c r="AD33" s="70"/>
-      <c r="AE33" s="71"/>
-      <c r="AF33" s="71"/>
-      <c r="AG33" s="71"/>
-      <c r="AH33" s="71"/>
-      <c r="AI33" s="72"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="74"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="74"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
+      <c r="Q33" s="74"/>
+      <c r="R33" s="74"/>
+      <c r="S33" s="74"/>
+      <c r="T33" s="74"/>
+      <c r="U33" s="74"/>
+      <c r="V33" s="74"/>
+      <c r="W33" s="74"/>
+      <c r="X33" s="74"/>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="74"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="74"/>
+      <c r="AD33" s="71"/>
+      <c r="AE33" s="72"/>
+      <c r="AF33" s="72"/>
+      <c r="AG33" s="72"/>
+      <c r="AH33" s="72"/>
+      <c r="AI33" s="73"/>
       <c r="AJ33" s="8"/>
     </row>
     <row r="34" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3333,38 +3201,38 @@
       <c r="C34" s="15">
         <v>9</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
-      <c r="J34" s="61"/>
-      <c r="K34" s="61"/>
-      <c r="L34" s="73"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="73"/>
-      <c r="O34" s="73"/>
-      <c r="P34" s="73"/>
-      <c r="Q34" s="73"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="73"/>
-      <c r="W34" s="73"/>
-      <c r="X34" s="73"/>
-      <c r="Y34" s="73"/>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="73"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="73"/>
-      <c r="AD34" s="70"/>
-      <c r="AE34" s="71"/>
-      <c r="AF34" s="71"/>
-      <c r="AG34" s="71"/>
-      <c r="AH34" s="71"/>
-      <c r="AI34" s="72"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="74"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="74"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="74"/>
+      <c r="Q34" s="74"/>
+      <c r="R34" s="74"/>
+      <c r="S34" s="74"/>
+      <c r="T34" s="74"/>
+      <c r="U34" s="74"/>
+      <c r="V34" s="74"/>
+      <c r="W34" s="74"/>
+      <c r="X34" s="74"/>
+      <c r="Y34" s="74"/>
+      <c r="Z34" s="74"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="74"/>
+      <c r="AC34" s="74"/>
+      <c r="AD34" s="71"/>
+      <c r="AE34" s="72"/>
+      <c r="AF34" s="72"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="72"/>
+      <c r="AI34" s="73"/>
       <c r="AJ34" s="8"/>
     </row>
     <row r="35" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3372,38 +3240,38 @@
       <c r="C35" s="15">
         <v>10</v>
       </c>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
-      <c r="J35" s="61"/>
-      <c r="K35" s="61"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="73"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="73"/>
-      <c r="Q35" s="73"/>
-      <c r="R35" s="73"/>
-      <c r="S35" s="73"/>
-      <c r="T35" s="73"/>
-      <c r="U35" s="73"/>
-      <c r="V35" s="73"/>
-      <c r="W35" s="73"/>
-      <c r="X35" s="73"/>
-      <c r="Y35" s="73"/>
-      <c r="Z35" s="73"/>
-      <c r="AA35" s="73"/>
-      <c r="AB35" s="73"/>
-      <c r="AC35" s="73"/>
-      <c r="AD35" s="70"/>
-      <c r="AE35" s="71"/>
-      <c r="AF35" s="71"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="71"/>
-      <c r="AI35" s="72"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="62"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="74"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="74"/>
+      <c r="P35" s="74"/>
+      <c r="Q35" s="74"/>
+      <c r="R35" s="74"/>
+      <c r="S35" s="74"/>
+      <c r="T35" s="74"/>
+      <c r="U35" s="74"/>
+      <c r="V35" s="74"/>
+      <c r="W35" s="74"/>
+      <c r="X35" s="74"/>
+      <c r="Y35" s="74"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="74"/>
+      <c r="AD35" s="71"/>
+      <c r="AE35" s="72"/>
+      <c r="AF35" s="72"/>
+      <c r="AG35" s="72"/>
+      <c r="AH35" s="72"/>
+      <c r="AI35" s="73"/>
       <c r="AJ35" s="8"/>
     </row>
     <row r="36" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3411,38 +3279,38 @@
       <c r="C36" s="15">
         <v>11</v>
       </c>
-      <c r="D36" s="75"/>
-      <c r="E36" s="75"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="73"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="73"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="73"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="73"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="73"/>
-      <c r="U36" s="73"/>
-      <c r="V36" s="73"/>
-      <c r="W36" s="73"/>
-      <c r="X36" s="73"/>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="73"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="73"/>
-      <c r="AD36" s="70"/>
-      <c r="AE36" s="71"/>
-      <c r="AF36" s="71"/>
-      <c r="AG36" s="71"/>
-      <c r="AH36" s="71"/>
-      <c r="AI36" s="72"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
+      <c r="J36" s="62"/>
+      <c r="K36" s="62"/>
+      <c r="L36" s="74"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="74"/>
+      <c r="O36" s="74"/>
+      <c r="P36" s="74"/>
+      <c r="Q36" s="74"/>
+      <c r="R36" s="74"/>
+      <c r="S36" s="74"/>
+      <c r="T36" s="74"/>
+      <c r="U36" s="74"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="74"/>
+      <c r="X36" s="74"/>
+      <c r="Y36" s="74"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="74"/>
+      <c r="AD36" s="71"/>
+      <c r="AE36" s="72"/>
+      <c r="AF36" s="72"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="73"/>
       <c r="AJ36" s="8"/>
     </row>
     <row r="37" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3450,38 +3318,38 @@
       <c r="C37" s="15">
         <v>12</v>
       </c>
-      <c r="D37" s="75"/>
-      <c r="E37" s="75"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="77"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="78"/>
-      <c r="AE37" s="79"/>
-      <c r="AF37" s="79"/>
-      <c r="AG37" s="79"/>
-      <c r="AH37" s="79"/>
-      <c r="AI37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
+      <c r="K37" s="82"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="76"/>
+      <c r="U37" s="76"/>
+      <c r="V37" s="76"/>
+      <c r="W37" s="76"/>
+      <c r="X37" s="76"/>
+      <c r="Y37" s="76"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="76"/>
+      <c r="AB37" s="76"/>
+      <c r="AC37" s="76"/>
+      <c r="AD37" s="77"/>
+      <c r="AE37" s="78"/>
+      <c r="AF37" s="78"/>
+      <c r="AG37" s="78"/>
+      <c r="AH37" s="78"/>
+      <c r="AI37" s="79"/>
       <c r="AJ37" s="8"/>
     </row>
     <row r="38" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3489,38 +3357,38 @@
       <c r="C38" s="15">
         <v>13</v>
       </c>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="77"/>
-      <c r="M38" s="77"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
-      <c r="P38" s="77"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="77"/>
-      <c r="V38" s="77"/>
-      <c r="W38" s="77"/>
-      <c r="X38" s="77"/>
-      <c r="Y38" s="77"/>
-      <c r="Z38" s="77"/>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-      <c r="AC38" s="77"/>
-      <c r="AD38" s="78"/>
-      <c r="AE38" s="79"/>
-      <c r="AF38" s="79"/>
-      <c r="AG38" s="79"/>
-      <c r="AH38" s="79"/>
-      <c r="AI38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="80"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="82"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="76"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="76"/>
+      <c r="S38" s="76"/>
+      <c r="T38" s="76"/>
+      <c r="U38" s="76"/>
+      <c r="V38" s="76"/>
+      <c r="W38" s="76"/>
+      <c r="X38" s="76"/>
+      <c r="Y38" s="76"/>
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="76"/>
+      <c r="AB38" s="76"/>
+      <c r="AC38" s="76"/>
+      <c r="AD38" s="77"/>
+      <c r="AE38" s="78"/>
+      <c r="AF38" s="78"/>
+      <c r="AG38" s="78"/>
+      <c r="AH38" s="78"/>
+      <c r="AI38" s="79"/>
       <c r="AJ38" s="8"/>
     </row>
     <row r="39" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3528,38 +3396,38 @@
       <c r="C39" s="15">
         <v>14</v>
       </c>
-      <c r="D39" s="75"/>
-      <c r="E39" s="75"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
-      <c r="P39" s="77"/>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="77"/>
-      <c r="V39" s="77"/>
-      <c r="W39" s="77"/>
-      <c r="X39" s="77"/>
-      <c r="Y39" s="77"/>
-      <c r="Z39" s="77"/>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-      <c r="AC39" s="77"/>
-      <c r="AD39" s="78"/>
-      <c r="AE39" s="79"/>
-      <c r="AF39" s="79"/>
-      <c r="AG39" s="79"/>
-      <c r="AH39" s="79"/>
-      <c r="AI39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
+      <c r="K39" s="82"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="76"/>
+      <c r="N39" s="76"/>
+      <c r="O39" s="76"/>
+      <c r="P39" s="76"/>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="76"/>
+      <c r="U39" s="76"/>
+      <c r="V39" s="76"/>
+      <c r="W39" s="76"/>
+      <c r="X39" s="76"/>
+      <c r="Y39" s="76"/>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="76"/>
+      <c r="AB39" s="76"/>
+      <c r="AC39" s="76"/>
+      <c r="AD39" s="77"/>
+      <c r="AE39" s="78"/>
+      <c r="AF39" s="78"/>
+      <c r="AG39" s="78"/>
+      <c r="AH39" s="78"/>
+      <c r="AI39" s="79"/>
       <c r="AJ39" s="8"/>
     </row>
     <row r="40" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3567,373 +3435,373 @@
       <c r="C40" s="15">
         <v>15</v>
       </c>
-      <c r="D40" s="75"/>
-      <c r="E40" s="75"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="75"/>
-      <c r="H40" s="76"/>
-      <c r="I40" s="76"/>
-      <c r="J40" s="76"/>
-      <c r="K40" s="76"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="77"/>
-      <c r="W40" s="77"/>
-      <c r="X40" s="77"/>
-      <c r="Y40" s="77"/>
-      <c r="Z40" s="77"/>
-      <c r="AA40" s="77"/>
-      <c r="AB40" s="77"/>
-      <c r="AC40" s="77"/>
-      <c r="AD40" s="78"/>
-      <c r="AE40" s="79"/>
-      <c r="AF40" s="79"/>
-      <c r="AG40" s="79"/>
-      <c r="AH40" s="79"/>
-      <c r="AI40" s="80"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="80"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="76"/>
+      <c r="M40" s="76"/>
+      <c r="N40" s="76"/>
+      <c r="O40" s="76"/>
+      <c r="P40" s="76"/>
+      <c r="Q40" s="76"/>
+      <c r="R40" s="76"/>
+      <c r="S40" s="76"/>
+      <c r="T40" s="76"/>
+      <c r="U40" s="76"/>
+      <c r="V40" s="76"/>
+      <c r="W40" s="76"/>
+      <c r="X40" s="76"/>
+      <c r="Y40" s="76"/>
+      <c r="Z40" s="76"/>
+      <c r="AA40" s="76"/>
+      <c r="AB40" s="76"/>
+      <c r="AC40" s="76"/>
+      <c r="AD40" s="77"/>
+      <c r="AE40" s="78"/>
+      <c r="AF40" s="78"/>
+      <c r="AG40" s="78"/>
+      <c r="AH40" s="78"/>
+      <c r="AI40" s="79"/>
       <c r="AJ40" s="8"/>
     </row>
     <row r="41" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="14"/>
-      <c r="C41" s="81" t="s">
+      <c r="C41" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
-      <c r="M41" s="81"/>
-      <c r="N41" s="81"/>
-      <c r="O41" s="81"/>
-      <c r="P41" s="81"/>
-      <c r="Q41" s="81"/>
-      <c r="R41" s="81"/>
-      <c r="S41" s="81"/>
-      <c r="T41" s="81"/>
-      <c r="U41" s="81"/>
-      <c r="V41" s="81"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="81"/>
-      <c r="Y41" s="81"/>
-      <c r="Z41" s="81"/>
-      <c r="AA41" s="81"/>
-      <c r="AB41" s="81"/>
-      <c r="AC41" s="81"/>
-      <c r="AD41" s="81"/>
-      <c r="AE41" s="81"/>
-      <c r="AF41" s="81"/>
-      <c r="AG41" s="81"/>
-      <c r="AH41" s="81"/>
-      <c r="AI41" s="81"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="100"/>
+      <c r="N41" s="100"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="100"/>
+      <c r="Q41" s="100"/>
+      <c r="R41" s="100"/>
+      <c r="S41" s="100"/>
+      <c r="T41" s="100"/>
+      <c r="U41" s="100"/>
+      <c r="V41" s="100"/>
+      <c r="W41" s="100"/>
+      <c r="X41" s="100"/>
+      <c r="Y41" s="100"/>
+      <c r="Z41" s="100"/>
+      <c r="AA41" s="100"/>
+      <c r="AB41" s="100"/>
+      <c r="AC41" s="100"/>
+      <c r="AD41" s="100"/>
+      <c r="AE41" s="100"/>
+      <c r="AF41" s="100"/>
+      <c r="AG41" s="100"/>
+      <c r="AH41" s="100"/>
+      <c r="AI41" s="100"/>
       <c r="AJ41" s="8"/>
     </row>
     <row r="42" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="14"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="81"/>
-      <c r="N42" s="81"/>
-      <c r="O42" s="81"/>
-      <c r="P42" s="81"/>
-      <c r="Q42" s="81"/>
-      <c r="R42" s="81"/>
-      <c r="S42" s="81"/>
-      <c r="T42" s="81"/>
-      <c r="U42" s="81"/>
-      <c r="V42" s="81"/>
-      <c r="W42" s="81"/>
-      <c r="X42" s="81"/>
-      <c r="Y42" s="81"/>
-      <c r="Z42" s="81"/>
-      <c r="AA42" s="81"/>
-      <c r="AB42" s="81"/>
-      <c r="AC42" s="81"/>
-      <c r="AD42" s="81"/>
-      <c r="AE42" s="81"/>
-      <c r="AF42" s="81"/>
-      <c r="AG42" s="81"/>
-      <c r="AH42" s="81"/>
-      <c r="AI42" s="81"/>
+      <c r="C42" s="100"/>
+      <c r="D42" s="100"/>
+      <c r="E42" s="100"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="100"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="100"/>
+      <c r="M42" s="100"/>
+      <c r="N42" s="100"/>
+      <c r="O42" s="100"/>
+      <c r="P42" s="100"/>
+      <c r="Q42" s="100"/>
+      <c r="R42" s="100"/>
+      <c r="S42" s="100"/>
+      <c r="T42" s="100"/>
+      <c r="U42" s="100"/>
+      <c r="V42" s="100"/>
+      <c r="W42" s="100"/>
+      <c r="X42" s="100"/>
+      <c r="Y42" s="100"/>
+      <c r="Z42" s="100"/>
+      <c r="AA42" s="100"/>
+      <c r="AB42" s="100"/>
+      <c r="AC42" s="100"/>
+      <c r="AD42" s="100"/>
+      <c r="AE42" s="100"/>
+      <c r="AF42" s="100"/>
+      <c r="AG42" s="100"/>
+      <c r="AH42" s="100"/>
+      <c r="AI42" s="100"/>
       <c r="AJ42" s="8"/>
     </row>
     <row r="43" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="14"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="81"/>
-      <c r="G43" s="81"/>
-      <c r="H43" s="81"/>
-      <c r="I43" s="81"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="81"/>
-      <c r="L43" s="81"/>
-      <c r="M43" s="81"/>
-      <c r="N43" s="81"/>
-      <c r="O43" s="81"/>
-      <c r="P43" s="81"/>
-      <c r="Q43" s="81"/>
-      <c r="R43" s="81"/>
-      <c r="S43" s="81"/>
-      <c r="T43" s="81"/>
-      <c r="U43" s="81"/>
-      <c r="V43" s="81"/>
-      <c r="W43" s="81"/>
-      <c r="X43" s="81"/>
-      <c r="Y43" s="81"/>
-      <c r="Z43" s="81"/>
-      <c r="AA43" s="81"/>
-      <c r="AB43" s="81"/>
-      <c r="AC43" s="81"/>
-      <c r="AD43" s="81"/>
-      <c r="AE43" s="81"/>
-      <c r="AF43" s="81"/>
-      <c r="AG43" s="81"/>
-      <c r="AH43" s="81"/>
-      <c r="AI43" s="81"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="100"/>
+      <c r="J43" s="100"/>
+      <c r="K43" s="100"/>
+      <c r="L43" s="100"/>
+      <c r="M43" s="100"/>
+      <c r="N43" s="100"/>
+      <c r="O43" s="100"/>
+      <c r="P43" s="100"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="100"/>
+      <c r="S43" s="100"/>
+      <c r="T43" s="100"/>
+      <c r="U43" s="100"/>
+      <c r="V43" s="100"/>
+      <c r="W43" s="100"/>
+      <c r="X43" s="100"/>
+      <c r="Y43" s="100"/>
+      <c r="Z43" s="100"/>
+      <c r="AA43" s="100"/>
+      <c r="AB43" s="100"/>
+      <c r="AC43" s="100"/>
+      <c r="AD43" s="100"/>
+      <c r="AE43" s="100"/>
+      <c r="AF43" s="100"/>
+      <c r="AG43" s="100"/>
+      <c r="AH43" s="100"/>
+      <c r="AI43" s="100"/>
       <c r="AJ43" s="8"/>
     </row>
     <row r="44" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="14"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="81"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="81"/>
-      <c r="I44" s="81"/>
-      <c r="J44" s="81"/>
-      <c r="K44" s="81"/>
-      <c r="L44" s="81"/>
-      <c r="M44" s="81"/>
-      <c r="N44" s="81"/>
-      <c r="O44" s="81"/>
-      <c r="P44" s="81"/>
-      <c r="Q44" s="81"/>
-      <c r="R44" s="81"/>
-      <c r="S44" s="81"/>
-      <c r="T44" s="81"/>
-      <c r="U44" s="81"/>
-      <c r="V44" s="81"/>
-      <c r="W44" s="81"/>
-      <c r="X44" s="81"/>
-      <c r="Y44" s="81"/>
-      <c r="Z44" s="81"/>
-      <c r="AA44" s="81"/>
-      <c r="AB44" s="81"/>
-      <c r="AC44" s="81"/>
-      <c r="AD44" s="81"/>
-      <c r="AE44" s="81"/>
-      <c r="AF44" s="81"/>
-      <c r="AG44" s="81"/>
-      <c r="AH44" s="81"/>
-      <c r="AI44" s="81"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
+      <c r="S44" s="100"/>
+      <c r="T44" s="100"/>
+      <c r="U44" s="100"/>
+      <c r="V44" s="100"/>
+      <c r="W44" s="100"/>
+      <c r="X44" s="100"/>
+      <c r="Y44" s="100"/>
+      <c r="Z44" s="100"/>
+      <c r="AA44" s="100"/>
+      <c r="AB44" s="100"/>
+      <c r="AC44" s="100"/>
+      <c r="AD44" s="100"/>
+      <c r="AE44" s="100"/>
+      <c r="AF44" s="100"/>
+      <c r="AG44" s="100"/>
+      <c r="AH44" s="100"/>
+      <c r="AI44" s="100"/>
       <c r="AJ44" s="8"/>
     </row>
     <row r="45" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="14"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="81"/>
-      <c r="E45" s="81"/>
-      <c r="F45" s="81"/>
-      <c r="G45" s="81"/>
-      <c r="H45" s="81"/>
-      <c r="I45" s="81"/>
-      <c r="J45" s="81"/>
-      <c r="K45" s="81"/>
-      <c r="L45" s="81"/>
-      <c r="M45" s="81"/>
-      <c r="N45" s="81"/>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
-      <c r="Q45" s="81"/>
-      <c r="R45" s="81"/>
-      <c r="S45" s="81"/>
-      <c r="T45" s="81"/>
-      <c r="U45" s="81"/>
-      <c r="V45" s="81"/>
-      <c r="W45" s="81"/>
-      <c r="X45" s="81"/>
-      <c r="Y45" s="81"/>
-      <c r="Z45" s="81"/>
-      <c r="AA45" s="81"/>
-      <c r="AB45" s="81"/>
-      <c r="AC45" s="81"/>
-      <c r="AD45" s="81"/>
-      <c r="AE45" s="81"/>
-      <c r="AF45" s="81"/>
-      <c r="AG45" s="81"/>
-      <c r="AH45" s="81"/>
-      <c r="AI45" s="81"/>
+      <c r="C45" s="100"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
+      <c r="I45" s="100"/>
+      <c r="J45" s="100"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="100"/>
+      <c r="N45" s="100"/>
+      <c r="O45" s="100"/>
+      <c r="P45" s="100"/>
+      <c r="Q45" s="100"/>
+      <c r="R45" s="100"/>
+      <c r="S45" s="100"/>
+      <c r="T45" s="100"/>
+      <c r="U45" s="100"/>
+      <c r="V45" s="100"/>
+      <c r="W45" s="100"/>
+      <c r="X45" s="100"/>
+      <c r="Y45" s="100"/>
+      <c r="Z45" s="100"/>
+      <c r="AA45" s="100"/>
+      <c r="AB45" s="100"/>
+      <c r="AC45" s="100"/>
+      <c r="AD45" s="100"/>
+      <c r="AE45" s="100"/>
+      <c r="AF45" s="100"/>
+      <c r="AG45" s="100"/>
+      <c r="AH45" s="100"/>
+      <c r="AI45" s="100"/>
       <c r="AJ45" s="8"/>
     </row>
     <row r="46" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="14"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="81"/>
-      <c r="J46" s="81"/>
-      <c r="K46" s="81"/>
-      <c r="L46" s="81"/>
-      <c r="M46" s="81"/>
-      <c r="N46" s="81"/>
-      <c r="O46" s="81"/>
-      <c r="P46" s="81"/>
-      <c r="Q46" s="81"/>
-      <c r="R46" s="81"/>
-      <c r="S46" s="81"/>
-      <c r="T46" s="81"/>
-      <c r="U46" s="81"/>
-      <c r="V46" s="81"/>
-      <c r="W46" s="81"/>
-      <c r="X46" s="81"/>
-      <c r="Y46" s="81"/>
-      <c r="Z46" s="81"/>
-      <c r="AA46" s="81"/>
-      <c r="AB46" s="81"/>
-      <c r="AC46" s="81"/>
-      <c r="AD46" s="81"/>
-      <c r="AE46" s="81"/>
-      <c r="AF46" s="81"/>
-      <c r="AG46" s="81"/>
-      <c r="AH46" s="81"/>
-      <c r="AI46" s="81"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="100"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="100"/>
+      <c r="H46" s="100"/>
+      <c r="I46" s="100"/>
+      <c r="J46" s="100"/>
+      <c r="K46" s="100"/>
+      <c r="L46" s="100"/>
+      <c r="M46" s="100"/>
+      <c r="N46" s="100"/>
+      <c r="O46" s="100"/>
+      <c r="P46" s="100"/>
+      <c r="Q46" s="100"/>
+      <c r="R46" s="100"/>
+      <c r="S46" s="100"/>
+      <c r="T46" s="100"/>
+      <c r="U46" s="100"/>
+      <c r="V46" s="100"/>
+      <c r="W46" s="100"/>
+      <c r="X46" s="100"/>
+      <c r="Y46" s="100"/>
+      <c r="Z46" s="100"/>
+      <c r="AA46" s="100"/>
+      <c r="AB46" s="100"/>
+      <c r="AC46" s="100"/>
+      <c r="AD46" s="100"/>
+      <c r="AE46" s="100"/>
+      <c r="AF46" s="100"/>
+      <c r="AG46" s="100"/>
+      <c r="AH46" s="100"/>
+      <c r="AI46" s="100"/>
       <c r="AJ46" s="8"/>
     </row>
     <row r="47" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="14"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="81"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="81"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="81"/>
-      <c r="I47" s="81"/>
-      <c r="J47" s="81"/>
-      <c r="K47" s="81"/>
-      <c r="L47" s="81"/>
-      <c r="M47" s="81"/>
-      <c r="N47" s="81"/>
-      <c r="O47" s="81"/>
-      <c r="P47" s="81"/>
-      <c r="Q47" s="81"/>
-      <c r="R47" s="81"/>
-      <c r="S47" s="81"/>
-      <c r="T47" s="81"/>
-      <c r="U47" s="81"/>
-      <c r="V47" s="81"/>
-      <c r="W47" s="81"/>
-      <c r="X47" s="81"/>
-      <c r="Y47" s="81"/>
-      <c r="Z47" s="81"/>
-      <c r="AA47" s="81"/>
-      <c r="AB47" s="81"/>
-      <c r="AC47" s="81"/>
-      <c r="AD47" s="81"/>
-      <c r="AE47" s="81"/>
-      <c r="AF47" s="81"/>
-      <c r="AG47" s="81"/>
-      <c r="AH47" s="81"/>
-      <c r="AI47" s="81"/>
+      <c r="C47" s="100"/>
+      <c r="D47" s="100"/>
+      <c r="E47" s="100"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="100"/>
+      <c r="H47" s="100"/>
+      <c r="I47" s="100"/>
+      <c r="J47" s="100"/>
+      <c r="K47" s="100"/>
+      <c r="L47" s="100"/>
+      <c r="M47" s="100"/>
+      <c r="N47" s="100"/>
+      <c r="O47" s="100"/>
+      <c r="P47" s="100"/>
+      <c r="Q47" s="100"/>
+      <c r="R47" s="100"/>
+      <c r="S47" s="100"/>
+      <c r="T47" s="100"/>
+      <c r="U47" s="100"/>
+      <c r="V47" s="100"/>
+      <c r="W47" s="100"/>
+      <c r="X47" s="100"/>
+      <c r="Y47" s="100"/>
+      <c r="Z47" s="100"/>
+      <c r="AA47" s="100"/>
+      <c r="AB47" s="100"/>
+      <c r="AC47" s="100"/>
+      <c r="AD47" s="100"/>
+      <c r="AE47" s="100"/>
+      <c r="AF47" s="100"/>
+      <c r="AG47" s="100"/>
+      <c r="AH47" s="100"/>
+      <c r="AI47" s="100"/>
       <c r="AJ47" s="8"/>
     </row>
     <row r="48" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="14"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="81"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="81"/>
-      <c r="I48" s="81"/>
-      <c r="J48" s="81"/>
-      <c r="K48" s="81"/>
-      <c r="L48" s="81"/>
-      <c r="M48" s="81"/>
-      <c r="N48" s="81"/>
-      <c r="O48" s="81"/>
-      <c r="P48" s="81"/>
-      <c r="Q48" s="81"/>
-      <c r="R48" s="81"/>
-      <c r="S48" s="81"/>
-      <c r="T48" s="81"/>
-      <c r="U48" s="81"/>
-      <c r="V48" s="81"/>
-      <c r="W48" s="81"/>
-      <c r="X48" s="81"/>
-      <c r="Y48" s="81"/>
-      <c r="Z48" s="81"/>
-      <c r="AA48" s="81"/>
-      <c r="AB48" s="81"/>
-      <c r="AC48" s="81"/>
-      <c r="AD48" s="81"/>
-      <c r="AE48" s="81"/>
-      <c r="AF48" s="81"/>
-      <c r="AG48" s="81"/>
-      <c r="AH48" s="81"/>
-      <c r="AI48" s="81"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
+      <c r="I48" s="100"/>
+      <c r="J48" s="100"/>
+      <c r="K48" s="100"/>
+      <c r="L48" s="100"/>
+      <c r="M48" s="100"/>
+      <c r="N48" s="100"/>
+      <c r="O48" s="100"/>
+      <c r="P48" s="100"/>
+      <c r="Q48" s="100"/>
+      <c r="R48" s="100"/>
+      <c r="S48" s="100"/>
+      <c r="T48" s="100"/>
+      <c r="U48" s="100"/>
+      <c r="V48" s="100"/>
+      <c r="W48" s="100"/>
+      <c r="X48" s="100"/>
+      <c r="Y48" s="100"/>
+      <c r="Z48" s="100"/>
+      <c r="AA48" s="100"/>
+      <c r="AB48" s="100"/>
+      <c r="AC48" s="100"/>
+      <c r="AD48" s="100"/>
+      <c r="AE48" s="100"/>
+      <c r="AF48" s="100"/>
+      <c r="AG48" s="100"/>
+      <c r="AH48" s="100"/>
+      <c r="AI48" s="100"/>
       <c r="AJ48" s="8"/>
     </row>
     <row r="49" spans="2:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="14"/>
-      <c r="C49" s="81"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="81"/>
-      <c r="F49" s="81"/>
-      <c r="G49" s="81"/>
-      <c r="H49" s="81"/>
-      <c r="I49" s="81"/>
-      <c r="J49" s="81"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="81"/>
-      <c r="M49" s="81"/>
-      <c r="N49" s="81"/>
-      <c r="O49" s="81"/>
-      <c r="P49" s="81"/>
-      <c r="Q49" s="81"/>
-      <c r="R49" s="81"/>
-      <c r="S49" s="81"/>
-      <c r="T49" s="81"/>
-      <c r="U49" s="81"/>
-      <c r="V49" s="81"/>
-      <c r="W49" s="81"/>
-      <c r="X49" s="81"/>
-      <c r="Y49" s="81"/>
-      <c r="Z49" s="81"/>
-      <c r="AA49" s="81"/>
-      <c r="AB49" s="81"/>
-      <c r="AC49" s="81"/>
-      <c r="AD49" s="81"/>
-      <c r="AE49" s="81"/>
-      <c r="AF49" s="81"/>
-      <c r="AG49" s="81"/>
-      <c r="AH49" s="81"/>
-      <c r="AI49" s="81"/>
+      <c r="C49" s="100"/>
+      <c r="D49" s="100"/>
+      <c r="E49" s="100"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="100"/>
+      <c r="H49" s="100"/>
+      <c r="I49" s="100"/>
+      <c r="J49" s="100"/>
+      <c r="K49" s="100"/>
+      <c r="L49" s="100"/>
+      <c r="M49" s="100"/>
+      <c r="N49" s="100"/>
+      <c r="O49" s="100"/>
+      <c r="P49" s="100"/>
+      <c r="Q49" s="100"/>
+      <c r="R49" s="100"/>
+      <c r="S49" s="100"/>
+      <c r="T49" s="100"/>
+      <c r="U49" s="100"/>
+      <c r="V49" s="100"/>
+      <c r="W49" s="100"/>
+      <c r="X49" s="100"/>
+      <c r="Y49" s="100"/>
+      <c r="Z49" s="100"/>
+      <c r="AA49" s="100"/>
+      <c r="AB49" s="100"/>
+      <c r="AC49" s="100"/>
+      <c r="AD49" s="100"/>
+      <c r="AE49" s="100"/>
+      <c r="AF49" s="100"/>
+      <c r="AG49" s="100"/>
+      <c r="AH49" s="100"/>
+      <c r="AI49" s="100"/>
       <c r="AJ49" s="8"/>
     </row>
     <row r="50" spans="2:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -3973,255 +3841,255 @@
     </row>
     <row r="51" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B51" s="14"/>
-      <c r="C51" s="82" t="s">
+      <c r="C51" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="101"/>
+      <c r="F51" s="101"/>
+      <c r="G51" s="101"/>
       <c r="AJ51" s="8"/>
     </row>
     <row r="52" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B52" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="108" t="s">
+      <c r="C52" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="108"/>
-      <c r="I52" s="108"/>
-      <c r="J52" s="108"/>
-      <c r="K52" s="108"/>
-      <c r="L52" s="108"/>
-      <c r="M52" s="108"/>
-      <c r="N52" s="108"/>
-      <c r="O52" s="108"/>
-      <c r="P52" s="108"/>
-      <c r="Q52" s="108"/>
-      <c r="R52" s="108"/>
-      <c r="S52" s="108"/>
-      <c r="T52" s="108"/>
-      <c r="U52" s="108"/>
-      <c r="V52" s="108"/>
-      <c r="W52" s="108"/>
-      <c r="X52" s="108"/>
-      <c r="Y52" s="108"/>
-      <c r="Z52" s="108"/>
-      <c r="AA52" s="108"/>
-      <c r="AB52" s="108"/>
-      <c r="AC52" s="108"/>
-      <c r="AD52" s="108"/>
-      <c r="AE52" s="108"/>
-      <c r="AF52" s="108"/>
-      <c r="AG52" s="108"/>
-      <c r="AH52" s="108"/>
-      <c r="AI52" s="108"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="81"/>
+      <c r="S52" s="81"/>
+      <c r="T52" s="81"/>
+      <c r="U52" s="81"/>
+      <c r="V52" s="81"/>
+      <c r="W52" s="81"/>
+      <c r="X52" s="81"/>
+      <c r="Y52" s="81"/>
+      <c r="Z52" s="81"/>
+      <c r="AA52" s="81"/>
+      <c r="AB52" s="81"/>
+      <c r="AC52" s="81"/>
+      <c r="AD52" s="81"/>
+      <c r="AE52" s="81"/>
+      <c r="AF52" s="81"/>
+      <c r="AG52" s="81"/>
+      <c r="AH52" s="81"/>
+      <c r="AI52" s="81"/>
       <c r="AJ52" s="8"/>
     </row>
     <row r="53" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B53" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="108" t="s">
+      <c r="C53" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="108"/>
-      <c r="E53" s="108"/>
-      <c r="F53" s="108"/>
-      <c r="G53" s="108"/>
-      <c r="H53" s="108"/>
-      <c r="I53" s="108"/>
-      <c r="J53" s="108"/>
-      <c r="K53" s="108"/>
-      <c r="L53" s="108"/>
-      <c r="M53" s="108"/>
-      <c r="N53" s="108"/>
-      <c r="O53" s="108"/>
-      <c r="P53" s="108"/>
-      <c r="Q53" s="108"/>
-      <c r="R53" s="108"/>
-      <c r="S53" s="108"/>
-      <c r="T53" s="108"/>
-      <c r="U53" s="108"/>
-      <c r="V53" s="108"/>
-      <c r="W53" s="108"/>
-      <c r="X53" s="108"/>
-      <c r="Y53" s="108"/>
-      <c r="Z53" s="108"/>
-      <c r="AA53" s="108"/>
-      <c r="AB53" s="108"/>
-      <c r="AC53" s="108"/>
-      <c r="AD53" s="108"/>
-      <c r="AE53" s="108"/>
-      <c r="AF53" s="108"/>
-      <c r="AG53" s="108"/>
-      <c r="AH53" s="108"/>
-      <c r="AI53" s="108"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="81"/>
+      <c r="T53" s="81"/>
+      <c r="U53" s="81"/>
+      <c r="V53" s="81"/>
+      <c r="W53" s="81"/>
+      <c r="X53" s="81"/>
+      <c r="Y53" s="81"/>
+      <c r="Z53" s="81"/>
+      <c r="AA53" s="81"/>
+      <c r="AB53" s="81"/>
+      <c r="AC53" s="81"/>
+      <c r="AD53" s="81"/>
+      <c r="AE53" s="81"/>
+      <c r="AF53" s="81"/>
+      <c r="AG53" s="81"/>
+      <c r="AH53" s="81"/>
+      <c r="AI53" s="81"/>
       <c r="AJ53" s="8"/>
     </row>
     <row r="54" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B54" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="109" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="109"/>
-      <c r="E54" s="109"/>
-      <c r="F54" s="109"/>
-      <c r="G54" s="109"/>
-      <c r="H54" s="109"/>
-      <c r="I54" s="109"/>
-      <c r="J54" s="109"/>
-      <c r="K54" s="109"/>
-      <c r="L54" s="109"/>
-      <c r="M54" s="109"/>
-      <c r="N54" s="109"/>
-      <c r="O54" s="109"/>
-      <c r="P54" s="109"/>
-      <c r="Q54" s="109"/>
-      <c r="R54" s="109"/>
-      <c r="S54" s="109"/>
-      <c r="T54" s="109"/>
-      <c r="U54" s="109"/>
-      <c r="V54" s="109"/>
-      <c r="W54" s="109"/>
-      <c r="X54" s="109"/>
-      <c r="Y54" s="109"/>
-      <c r="Z54" s="109"/>
-      <c r="AA54" s="109"/>
-      <c r="AB54" s="109"/>
-      <c r="AC54" s="109"/>
-      <c r="AD54" s="109"/>
-      <c r="AE54" s="109"/>
-      <c r="AF54" s="109"/>
-      <c r="AG54" s="109"/>
-      <c r="AH54" s="109"/>
-      <c r="AI54" s="109"/>
+      <c r="C54" s="105" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="105"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="105"/>
+      <c r="G54" s="105"/>
+      <c r="H54" s="105"/>
+      <c r="I54" s="105"/>
+      <c r="J54" s="105"/>
+      <c r="K54" s="105"/>
+      <c r="L54" s="105"/>
+      <c r="M54" s="105"/>
+      <c r="N54" s="105"/>
+      <c r="O54" s="105"/>
+      <c r="P54" s="105"/>
+      <c r="Q54" s="105"/>
+      <c r="R54" s="105"/>
+      <c r="S54" s="105"/>
+      <c r="T54" s="105"/>
+      <c r="U54" s="105"/>
+      <c r="V54" s="105"/>
+      <c r="W54" s="105"/>
+      <c r="X54" s="105"/>
+      <c r="Y54" s="105"/>
+      <c r="Z54" s="105"/>
+      <c r="AA54" s="105"/>
+      <c r="AB54" s="105"/>
+      <c r="AC54" s="105"/>
+      <c r="AD54" s="105"/>
+      <c r="AE54" s="105"/>
+      <c r="AF54" s="105"/>
+      <c r="AG54" s="105"/>
+      <c r="AH54" s="105"/>
+      <c r="AI54" s="105"/>
       <c r="AJ54" s="8"/>
     </row>
     <row r="55" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B55" s="18"/>
-      <c r="C55" s="109"/>
-      <c r="D55" s="109"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="109"/>
-      <c r="G55" s="109"/>
-      <c r="H55" s="109"/>
-      <c r="I55" s="109"/>
-      <c r="J55" s="109"/>
-      <c r="K55" s="109"/>
-      <c r="L55" s="109"/>
-      <c r="M55" s="109"/>
-      <c r="N55" s="109"/>
-      <c r="O55" s="109"/>
-      <c r="P55" s="109"/>
-      <c r="Q55" s="109"/>
-      <c r="R55" s="109"/>
-      <c r="S55" s="109"/>
-      <c r="T55" s="109"/>
-      <c r="U55" s="109"/>
-      <c r="V55" s="109"/>
-      <c r="W55" s="109"/>
-      <c r="X55" s="109"/>
-      <c r="Y55" s="109"/>
-      <c r="Z55" s="109"/>
-      <c r="AA55" s="109"/>
-      <c r="AB55" s="109"/>
-      <c r="AC55" s="109"/>
-      <c r="AD55" s="109"/>
-      <c r="AE55" s="109"/>
-      <c r="AF55" s="109"/>
-      <c r="AG55" s="109"/>
-      <c r="AH55" s="109"/>
-      <c r="AI55" s="109"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="105"/>
+      <c r="J55" s="105"/>
+      <c r="K55" s="105"/>
+      <c r="L55" s="105"/>
+      <c r="M55" s="105"/>
+      <c r="N55" s="105"/>
+      <c r="O55" s="105"/>
+      <c r="P55" s="105"/>
+      <c r="Q55" s="105"/>
+      <c r="R55" s="105"/>
+      <c r="S55" s="105"/>
+      <c r="T55" s="105"/>
+      <c r="U55" s="105"/>
+      <c r="V55" s="105"/>
+      <c r="W55" s="105"/>
+      <c r="X55" s="105"/>
+      <c r="Y55" s="105"/>
+      <c r="Z55" s="105"/>
+      <c r="AA55" s="105"/>
+      <c r="AB55" s="105"/>
+      <c r="AC55" s="105"/>
+      <c r="AD55" s="105"/>
+      <c r="AE55" s="105"/>
+      <c r="AF55" s="105"/>
+      <c r="AG55" s="105"/>
+      <c r="AH55" s="105"/>
+      <c r="AI55" s="105"/>
       <c r="AJ55" s="8"/>
     </row>
     <row r="56" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B56" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="108" t="s">
+      <c r="C56" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D56" s="108"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="108"/>
-      <c r="G56" s="108"/>
-      <c r="H56" s="108"/>
-      <c r="I56" s="108"/>
-      <c r="J56" s="108"/>
-      <c r="K56" s="108"/>
-      <c r="L56" s="108"/>
-      <c r="M56" s="108"/>
-      <c r="N56" s="108"/>
-      <c r="O56" s="108"/>
-      <c r="P56" s="108"/>
-      <c r="Q56" s="108"/>
-      <c r="R56" s="108"/>
-      <c r="S56" s="108"/>
-      <c r="T56" s="108"/>
-      <c r="U56" s="108"/>
-      <c r="V56" s="108"/>
-      <c r="W56" s="108"/>
-      <c r="X56" s="108"/>
-      <c r="Y56" s="108"/>
-      <c r="Z56" s="108"/>
-      <c r="AA56" s="108"/>
-      <c r="AB56" s="108"/>
-      <c r="AC56" s="108"/>
-      <c r="AD56" s="108"/>
-      <c r="AE56" s="108"/>
-      <c r="AF56" s="108"/>
-      <c r="AG56" s="108"/>
-      <c r="AH56" s="108"/>
-      <c r="AI56" s="108"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="81"/>
+      <c r="N56" s="81"/>
+      <c r="O56" s="81"/>
+      <c r="P56" s="81"/>
+      <c r="Q56" s="81"/>
+      <c r="R56" s="81"/>
+      <c r="S56" s="81"/>
+      <c r="T56" s="81"/>
+      <c r="U56" s="81"/>
+      <c r="V56" s="81"/>
+      <c r="W56" s="81"/>
+      <c r="X56" s="81"/>
+      <c r="Y56" s="81"/>
+      <c r="Z56" s="81"/>
+      <c r="AA56" s="81"/>
+      <c r="AB56" s="81"/>
+      <c r="AC56" s="81"/>
+      <c r="AD56" s="81"/>
+      <c r="AE56" s="81"/>
+      <c r="AF56" s="81"/>
+      <c r="AG56" s="81"/>
+      <c r="AH56" s="81"/>
+      <c r="AI56" s="81"/>
       <c r="AJ56" s="8"/>
     </row>
     <row r="57" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B57" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="108" t="s">
+      <c r="C57" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="108"/>
-      <c r="E57" s="108"/>
-      <c r="F57" s="108"/>
-      <c r="G57" s="108"/>
-      <c r="H57" s="108"/>
-      <c r="I57" s="108"/>
-      <c r="J57" s="108"/>
-      <c r="K57" s="108"/>
-      <c r="L57" s="108"/>
-      <c r="M57" s="108"/>
-      <c r="N57" s="108"/>
-      <c r="O57" s="108"/>
-      <c r="P57" s="108"/>
-      <c r="Q57" s="108"/>
-      <c r="R57" s="108"/>
-      <c r="S57" s="108"/>
-      <c r="T57" s="108"/>
-      <c r="U57" s="108"/>
-      <c r="V57" s="108"/>
-      <c r="W57" s="108"/>
-      <c r="X57" s="108"/>
-      <c r="Y57" s="108"/>
-      <c r="Z57" s="108"/>
-      <c r="AA57" s="108"/>
-      <c r="AB57" s="108"/>
-      <c r="AC57" s="108"/>
-      <c r="AD57" s="108"/>
-      <c r="AE57" s="108"/>
-      <c r="AF57" s="108"/>
-      <c r="AG57" s="108"/>
-      <c r="AH57" s="108"/>
-      <c r="AI57" s="108"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81"/>
+      <c r="N57" s="81"/>
+      <c r="O57" s="81"/>
+      <c r="P57" s="81"/>
+      <c r="Q57" s="81"/>
+      <c r="R57" s="81"/>
+      <c r="S57" s="81"/>
+      <c r="T57" s="81"/>
+      <c r="U57" s="81"/>
+      <c r="V57" s="81"/>
+      <c r="W57" s="81"/>
+      <c r="X57" s="81"/>
+      <c r="Y57" s="81"/>
+      <c r="Z57" s="81"/>
+      <c r="AA57" s="81"/>
+      <c r="AB57" s="81"/>
+      <c r="AC57" s="81"/>
+      <c r="AD57" s="81"/>
+      <c r="AE57" s="81"/>
+      <c r="AF57" s="81"/>
+      <c r="AG57" s="81"/>
+      <c r="AH57" s="81"/>
+      <c r="AI57" s="81"/>
       <c r="AJ57" s="8"/>
     </row>
     <row r="58" spans="2:36" ht="3" customHeight="1" x14ac:dyDescent="0.35">
@@ -4234,345 +4102,345 @@
     </row>
     <row r="60" spans="2:36" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="14"/>
-      <c r="H60" s="83" t="s">
+      <c r="H60" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="I60" s="84"/>
-      <c r="J60" s="84"/>
-      <c r="K60" s="84"/>
-      <c r="L60" s="84"/>
-      <c r="M60" s="84"/>
-      <c r="N60" s="84"/>
-      <c r="O60" s="84"/>
-      <c r="P60" s="84"/>
-      <c r="Q60" s="84"/>
-      <c r="R60" s="84"/>
-      <c r="S60" s="84"/>
-      <c r="T60" s="84"/>
-      <c r="U60" s="84"/>
-      <c r="V60" s="84"/>
-      <c r="W60" s="84"/>
-      <c r="X60" s="84"/>
-      <c r="Y60" s="84"/>
-      <c r="Z60" s="84"/>
-      <c r="AA60" s="84"/>
-      <c r="AB60" s="84"/>
-      <c r="AC60" s="84"/>
-      <c r="AD60" s="84"/>
+      <c r="I60" s="103"/>
+      <c r="J60" s="103"/>
+      <c r="K60" s="103"/>
+      <c r="L60" s="103"/>
+      <c r="M60" s="103"/>
+      <c r="N60" s="103"/>
+      <c r="O60" s="103"/>
+      <c r="P60" s="103"/>
+      <c r="Q60" s="103"/>
+      <c r="R60" s="103"/>
+      <c r="S60" s="103"/>
+      <c r="T60" s="103"/>
+      <c r="U60" s="103"/>
+      <c r="V60" s="103"/>
+      <c r="W60" s="103"/>
+      <c r="X60" s="103"/>
+      <c r="Y60" s="103"/>
+      <c r="Z60" s="103"/>
+      <c r="AA60" s="103"/>
+      <c r="AB60" s="103"/>
+      <c r="AC60" s="103"/>
+      <c r="AD60" s="103"/>
       <c r="AJ60" s="8"/>
     </row>
     <row r="61" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B61" s="14"/>
-      <c r="H61" s="85" t="s">
+      <c r="H61" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="I61" s="85"/>
-      <c r="J61" s="85"/>
-      <c r="K61" s="85"/>
-      <c r="L61" s="85"/>
-      <c r="M61" s="85"/>
-      <c r="N61" s="85"/>
-      <c r="O61" s="85"/>
-      <c r="P61" s="85"/>
-      <c r="Q61" s="85"/>
-      <c r="R61" s="85"/>
-      <c r="S61" s="85"/>
-      <c r="T61" s="85"/>
-      <c r="U61" s="85"/>
-      <c r="V61" s="85"/>
-      <c r="W61" s="85"/>
-      <c r="X61" s="85"/>
-      <c r="Y61" s="85"/>
-      <c r="Z61" s="85"/>
-      <c r="AA61" s="85"/>
-      <c r="AB61" s="85"/>
-      <c r="AC61" s="85"/>
-      <c r="AD61" s="85"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="104"/>
+      <c r="N61" s="104"/>
+      <c r="O61" s="104"/>
+      <c r="P61" s="104"/>
+      <c r="Q61" s="104"/>
+      <c r="R61" s="104"/>
+      <c r="S61" s="104"/>
+      <c r="T61" s="104"/>
+      <c r="U61" s="104"/>
+      <c r="V61" s="104"/>
+      <c r="W61" s="104"/>
+      <c r="X61" s="104"/>
+      <c r="Y61" s="104"/>
+      <c r="Z61" s="104"/>
+      <c r="AA61" s="104"/>
+      <c r="AB61" s="104"/>
+      <c r="AC61" s="104"/>
+      <c r="AD61" s="104"/>
       <c r="AJ61" s="8"/>
     </row>
     <row r="62" spans="2:36" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="14"/>
-      <c r="C62" s="86" t="s">
+      <c r="C62" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="D62" s="86"/>
-      <c r="E62" s="86"/>
-      <c r="F62" s="86"/>
-      <c r="G62" s="86"/>
-      <c r="H62" s="87" t="s">
+      <c r="D62" s="87"/>
+      <c r="E62" s="87"/>
+      <c r="F62" s="87"/>
+      <c r="G62" s="87"/>
+      <c r="H62" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="I62" s="87"/>
-      <c r="J62" s="87"/>
-      <c r="K62" s="87"/>
-      <c r="L62" s="87"/>
-      <c r="M62" s="88" t="s">
+      <c r="I62" s="88"/>
+      <c r="J62" s="88"/>
+      <c r="K62" s="88"/>
+      <c r="L62" s="88"/>
+      <c r="M62" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="N62" s="89"/>
-      <c r="O62" s="89"/>
-      <c r="P62" s="89"/>
-      <c r="Q62" s="89"/>
-      <c r="R62" s="90"/>
-      <c r="S62" s="87" t="s">
+      <c r="N62" s="90"/>
+      <c r="O62" s="90"/>
+      <c r="P62" s="90"/>
+      <c r="Q62" s="90"/>
+      <c r="R62" s="91"/>
+      <c r="S62" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="T62" s="87"/>
-      <c r="U62" s="87"/>
-      <c r="V62" s="87"/>
-      <c r="W62" s="87"/>
-      <c r="X62" s="91"/>
-      <c r="Y62" s="92"/>
-      <c r="Z62" s="92"/>
-      <c r="AA62" s="92"/>
-      <c r="AB62" s="92"/>
-      <c r="AC62" s="92"/>
-      <c r="AD62" s="92"/>
-      <c r="AE62" s="92"/>
-      <c r="AF62" s="92"/>
-      <c r="AG62" s="92"/>
-      <c r="AH62" s="92"/>
-      <c r="AI62" s="93"/>
+      <c r="T62" s="88"/>
+      <c r="U62" s="88"/>
+      <c r="V62" s="88"/>
+      <c r="W62" s="88"/>
+      <c r="X62" s="95"/>
+      <c r="Y62" s="96"/>
+      <c r="Z62" s="96"/>
+      <c r="AA62" s="96"/>
+      <c r="AB62" s="96"/>
+      <c r="AC62" s="96"/>
+      <c r="AD62" s="96"/>
+      <c r="AE62" s="96"/>
+      <c r="AF62" s="96"/>
+      <c r="AG62" s="96"/>
+      <c r="AH62" s="96"/>
+      <c r="AI62" s="97"/>
       <c r="AJ62" s="8"/>
     </row>
     <row r="63" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B63" s="14"/>
-      <c r="C63" s="94"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="94"/>
-      <c r="F63" s="94"/>
-      <c r="G63" s="94"/>
-      <c r="H63" s="94"/>
-      <c r="I63" s="94"/>
-      <c r="J63" s="94"/>
-      <c r="K63" s="94"/>
-      <c r="L63" s="94"/>
-      <c r="M63" s="95"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="28"/>
-      <c r="S63" s="94"/>
-      <c r="T63" s="94"/>
-      <c r="U63" s="94"/>
-      <c r="V63" s="94"/>
-      <c r="W63" s="94"/>
-      <c r="X63" s="96" t="s">
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="92"/>
+      <c r="F63" s="92"/>
+      <c r="G63" s="92"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
+      <c r="J63" s="92"/>
+      <c r="K63" s="92"/>
+      <c r="L63" s="92"/>
+      <c r="M63" s="93"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="28"/>
+      <c r="P63" s="28"/>
+      <c r="Q63" s="28"/>
+      <c r="R63" s="29"/>
+      <c r="S63" s="92"/>
+      <c r="T63" s="92"/>
+      <c r="U63" s="92"/>
+      <c r="V63" s="92"/>
+      <c r="W63" s="92"/>
+      <c r="X63" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="Y63" s="97"/>
-      <c r="Z63" s="97"/>
-      <c r="AA63" s="97"/>
-      <c r="AB63" s="97"/>
-      <c r="AC63" s="97"/>
-      <c r="AD63" s="97"/>
-      <c r="AE63" s="97"/>
-      <c r="AF63" s="97"/>
-      <c r="AG63" s="97"/>
-      <c r="AH63" s="97"/>
-      <c r="AI63" s="97"/>
+      <c r="Y63" s="99"/>
+      <c r="Z63" s="99"/>
+      <c r="AA63" s="99"/>
+      <c r="AB63" s="99"/>
+      <c r="AC63" s="99"/>
+      <c r="AD63" s="99"/>
+      <c r="AE63" s="99"/>
+      <c r="AF63" s="99"/>
+      <c r="AG63" s="99"/>
+      <c r="AH63" s="99"/>
+      <c r="AI63" s="99"/>
       <c r="AJ63" s="8"/>
     </row>
     <row r="64" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B64" s="14"/>
-      <c r="C64" s="94"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="94"/>
-      <c r="F64" s="94"/>
-      <c r="G64" s="94"/>
-      <c r="H64" s="94"/>
-      <c r="I64" s="94"/>
-      <c r="J64" s="94"/>
-      <c r="K64" s="94"/>
-      <c r="L64" s="94"/>
-      <c r="M64" s="95"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="94"/>
-      <c r="T64" s="94"/>
-      <c r="U64" s="94"/>
-      <c r="V64" s="94"/>
-      <c r="W64" s="94"/>
-      <c r="X64" s="97"/>
-      <c r="Y64" s="97"/>
-      <c r="Z64" s="97"/>
-      <c r="AA64" s="97"/>
-      <c r="AB64" s="97"/>
-      <c r="AC64" s="97"/>
-      <c r="AD64" s="97"/>
-      <c r="AE64" s="97"/>
-      <c r="AF64" s="97"/>
-      <c r="AG64" s="97"/>
-      <c r="AH64" s="97"/>
-      <c r="AI64" s="97"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="92"/>
+      <c r="F64" s="92"/>
+      <c r="G64" s="92"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
+      <c r="J64" s="92"/>
+      <c r="K64" s="92"/>
+      <c r="L64" s="92"/>
+      <c r="M64" s="93"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="92"/>
+      <c r="T64" s="92"/>
+      <c r="U64" s="92"/>
+      <c r="V64" s="92"/>
+      <c r="W64" s="92"/>
+      <c r="X64" s="99"/>
+      <c r="Y64" s="99"/>
+      <c r="Z64" s="99"/>
+      <c r="AA64" s="99"/>
+      <c r="AB64" s="99"/>
+      <c r="AC64" s="99"/>
+      <c r="AD64" s="99"/>
+      <c r="AE64" s="99"/>
+      <c r="AF64" s="99"/>
+      <c r="AG64" s="99"/>
+      <c r="AH64" s="99"/>
+      <c r="AI64" s="99"/>
       <c r="AJ64" s="8"/>
     </row>
     <row r="65" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B65" s="14"/>
-      <c r="C65" s="94"/>
-      <c r="D65" s="94"/>
-      <c r="E65" s="94"/>
-      <c r="F65" s="94"/>
-      <c r="G65" s="94"/>
-      <c r="H65" s="94"/>
-      <c r="I65" s="94"/>
-      <c r="J65" s="94"/>
-      <c r="K65" s="94"/>
-      <c r="L65" s="94"/>
-      <c r="M65" s="95"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
-      <c r="P65" s="27"/>
-      <c r="Q65" s="27"/>
-      <c r="R65" s="28"/>
-      <c r="S65" s="94"/>
-      <c r="T65" s="94"/>
-      <c r="U65" s="94"/>
-      <c r="V65" s="94"/>
-      <c r="W65" s="94"/>
-      <c r="X65" s="97"/>
-      <c r="Y65" s="97"/>
-      <c r="Z65" s="97"/>
-      <c r="AA65" s="97"/>
-      <c r="AB65" s="97"/>
-      <c r="AC65" s="97"/>
-      <c r="AD65" s="97"/>
-      <c r="AE65" s="97"/>
-      <c r="AF65" s="97"/>
-      <c r="AG65" s="97"/>
-      <c r="AH65" s="97"/>
-      <c r="AI65" s="97"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="92"/>
+      <c r="E65" s="92"/>
+      <c r="F65" s="92"/>
+      <c r="G65" s="92"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
+      <c r="J65" s="92"/>
+      <c r="K65" s="92"/>
+      <c r="L65" s="92"/>
+      <c r="M65" s="93"/>
+      <c r="N65" s="28"/>
+      <c r="O65" s="28"/>
+      <c r="P65" s="28"/>
+      <c r="Q65" s="28"/>
+      <c r="R65" s="29"/>
+      <c r="S65" s="92"/>
+      <c r="T65" s="92"/>
+      <c r="U65" s="92"/>
+      <c r="V65" s="92"/>
+      <c r="W65" s="92"/>
+      <c r="X65" s="99"/>
+      <c r="Y65" s="99"/>
+      <c r="Z65" s="99"/>
+      <c r="AA65" s="99"/>
+      <c r="AB65" s="99"/>
+      <c r="AC65" s="99"/>
+      <c r="AD65" s="99"/>
+      <c r="AE65" s="99"/>
+      <c r="AF65" s="99"/>
+      <c r="AG65" s="99"/>
+      <c r="AH65" s="99"/>
+      <c r="AI65" s="99"/>
       <c r="AJ65" s="8"/>
     </row>
     <row r="66" spans="2:36" x14ac:dyDescent="0.35">
       <c r="B66" s="14"/>
-      <c r="C66" s="94"/>
-      <c r="D66" s="94"/>
-      <c r="E66" s="94"/>
-      <c r="F66" s="94"/>
-      <c r="G66" s="94"/>
-      <c r="H66" s="94"/>
-      <c r="I66" s="94"/>
-      <c r="J66" s="94"/>
-      <c r="K66" s="94"/>
-      <c r="L66" s="94"/>
-      <c r="M66" s="95"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="28"/>
-      <c r="S66" s="94"/>
-      <c r="T66" s="94"/>
-      <c r="U66" s="94"/>
-      <c r="V66" s="94"/>
-      <c r="W66" s="94"/>
-      <c r="X66" s="97"/>
-      <c r="Y66" s="97"/>
-      <c r="Z66" s="97"/>
-      <c r="AA66" s="97"/>
-      <c r="AB66" s="97"/>
-      <c r="AC66" s="97"/>
-      <c r="AD66" s="97"/>
-      <c r="AE66" s="97"/>
-      <c r="AF66" s="97"/>
-      <c r="AG66" s="97"/>
-      <c r="AH66" s="97"/>
-      <c r="AI66" s="97"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="92"/>
+      <c r="F66" s="92"/>
+      <c r="G66" s="92"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
+      <c r="J66" s="92"/>
+      <c r="K66" s="92"/>
+      <c r="L66" s="92"/>
+      <c r="M66" s="93"/>
+      <c r="N66" s="28"/>
+      <c r="O66" s="28"/>
+      <c r="P66" s="28"/>
+      <c r="Q66" s="28"/>
+      <c r="R66" s="29"/>
+      <c r="S66" s="92"/>
+      <c r="T66" s="92"/>
+      <c r="U66" s="92"/>
+      <c r="V66" s="92"/>
+      <c r="W66" s="92"/>
+      <c r="X66" s="99"/>
+      <c r="Y66" s="99"/>
+      <c r="Z66" s="99"/>
+      <c r="AA66" s="99"/>
+      <c r="AB66" s="99"/>
+      <c r="AC66" s="99"/>
+      <c r="AD66" s="99"/>
+      <c r="AE66" s="99"/>
+      <c r="AF66" s="99"/>
+      <c r="AG66" s="99"/>
+      <c r="AH66" s="99"/>
+      <c r="AI66" s="99"/>
       <c r="AJ66" s="8"/>
     </row>
     <row r="67" spans="2:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B67" s="14"/>
-      <c r="C67" s="99" t="s">
+      <c r="C67" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="99"/>
-      <c r="E67" s="99"/>
-      <c r="F67" s="99"/>
-      <c r="G67" s="99"/>
-      <c r="H67" s="99" t="s">
+      <c r="D67" s="83"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="83"/>
+      <c r="G67" s="83"/>
+      <c r="H67" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="I67" s="99"/>
-      <c r="J67" s="99"/>
-      <c r="K67" s="99"/>
-      <c r="L67" s="99"/>
-      <c r="M67" s="100" t="s">
+      <c r="I67" s="83"/>
+      <c r="J67" s="83"/>
+      <c r="K67" s="83"/>
+      <c r="L67" s="83"/>
+      <c r="M67" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="N67" s="101"/>
-      <c r="O67" s="101"/>
-      <c r="P67" s="101"/>
-      <c r="Q67" s="101"/>
-      <c r="R67" s="102"/>
-      <c r="S67" s="49" t="s">
+      <c r="N67" s="85"/>
+      <c r="O67" s="85"/>
+      <c r="P67" s="85"/>
+      <c r="Q67" s="85"/>
+      <c r="R67" s="86"/>
+      <c r="S67" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="T67" s="49"/>
-      <c r="U67" s="49"/>
-      <c r="V67" s="49"/>
-      <c r="W67" s="49"/>
-      <c r="X67" s="97"/>
-      <c r="Y67" s="97"/>
-      <c r="Z67" s="97"/>
-      <c r="AA67" s="97"/>
-      <c r="AB67" s="97"/>
-      <c r="AC67" s="97"/>
-      <c r="AD67" s="97"/>
-      <c r="AE67" s="97"/>
-      <c r="AF67" s="97"/>
-      <c r="AG67" s="97"/>
-      <c r="AH67" s="97"/>
-      <c r="AI67" s="97"/>
+      <c r="T67" s="50"/>
+      <c r="U67" s="50"/>
+      <c r="V67" s="50"/>
+      <c r="W67" s="50"/>
+      <c r="X67" s="99"/>
+      <c r="Y67" s="99"/>
+      <c r="Z67" s="99"/>
+      <c r="AA67" s="99"/>
+      <c r="AB67" s="99"/>
+      <c r="AC67" s="99"/>
+      <c r="AD67" s="99"/>
+      <c r="AE67" s="99"/>
+      <c r="AF67" s="99"/>
+      <c r="AG67" s="99"/>
+      <c r="AH67" s="99"/>
+      <c r="AI67" s="99"/>
       <c r="AJ67" s="8"/>
     </row>
     <row r="68" spans="2:36" ht="19" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="14"/>
-      <c r="C68" s="68" t="s">
+      <c r="C68" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="50" t="s">
+      <c r="D68" s="69"/>
+      <c r="E68" s="69"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="I68" s="50"/>
-      <c r="J68" s="50"/>
-      <c r="K68" s="50"/>
-      <c r="L68" s="50"/>
-      <c r="M68" s="65" t="s">
+      <c r="I68" s="51"/>
+      <c r="J68" s="51"/>
+      <c r="K68" s="51"/>
+      <c r="L68" s="51"/>
+      <c r="M68" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="N68" s="66"/>
-      <c r="O68" s="66"/>
-      <c r="P68" s="66"/>
-      <c r="Q68" s="66"/>
-      <c r="R68" s="67"/>
-      <c r="S68" s="68" t="s">
+      <c r="N68" s="67"/>
+      <c r="O68" s="67"/>
+      <c r="P68" s="67"/>
+      <c r="Q68" s="67"/>
+      <c r="R68" s="68"/>
+      <c r="S68" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="T68" s="68"/>
-      <c r="U68" s="68"/>
-      <c r="V68" s="68"/>
-      <c r="W68" s="68"/>
-      <c r="X68" s="97"/>
-      <c r="Y68" s="97"/>
-      <c r="Z68" s="97"/>
-      <c r="AA68" s="97"/>
-      <c r="AB68" s="97"/>
-      <c r="AC68" s="97"/>
-      <c r="AD68" s="97"/>
-      <c r="AE68" s="97"/>
-      <c r="AF68" s="97"/>
-      <c r="AG68" s="97"/>
-      <c r="AH68" s="97"/>
-      <c r="AI68" s="97"/>
+      <c r="T68" s="69"/>
+      <c r="U68" s="69"/>
+      <c r="V68" s="69"/>
+      <c r="W68" s="69"/>
+      <c r="X68" s="99"/>
+      <c r="Y68" s="99"/>
+      <c r="Z68" s="99"/>
+      <c r="AA68" s="99"/>
+      <c r="AB68" s="99"/>
+      <c r="AC68" s="99"/>
+      <c r="AD68" s="99"/>
+      <c r="AE68" s="99"/>
+      <c r="AF68" s="99"/>
+      <c r="AG68" s="99"/>
+      <c r="AH68" s="99"/>
+      <c r="AI68" s="99"/>
       <c r="AJ68" s="8"/>
     </row>
     <row r="69" spans="2:36" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4613,14 +4481,14 @@
       <c r="AJ69" s="22"/>
     </row>
     <row r="70" spans="2:36" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="AE70" s="98" t="s">
+      <c r="AE70" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="AF70" s="98"/>
-      <c r="AG70" s="98"/>
-      <c r="AH70" s="98"/>
-      <c r="AI70" s="98"/>
-      <c r="AJ70" s="98"/>
+      <c r="AF70" s="94"/>
+      <c r="AG70" s="94"/>
+      <c r="AH70" s="94"/>
+      <c r="AI70" s="94"/>
+      <c r="AJ70" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="223">
@@ -4633,6 +4501,21 @@
     <mergeCell ref="C54:AI55"/>
     <mergeCell ref="C56:AI56"/>
     <mergeCell ref="AA8:AI8"/>
+    <mergeCell ref="R40:T40"/>
+    <mergeCell ref="U40:W40"/>
+    <mergeCell ref="X40:Z40"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="O39:Q39"/>
+    <mergeCell ref="R39:T39"/>
+    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="U37:W37"/>
     <mergeCell ref="AA7:AI7"/>
     <mergeCell ref="I7:Q7"/>
     <mergeCell ref="I8:Q8"/>
@@ -4642,23 +4525,7 @@
     <mergeCell ref="I12:Q12"/>
     <mergeCell ref="I13:Q13"/>
     <mergeCell ref="AE70:AJ70"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:L67"/>
-    <mergeCell ref="M67:R67"/>
-    <mergeCell ref="S67:W67"/>
-    <mergeCell ref="C68:G68"/>
-    <mergeCell ref="H68:L68"/>
-    <mergeCell ref="M68:R68"/>
-    <mergeCell ref="S68:W68"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="H62:L62"/>
-    <mergeCell ref="M62:R62"/>
-    <mergeCell ref="S62:W62"/>
     <mergeCell ref="X62:AI62"/>
-    <mergeCell ref="C63:G66"/>
-    <mergeCell ref="H63:L66"/>
-    <mergeCell ref="M63:R66"/>
-    <mergeCell ref="S63:W66"/>
     <mergeCell ref="X63:AI68"/>
     <mergeCell ref="AA40:AC40"/>
     <mergeCell ref="AD40:AI40"/>
@@ -4673,15 +4540,22 @@
     <mergeCell ref="H40:K40"/>
     <mergeCell ref="L40:N40"/>
     <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="R40:T40"/>
-    <mergeCell ref="U40:W40"/>
-    <mergeCell ref="X40:Z40"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="L39:N39"/>
-    <mergeCell ref="O39:Q39"/>
-    <mergeCell ref="R39:T39"/>
-    <mergeCell ref="U39:W39"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:L67"/>
+    <mergeCell ref="M67:R67"/>
+    <mergeCell ref="S67:W67"/>
+    <mergeCell ref="C68:G68"/>
+    <mergeCell ref="H68:L68"/>
+    <mergeCell ref="M68:R68"/>
+    <mergeCell ref="S68:W68"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="H62:L62"/>
+    <mergeCell ref="M62:R62"/>
+    <mergeCell ref="S62:W62"/>
+    <mergeCell ref="C63:G66"/>
+    <mergeCell ref="H63:L66"/>
+    <mergeCell ref="M63:R66"/>
+    <mergeCell ref="S63:W66"/>
     <mergeCell ref="C57:AI57"/>
     <mergeCell ref="D38:G38"/>
     <mergeCell ref="H38:K38"/>
@@ -4692,12 +4566,6 @@
     <mergeCell ref="X38:Z38"/>
     <mergeCell ref="AA38:AC38"/>
     <mergeCell ref="AD38:AI38"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="H37:K37"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="R37:T37"/>
-    <mergeCell ref="U37:W37"/>
     <mergeCell ref="X37:Z37"/>
     <mergeCell ref="AA37:AC37"/>
     <mergeCell ref="AD37:AI37"/>
@@ -4773,6 +4641,7 @@
     <mergeCell ref="X29:Z29"/>
     <mergeCell ref="AA29:AC29"/>
     <mergeCell ref="AD29:AI29"/>
+    <mergeCell ref="AD26:AI26"/>
     <mergeCell ref="X27:Z27"/>
     <mergeCell ref="AA27:AC27"/>
     <mergeCell ref="AD27:AI27"/>
@@ -4791,6 +4660,9 @@
     <mergeCell ref="U27:W27"/>
     <mergeCell ref="AA28:AC28"/>
     <mergeCell ref="AD28:AI28"/>
+    <mergeCell ref="U25:W25"/>
+    <mergeCell ref="X25:Z25"/>
+    <mergeCell ref="AA25:AC25"/>
     <mergeCell ref="D26:G26"/>
     <mergeCell ref="H26:K26"/>
     <mergeCell ref="L26:N26"/>
@@ -4799,7 +4671,10 @@
     <mergeCell ref="U26:W26"/>
     <mergeCell ref="X26:Z26"/>
     <mergeCell ref="AA26:AC26"/>
-    <mergeCell ref="AD26:AI26"/>
+    <mergeCell ref="S11:Y11"/>
+    <mergeCell ref="AA11:AI11"/>
+    <mergeCell ref="AA10:AI10"/>
+    <mergeCell ref="AA9:AI9"/>
     <mergeCell ref="L24:N24"/>
     <mergeCell ref="O24:Q24"/>
     <mergeCell ref="R24:T24"/>
@@ -4820,9 +4695,6 @@
     <mergeCell ref="L25:N25"/>
     <mergeCell ref="O25:Q25"/>
     <mergeCell ref="R25:T25"/>
-    <mergeCell ref="U25:W25"/>
-    <mergeCell ref="X25:Z25"/>
-    <mergeCell ref="AA25:AC25"/>
     <mergeCell ref="B2:G5"/>
     <mergeCell ref="H2:AJ5"/>
     <mergeCell ref="B6:AJ6"/>
@@ -4843,10 +4715,6 @@
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="S10:Y10"/>
     <mergeCell ref="B11:G11"/>
-    <mergeCell ref="S11:Y11"/>
-    <mergeCell ref="AA11:AI11"/>
-    <mergeCell ref="AA10:AI10"/>
-    <mergeCell ref="AA9:AI9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0.23999999999999996" bottom="0" header="0" footer="0"/>
